--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="277">
   <si>
     <t>Buy Date</t>
   </si>
@@ -488,6 +488,9 @@
   </si>
   <si>
     <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1205,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S325"/>
+  <dimension ref="A1:S330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1282,13 +1285,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1318,7 +1321,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1338,13 +1341,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1374,7 +1377,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1397,13 +1400,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1433,7 +1436,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1453,13 +1456,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1489,7 +1492,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1509,13 +1512,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1545,7 +1548,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1565,13 +1568,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1601,7 +1604,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1621,13 +1624,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1657,7 +1660,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1677,13 +1680,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1713,7 +1716,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1733,13 +1736,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1769,7 +1772,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1789,13 +1792,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1816,7 +1819,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1825,7 +1828,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1840,7 +1843,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1848,13 +1851,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1884,7 +1887,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1907,13 +1910,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1943,7 +1946,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1963,13 +1966,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1999,7 +2002,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2019,13 +2022,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2055,7 +2058,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2075,13 +2078,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2111,7 +2114,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2131,13 +2134,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2167,7 +2170,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2187,13 +2190,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2223,7 +2226,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2243,13 +2246,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2279,7 +2282,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2299,13 +2302,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2335,7 +2338,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2355,13 +2358,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2382,7 +2385,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2391,7 +2394,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2411,13 +2414,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2438,7 +2441,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2447,7 +2450,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2467,13 +2470,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2503,7 +2506,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2523,13 +2526,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2559,7 +2562,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2579,13 +2582,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2615,7 +2618,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2635,13 +2638,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2662,7 +2665,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2671,7 +2674,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2691,13 +2694,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2727,7 +2730,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2747,13 +2750,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2783,7 +2786,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2803,13 +2806,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2839,7 +2842,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2859,13 +2862,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2895,7 +2898,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2915,13 +2918,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2942,7 +2945,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2951,7 +2954,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2971,13 +2974,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3007,7 +3010,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3027,13 +3030,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3063,7 +3066,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3083,13 +3086,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3110,7 +3113,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3119,7 +3122,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3139,13 +3142,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3166,7 +3169,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3175,7 +3178,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3195,13 +3198,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3231,7 +3234,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3251,13 +3254,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3287,7 +3290,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3307,13 +3310,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C38" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3343,7 +3346,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3366,13 +3369,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3402,7 +3405,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3422,13 +3425,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D40" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3458,7 +3461,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3478,13 +3481,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3514,7 +3517,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3534,13 +3537,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3561,7 +3564,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3570,7 +3573,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3590,13 +3593,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D43" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3617,7 +3620,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3626,7 +3629,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3646,13 +3649,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3682,7 +3685,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3702,13 +3705,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3738,7 +3741,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3758,13 +3761,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3794,7 +3797,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3817,13 +3820,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3853,7 +3856,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3873,13 +3876,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3909,7 +3912,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3929,13 +3932,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3965,7 +3968,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3988,13 +3991,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4024,7 +4027,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4044,13 +4047,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4080,7 +4083,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4100,13 +4103,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4136,7 +4139,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4159,13 +4162,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4195,7 +4198,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4215,13 +4218,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4251,7 +4254,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4274,13 +4277,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4310,7 +4313,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4333,13 +4336,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C56" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4369,7 +4372,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4389,13 +4392,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4416,7 +4419,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4425,7 +4428,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4445,13 +4448,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C58" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4481,7 +4484,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4501,13 +4504,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4537,7 +4540,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4560,13 +4563,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4596,7 +4599,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4616,13 +4619,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4652,7 +4655,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4675,13 +4678,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4711,7 +4714,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4726,7 +4729,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4734,13 +4737,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4770,7 +4773,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4790,13 +4793,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C64" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4826,7 +4829,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4846,13 +4849,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4882,7 +4885,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4902,13 +4905,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D66" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4938,7 +4941,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4958,13 +4961,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4994,7 +4997,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5014,13 +5017,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5050,7 +5053,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5070,13 +5073,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5097,7 +5100,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5106,7 +5109,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5126,13 +5129,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C70" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5162,7 +5165,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5182,13 +5185,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5218,7 +5221,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5238,13 +5241,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5274,7 +5277,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5294,13 +5297,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5330,7 +5333,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5350,13 +5353,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5386,7 +5389,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5406,13 +5409,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C75" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5442,7 +5445,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5462,13 +5465,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5498,7 +5501,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5518,13 +5521,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5554,7 +5557,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5574,13 +5577,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5610,7 +5613,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5630,13 +5633,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C79" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D79" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5666,7 +5669,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5686,13 +5689,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5722,7 +5725,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5742,13 +5745,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5778,7 +5781,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5798,13 +5801,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C82" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5834,7 +5837,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5857,13 +5860,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5893,7 +5896,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5913,13 +5916,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5949,7 +5952,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5969,13 +5972,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C85" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6005,7 +6008,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6025,13 +6028,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6061,7 +6064,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6081,13 +6084,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D87" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6117,7 +6120,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6137,13 +6140,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6173,7 +6176,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6193,13 +6196,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6229,7 +6232,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6249,13 +6252,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6285,7 +6288,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6305,13 +6308,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C91" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D91" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6341,7 +6344,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6364,13 +6367,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C92" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6400,7 +6403,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6420,13 +6423,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D93" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6456,7 +6459,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6476,13 +6479,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6512,7 +6515,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6532,13 +6535,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6568,7 +6571,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6588,13 +6591,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C96" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D96" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6624,7 +6627,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6644,13 +6647,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C97" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D97" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6680,7 +6683,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6700,13 +6703,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C98" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D98" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6736,7 +6739,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6759,13 +6762,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C99" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D99" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6795,7 +6798,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6815,13 +6818,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C100" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D100" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6851,7 +6854,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6871,13 +6874,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C101" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D101" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6907,7 +6910,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6927,13 +6930,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C102" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6963,7 +6966,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6983,13 +6986,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C103" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D103" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7019,7 +7022,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7039,13 +7042,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C104" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D104" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7075,7 +7078,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7095,13 +7098,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C105" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D105" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7131,7 +7134,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7151,13 +7154,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C106" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7178,7 +7181,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7187,7 +7190,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7207,13 +7210,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C107" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D107" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7243,7 +7246,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7263,13 +7266,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7299,7 +7302,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7319,13 +7322,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D109" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7346,7 +7349,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7355,7 +7358,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7375,13 +7378,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C110" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7411,7 +7414,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7431,13 +7434,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7467,7 +7470,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7487,13 +7490,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D112" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7523,7 +7526,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7543,13 +7546,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D113" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7579,7 +7582,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7599,13 +7602,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C114" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D114" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7635,7 +7638,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7655,13 +7658,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C115" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7691,7 +7694,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7711,13 +7714,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C116" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7747,7 +7750,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7767,13 +7770,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7803,7 +7806,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7823,13 +7826,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D118" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7859,7 +7862,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7882,13 +7885,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D119" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7918,7 +7921,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7938,13 +7941,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7974,7 +7977,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7994,13 +7997,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C121" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D121" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8030,7 +8033,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8050,13 +8053,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8086,7 +8089,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8106,13 +8109,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C123" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D123" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8133,7 +8136,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8142,7 +8145,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8162,13 +8165,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8198,7 +8201,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8218,13 +8221,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8254,7 +8257,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8274,13 +8277,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8310,7 +8313,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8333,13 +8336,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C127" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8369,7 +8372,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8389,13 +8392,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C128" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D128" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8425,7 +8428,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8448,13 +8451,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C129" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D129" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8484,7 +8487,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8504,13 +8507,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D130" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8540,7 +8543,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8560,13 +8563,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C131" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8596,7 +8599,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8616,13 +8619,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D132" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8652,7 +8655,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8672,13 +8675,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C133" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D133" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8699,7 +8702,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8708,7 +8711,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8728,13 +8731,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C134" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D134" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8764,7 +8767,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8784,13 +8787,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C135" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D135" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8820,7 +8823,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8840,13 +8843,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C136" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D136" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8876,7 +8879,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8896,13 +8899,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C137" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D137" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8932,7 +8935,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8955,13 +8958,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C138" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D138" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8991,7 +8994,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9011,13 +9014,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C139" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D139" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9047,7 +9050,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9067,13 +9070,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C140" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D140" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9103,7 +9106,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9123,13 +9126,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C141" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D141" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9159,7 +9162,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9179,13 +9182,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C142" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D142" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9215,7 +9218,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9235,13 +9238,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C143" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D143" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9271,7 +9274,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9291,13 +9294,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C144" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9327,7 +9330,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9347,13 +9350,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D145" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9383,7 +9386,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9403,13 +9406,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C146" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D146" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9439,7 +9442,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9462,13 +9465,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C147" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D147" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9498,7 +9501,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9521,13 +9524,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D148" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9557,7 +9560,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9580,13 +9583,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C149" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9607,7 +9610,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9616,7 +9619,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9639,13 +9642,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C150" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9675,7 +9678,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9698,13 +9701,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C151" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D151" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9734,7 +9737,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9754,13 +9757,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C152" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D152" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9790,7 +9793,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9813,13 +9816,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C153" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D153" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9849,7 +9852,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9872,13 +9875,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C154" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D154" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9908,7 +9911,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9923,7 +9926,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9931,13 +9934,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C155" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D155" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9967,7 +9970,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -9990,13 +9993,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C156" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D156" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10026,7 +10029,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10046,13 +10049,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C157" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D157" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10082,7 +10085,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10102,13 +10105,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C158" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D158" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10138,7 +10141,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10158,13 +10161,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C159" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D159" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10194,7 +10197,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10217,13 +10220,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C160" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D160" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10253,7 +10256,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10273,13 +10276,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C161" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D161" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10309,7 +10312,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10332,13 +10335,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C162" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D162" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10368,7 +10371,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10388,13 +10391,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C163" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D163" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10424,7 +10427,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10447,13 +10450,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C164" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D164" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10474,7 +10477,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10483,7 +10486,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10506,13 +10509,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C165" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D165" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10533,7 +10536,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10542,7 +10545,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10562,13 +10565,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C166" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D166" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10598,7 +10601,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10621,13 +10624,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C167" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D167" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10657,7 +10660,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10677,13 +10680,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C168" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D168" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10713,7 +10716,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10733,13 +10736,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C169" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D169" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10769,7 +10772,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10792,13 +10795,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C170" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D170" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10828,7 +10831,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10851,13 +10854,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C171" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D171" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10887,7 +10890,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10907,13 +10910,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C172" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D172" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10943,7 +10946,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10966,13 +10969,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C173" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D173" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11002,7 +11005,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11022,13 +11025,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C174" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D174" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11058,7 +11061,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11081,13 +11084,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C175" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D175" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11117,7 +11120,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11137,13 +11140,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C176" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D176" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11173,7 +11176,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11193,13 +11196,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C177" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D177" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11229,7 +11232,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11252,13 +11255,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C178" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D178" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11279,7 +11282,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11288,7 +11291,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11308,13 +11311,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C179" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D179" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11344,7 +11347,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11364,13 +11367,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C180" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D180" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11400,7 +11403,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11420,13 +11423,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C181" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D181" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11456,7 +11459,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11476,13 +11479,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C182" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D182" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11512,7 +11515,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11535,13 +11538,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C183" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D183" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11571,7 +11574,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11591,13 +11594,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C184" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D184" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11627,7 +11630,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11650,13 +11653,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C185" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D185" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11686,7 +11689,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11706,13 +11709,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C186" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D186" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11733,7 +11736,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11742,7 +11745,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11762,13 +11765,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C187" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D187" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11789,7 +11792,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11798,7 +11801,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11821,13 +11824,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C188" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D188" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11848,7 +11851,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11857,7 +11860,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11877,13 +11880,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C189" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D189" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11913,7 +11916,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11933,13 +11936,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C190" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D190" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11969,7 +11972,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -11989,13 +11992,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C191" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D191" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12016,7 +12019,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12025,7 +12028,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12040,7 +12043,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12048,13 +12051,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C192" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D192" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12084,7 +12087,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12104,13 +12107,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C193" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D193" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12140,7 +12143,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12160,13 +12163,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C194" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D194" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12187,7 +12190,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12196,7 +12199,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12216,13 +12219,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C195" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D195" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12252,7 +12255,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12267,7 +12270,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12275,13 +12278,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C196" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D196" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12311,7 +12314,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12334,13 +12337,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C197" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D197" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12361,7 +12364,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12370,7 +12373,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12390,13 +12393,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C198" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D198" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12426,7 +12429,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12446,13 +12449,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C199" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D199" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12482,7 +12485,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12502,13 +12505,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D200" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12538,7 +12541,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12558,13 +12561,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C201" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D201" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12594,7 +12597,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12614,13 +12617,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C202" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D202" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12650,7 +12653,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12670,13 +12673,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D203" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12706,7 +12709,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12721,7 +12724,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12729,13 +12732,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C204" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D204" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12765,7 +12768,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12785,13 +12788,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C205" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D205" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12821,7 +12824,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12841,13 +12844,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C206" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D206" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12877,7 +12880,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12897,13 +12900,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C207" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D207" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12933,7 +12936,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12956,13 +12959,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C208" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D208" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -12992,7 +12995,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13012,13 +13015,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C209" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D209" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13048,7 +13051,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13068,13 +13071,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C210" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D210" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13095,7 +13098,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13104,7 +13107,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13124,13 +13127,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C211" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D211" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13160,7 +13163,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13180,13 +13183,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C212" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D212" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13216,7 +13219,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13236,13 +13239,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C213" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D213" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13272,7 +13275,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13292,13 +13295,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C214" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D214" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13328,7 +13331,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13343,7 +13346,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13351,13 +13354,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C215" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D215" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13387,7 +13390,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13407,13 +13410,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C216" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D216" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13443,7 +13446,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13463,13 +13466,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C217" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D217" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13499,7 +13502,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13519,13 +13522,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C218" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D218" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13555,7 +13558,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13575,13 +13578,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C219" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D219" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13611,7 +13614,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13631,13 +13634,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C220" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D220" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13658,7 +13661,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13667,7 +13670,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13687,13 +13690,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C221" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D221" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13714,7 +13717,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13723,7 +13726,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13743,13 +13746,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C222" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D222" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13779,7 +13782,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13799,13 +13802,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C223" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D223" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13826,7 +13829,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13835,7 +13838,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13855,13 +13858,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C224" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D224" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13891,7 +13894,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13911,13 +13914,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C225" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D225" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13947,7 +13950,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13967,13 +13970,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C226" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D226" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14003,7 +14006,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14023,13 +14026,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C227" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D227" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14059,7 +14062,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14079,13 +14082,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C228" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D228" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14115,7 +14118,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14135,13 +14138,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D229" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14159,7 +14162,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8836</v>
+        <v>8714</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14171,13 +14174,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>545.5</v>
+        <v>423.5</v>
       </c>
       <c r="Q229">
-        <v>545.5</v>
+        <v>423.5</v>
       </c>
       <c r="R229">
-        <v>6.58</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14185,13 +14188,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C230" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D230" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14221,7 +14224,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14241,13 +14244,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C231" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D231" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14268,7 +14271,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14277,7 +14280,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14292,7 +14295,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14300,13 +14303,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C232" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D232" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14336,7 +14339,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14356,13 +14359,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C233" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D233" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14392,7 +14395,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14412,13 +14415,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C234" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D234" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14448,7 +14451,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14468,13 +14471,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C235" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D235" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14495,7 +14498,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14504,7 +14507,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14527,13 +14530,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C236" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D236" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14554,7 +14557,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14563,7 +14566,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14586,13 +14589,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C237" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D237" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14622,7 +14625,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14642,13 +14645,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C238" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D238" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14678,7 +14681,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14698,13 +14701,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C239" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D239" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14734,7 +14737,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14754,13 +14757,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C240" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D240" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14790,7 +14793,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14810,13 +14813,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C241" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D241" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14846,7 +14849,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14866,13 +14869,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C242" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D242" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14902,7 +14905,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14922,13 +14925,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C243" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D243" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14958,7 +14961,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14981,13 +14984,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C244" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D244" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15017,7 +15020,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15032,7 +15035,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15040,13 +15043,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C245" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D245" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15067,7 +15070,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15076,7 +15079,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15096,13 +15099,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C246" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D246" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15132,7 +15135,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15152,13 +15155,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C247" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D247" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15188,7 +15191,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15208,13 +15211,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C248" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D248" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15244,7 +15247,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15264,13 +15267,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C249" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D249" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15300,7 +15303,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15320,13 +15323,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C250" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D250" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15356,7 +15359,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15376,13 +15379,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C251" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D251" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15412,7 +15415,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15432,13 +15435,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C252" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D252" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15468,7 +15471,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15491,13 +15494,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C253" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D253" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15527,7 +15530,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15547,13 +15550,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C254" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D254" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15571,7 +15574,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>718.5</v>
+        <v>715</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15583,13 +15586,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>160.3</v>
+        <v>111.3</v>
       </c>
       <c r="Q254">
-        <v>160.3</v>
+        <v>111.3</v>
       </c>
       <c r="R254">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15597,13 +15600,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C255" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D255" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15633,7 +15636,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15653,13 +15656,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C256" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D256" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15689,7 +15692,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15709,13 +15712,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C257" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D257" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15736,7 +15739,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15745,7 +15748,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15765,10 +15768,10 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C258" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D258" t="s">
         <v>253</v>
@@ -15783,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="H258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258">
         <v>7471.5</v>
@@ -15791,23 +15794,29 @@
       <c r="J258">
         <v>7530</v>
       </c>
+      <c r="K258" t="s">
+        <v>158</v>
+      </c>
       <c r="L258">
         <v>7471.5</v>
       </c>
       <c r="M258">
-        <v>0</v>
+        <v>7471.5</v>
+      </c>
+      <c r="N258" t="s">
+        <v>271</v>
       </c>
       <c r="O258">
         <v>0</v>
       </c>
       <c r="P258">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="Q258">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="R258">
-        <v>0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:19">
@@ -15815,13 +15824,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C259" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D259" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15851,7 +15860,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15874,13 +15883,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C260" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D260" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15898,7 +15907,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15910,13 +15919,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-128.8</v>
+        <v>-284.2</v>
       </c>
       <c r="Q260">
-        <v>-128.8</v>
+        <v>-284.2</v>
       </c>
       <c r="R260">
-        <v>-1.44</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15924,13 +15933,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C261" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D261" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15948,7 +15957,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1379.3</v>
+        <v>1350.4</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15960,13 +15969,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-9.1</v>
+        <v>-211.4</v>
       </c>
       <c r="Q261">
-        <v>-9.1</v>
+        <v>-211.4</v>
       </c>
       <c r="R261">
-        <v>-0.09</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15974,13 +15983,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C262" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D262" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16010,7 +16019,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16033,13 +16042,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C263" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D263" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16069,7 +16078,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16089,13 +16098,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C264" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D264" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16125,7 +16134,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16148,13 +16157,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C265" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D265" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16184,7 +16193,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16207,13 +16216,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C266" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D266" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16243,7 +16252,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16263,13 +16272,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C267" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D267" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16299,7 +16308,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16319,13 +16328,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C268" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D268" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16355,7 +16364,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16375,13 +16384,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C269" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D269" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16411,7 +16420,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16431,13 +16440,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C270" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D270" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16467,7 +16476,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16487,13 +16496,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C271" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D271" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16511,7 +16520,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1566.9</v>
+        <v>1521.1</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16523,13 +16532,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-146.4</v>
+        <v>-421.2</v>
       </c>
       <c r="Q271">
-        <v>-146.4</v>
+        <v>-421.2</v>
       </c>
       <c r="R271">
-        <v>-1.53</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16537,13 +16546,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C272" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D272" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16573,7 +16582,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16593,13 +16602,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C273" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D273" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16629,7 +16638,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16649,13 +16658,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C274" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D274" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16676,7 +16685,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16685,7 +16694,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16705,10 +16714,10 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C275" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D275" t="s">
         <v>253</v>
@@ -16723,7 +16732,7 @@
         <v>1</v>
       </c>
       <c r="H275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I275">
         <v>7375.5</v>
@@ -16731,23 +16740,29 @@
       <c r="J275">
         <v>7274</v>
       </c>
+      <c r="K275" t="s">
+        <v>158</v>
+      </c>
       <c r="L275">
         <v>7006.72</v>
       </c>
       <c r="M275">
-        <v>0</v>
+        <v>7006.72</v>
+      </c>
+      <c r="N275" t="s">
+        <v>271</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>-368.7799999999997</v>
       </c>
       <c r="P275">
-        <v>-101.5</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>-101.5</v>
+        <v>-368.7799999999997</v>
       </c>
       <c r="R275">
-        <v>-1.38</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="276" spans="1:18">
@@ -16755,13 +16770,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C276" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D276" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16791,7 +16806,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16811,13 +16826,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C277" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D277" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16847,7 +16862,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16867,13 +16882,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C278" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D278" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16903,7 +16918,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16923,13 +16938,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C279" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D279" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16959,7 +16974,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -16979,13 +16994,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C280" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D280" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17015,7 +17030,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17035,13 +17050,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C281" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D281" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17071,7 +17086,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17091,13 +17106,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C282" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D282" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17127,7 +17142,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17147,13 +17162,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C283" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D283" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17183,7 +17198,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17203,13 +17218,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C284" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D284" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17239,7 +17254,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17259,10 +17274,10 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C285" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D285" t="s">
         <v>253</v>
@@ -17277,7 +17292,7 @@
         <v>9</v>
       </c>
       <c r="H285">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I285">
         <v>9180</v>
@@ -17285,23 +17300,29 @@
       <c r="J285">
         <v>981.5</v>
       </c>
+      <c r="K285" t="s">
+        <v>158</v>
+      </c>
       <c r="L285">
         <v>969</v>
       </c>
       <c r="M285">
-        <v>0</v>
+        <v>969</v>
+      </c>
+      <c r="N285" t="s">
+        <v>271</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>-459</v>
       </c>
       <c r="P285">
-        <v>-346.5</v>
+        <v>0</v>
       </c>
       <c r="Q285">
-        <v>-346.5</v>
+        <v>-459</v>
       </c>
       <c r="R285">
-        <v>-3.77</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="286" spans="1:18">
@@ -17309,13 +17330,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C286" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D286" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17345,7 +17366,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17365,13 +17386,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C287" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D287" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17401,7 +17422,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17421,13 +17442,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C288" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D288" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17457,7 +17478,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17477,13 +17498,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C289" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D289" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17504,7 +17525,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17513,7 +17534,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17533,13 +17554,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C290" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D290" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17569,7 +17590,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17589,13 +17610,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C291" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D291" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17613,7 +17634,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>572.95</v>
+        <v>560.8</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17625,13 +17646,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>101.15</v>
+        <v>-105.4</v>
       </c>
       <c r="Q291">
-        <v>101.15</v>
+        <v>-105.4</v>
       </c>
       <c r="R291">
-        <v>1.05</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17639,13 +17660,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C292" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D292" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17666,7 +17687,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17675,7 +17696,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17695,13 +17716,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C293" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D293" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17731,7 +17752,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17751,13 +17772,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C294" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D294" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17787,7 +17808,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17810,13 +17831,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C295" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D295" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17846,7 +17867,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17866,13 +17887,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C296" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D296" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17902,7 +17923,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17922,13 +17943,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C297" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D297" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17946,7 +17967,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>116.75</v>
+        <v>114.7</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17958,13 +17979,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>21.25</v>
+        <v>-153</v>
       </c>
       <c r="Q297">
-        <v>21.25</v>
+        <v>-153</v>
       </c>
       <c r="R297">
-        <v>0.21</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -17972,13 +17993,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C298" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D298" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -17996,7 +18017,7 @@
         <v>9840</v>
       </c>
       <c r="J298">
-        <v>655.2</v>
+        <v>618.6</v>
       </c>
       <c r="L298">
         <v>615</v>
@@ -18008,13 +18029,13 @@
         <v>0</v>
       </c>
       <c r="P298">
-        <v>643.2</v>
+        <v>57.6</v>
       </c>
       <c r="Q298">
-        <v>643.2</v>
+        <v>57.6</v>
       </c>
       <c r="R298">
-        <v>6.54</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="299" spans="1:19">
@@ -18022,13 +18043,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C299" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D299" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18058,7 +18079,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18078,13 +18099,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C300" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D300" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18114,7 +18135,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18134,13 +18155,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C301" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D301" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18170,7 +18191,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18190,10 +18211,10 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C302" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D302" t="s">
         <v>253</v>
@@ -18208,7 +18229,7 @@
         <v>7</v>
       </c>
       <c r="H302">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I302">
         <v>9097.9</v>
@@ -18216,23 +18237,29 @@
       <c r="J302">
         <v>1265</v>
       </c>
+      <c r="K302" t="s">
+        <v>158</v>
+      </c>
       <c r="L302">
         <v>1234.71</v>
       </c>
       <c r="M302">
-        <v>0</v>
+        <v>1234.71</v>
+      </c>
+      <c r="N302" t="s">
+        <v>271</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>-454.9300000000001</v>
       </c>
       <c r="P302">
-        <v>-242.9</v>
+        <v>0</v>
       </c>
       <c r="Q302">
-        <v>-242.9</v>
+        <v>-454.9300000000001</v>
       </c>
       <c r="R302">
-        <v>-2.67</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="303" spans="1:19">
@@ -18240,13 +18267,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C303" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D303" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18267,7 +18294,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18276,7 +18303,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18296,13 +18323,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C304" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D304" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18332,7 +18359,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18352,13 +18379,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C305" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D305" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18388,7 +18415,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18408,13 +18435,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C306" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D306" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18432,7 +18459,7 @@
         <v>9080</v>
       </c>
       <c r="J306">
-        <v>2200.8</v>
+        <v>2251</v>
       </c>
       <c r="L306">
         <v>2156.5</v>
@@ -18444,13 +18471,13 @@
         <v>0</v>
       </c>
       <c r="P306">
-        <v>-276.8</v>
+        <v>-76</v>
       </c>
       <c r="Q306">
-        <v>-276.8</v>
+        <v>-76</v>
       </c>
       <c r="R306">
-        <v>-3.05</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -18458,13 +18485,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C307" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D307" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18494,7 +18521,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18514,10 +18541,10 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C308" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D308" t="s">
         <v>253</v>
@@ -18532,7 +18559,7 @@
         <v>12</v>
       </c>
       <c r="H308">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I308">
         <v>9996</v>
@@ -18540,23 +18567,29 @@
       <c r="J308">
         <v>802.1</v>
       </c>
+      <c r="K308" t="s">
+        <v>158</v>
+      </c>
       <c r="L308">
         <v>791.35</v>
       </c>
       <c r="M308">
-        <v>0</v>
+        <v>791.35</v>
+      </c>
+      <c r="N308" t="s">
+        <v>271</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>-499.7999999999997</v>
       </c>
       <c r="P308">
-        <v>-370.8</v>
+        <v>0</v>
       </c>
       <c r="Q308">
-        <v>-370.8</v>
+        <v>-499.7999999999997</v>
       </c>
       <c r="R308">
-        <v>-3.71</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="309" spans="1:18">
@@ -18564,13 +18597,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C309" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D309" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18591,7 +18624,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18600,7 +18633,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18620,13 +18653,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C310" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D310" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18656,7 +18689,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18676,13 +18709,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C311" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D311" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18712,7 +18745,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18732,13 +18765,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C312" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D312" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18768,7 +18801,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18788,13 +18821,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C313" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D313" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18824,7 +18857,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18844,13 +18877,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C314" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D314" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18868,7 +18901,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18880,13 +18913,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-192.6</v>
+        <v>-420.3</v>
       </c>
       <c r="Q314">
-        <v>-192.6</v>
+        <v>-420.3</v>
       </c>
       <c r="R314">
-        <v>-2.03</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18894,13 +18927,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C315" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D315" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18918,7 +18951,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4905</v>
+        <v>4695</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18930,13 +18963,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>278.8</v>
+        <v>-141.2</v>
       </c>
       <c r="Q315">
-        <v>278.8</v>
+        <v>-141.2</v>
       </c>
       <c r="R315">
-        <v>2.93</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -18944,13 +18977,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C316" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D316" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -18968,7 +19001,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -18980,13 +19013,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>366</v>
+        <v>-28.2</v>
       </c>
       <c r="Q316">
-        <v>366</v>
+        <v>-28.2</v>
       </c>
       <c r="R316">
-        <v>4.15</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -18994,13 +19027,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C317" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D317" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19018,7 +19051,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>312.7</v>
+        <v>308.5</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19030,13 +19063,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-186</v>
+        <v>-316.2</v>
       </c>
       <c r="Q317">
-        <v>-186</v>
+        <v>-316.2</v>
       </c>
       <c r="R317">
-        <v>-1.88</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19044,13 +19077,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C318" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D318" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19071,7 +19104,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19080,7 +19113,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19100,13 +19133,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C319" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D319" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19124,7 +19157,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1165.5</v>
+        <v>1145</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19136,13 +19169,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>170.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q319">
-        <v>170.4</v>
+        <v>6.4</v>
       </c>
       <c r="R319">
-        <v>1.86</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19150,13 +19183,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C320" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D320" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19174,7 +19207,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>419</v>
+        <v>409.8</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19186,13 +19219,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-5.75</v>
+        <v>-217.35</v>
       </c>
       <c r="Q320">
-        <v>-5.75</v>
+        <v>-217.35</v>
       </c>
       <c r="R320">
-        <v>-0.06</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19200,13 +19233,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C321" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D321" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19224,7 +19257,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2802.4</v>
+        <v>2730</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19236,13 +19269,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-52.8</v>
+        <v>-270</v>
       </c>
       <c r="Q321">
-        <v>-52.8</v>
+        <v>-270</v>
       </c>
       <c r="R321">
-        <v>-0.62</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19250,13 +19283,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C322" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D322" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19274,7 +19307,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19286,13 +19319,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>-52</v>
+        <v>-306</v>
       </c>
       <c r="Q322">
-        <v>-52</v>
+        <v>-306</v>
       </c>
       <c r="R322">
-        <v>-0.59</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19300,13 +19333,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C323" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D323" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19324,7 +19357,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1206.1</v>
+        <v>1253.7</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19336,13 +19369,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>-189.6</v>
+        <v>191.2</v>
       </c>
       <c r="Q323">
-        <v>-189.6</v>
+        <v>191.2</v>
       </c>
       <c r="R323">
-        <v>-1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19350,13 +19383,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C324" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D324" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19374,7 +19407,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>471.5</v>
+        <v>457.6</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19386,13 +19419,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>10.5</v>
+        <v>-281.4</v>
       </c>
       <c r="Q324">
-        <v>10.5</v>
+        <v>-281.4</v>
       </c>
       <c r="R324">
-        <v>0.11</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19400,13 +19433,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C325" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D325" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19424,7 +19457,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1058.9</v>
+        <v>1028</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19436,13 +19469,263 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>37.8</v>
+        <v>-240.3</v>
       </c>
       <c r="Q325">
-        <v>37.8</v>
+        <v>-240.3</v>
       </c>
       <c r="R325">
-        <v>0.4</v>
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18">
+      <c r="A326" t="s">
+        <v>158</v>
+      </c>
+      <c r="B326" t="s">
+        <v>194</v>
+      </c>
+      <c r="C326" t="s">
+        <v>251</v>
+      </c>
+      <c r="D326" t="s">
+        <v>254</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>158.15</v>
+      </c>
+      <c r="G326">
+        <v>63</v>
+      </c>
+      <c r="H326">
+        <v>63</v>
+      </c>
+      <c r="I326">
+        <v>9963.450000000001</v>
+      </c>
+      <c r="J326">
+        <v>158.15</v>
+      </c>
+      <c r="L326">
+        <v>150.24</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
+      </c>
+      <c r="O326">
+        <v>0</v>
+      </c>
+      <c r="P326">
+        <v>0</v>
+      </c>
+      <c r="Q326">
+        <v>0</v>
+      </c>
+      <c r="R326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18">
+      <c r="A327" t="s">
+        <v>158</v>
+      </c>
+      <c r="B327" t="s">
+        <v>236</v>
+      </c>
+      <c r="C327" t="s">
+        <v>250</v>
+      </c>
+      <c r="D327" t="s">
+        <v>254</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>1820.3</v>
+      </c>
+      <c r="G327">
+        <v>5</v>
+      </c>
+      <c r="H327">
+        <v>5</v>
+      </c>
+      <c r="I327">
+        <v>9101.5</v>
+      </c>
+      <c r="J327">
+        <v>1820.3</v>
+      </c>
+      <c r="L327">
+        <v>1729.28</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="O327">
+        <v>0</v>
+      </c>
+      <c r="P327">
+        <v>0</v>
+      </c>
+      <c r="Q327">
+        <v>0</v>
+      </c>
+      <c r="R327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18">
+      <c r="A328" t="s">
+        <v>158</v>
+      </c>
+      <c r="B328" t="s">
+        <v>201</v>
+      </c>
+      <c r="C328" t="s">
+        <v>250</v>
+      </c>
+      <c r="D328" t="s">
+        <v>254</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>1077</v>
+      </c>
+      <c r="G328">
+        <v>9</v>
+      </c>
+      <c r="H328">
+        <v>9</v>
+      </c>
+      <c r="I328">
+        <v>9693</v>
+      </c>
+      <c r="J328">
+        <v>1077</v>
+      </c>
+      <c r="L328">
+        <v>1023.15</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
+      </c>
+      <c r="O328">
+        <v>0</v>
+      </c>
+      <c r="P328">
+        <v>0</v>
+      </c>
+      <c r="Q328">
+        <v>0</v>
+      </c>
+      <c r="R328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18">
+      <c r="A329" t="s">
+        <v>158</v>
+      </c>
+      <c r="B329" t="s">
+        <v>245</v>
+      </c>
+      <c r="C329" t="s">
+        <v>251</v>
+      </c>
+      <c r="D329" t="s">
+        <v>254</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>315.25</v>
+      </c>
+      <c r="G329">
+        <v>31</v>
+      </c>
+      <c r="H329">
+        <v>31</v>
+      </c>
+      <c r="I329">
+        <v>9772.75</v>
+      </c>
+      <c r="J329">
+        <v>315.25</v>
+      </c>
+      <c r="L329">
+        <v>299.49</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="O329">
+        <v>0</v>
+      </c>
+      <c r="P329">
+        <v>0</v>
+      </c>
+      <c r="Q329">
+        <v>0</v>
+      </c>
+      <c r="R329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18">
+      <c r="A330" t="s">
+        <v>158</v>
+      </c>
+      <c r="B330" t="s">
+        <v>179</v>
+      </c>
+      <c r="C330" t="s">
+        <v>251</v>
+      </c>
+      <c r="D330" t="s">
+        <v>254</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>4856</v>
+      </c>
+      <c r="G330">
+        <v>2</v>
+      </c>
+      <c r="H330">
+        <v>2</v>
+      </c>
+      <c r="I330">
+        <v>9712</v>
+      </c>
+      <c r="J330">
+        <v>4856</v>
+      </c>
+      <c r="L330">
+        <v>4613.2</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="O330">
+        <v>0</v>
+      </c>
+      <c r="P330">
+        <v>0</v>
+      </c>
+      <c r="Q330">
+        <v>0</v>
+      </c>
+      <c r="R330">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="278">
   <si>
     <t>Buy Date</t>
   </si>
@@ -491,6 +491,9 @@
   </si>
   <si>
     <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1208,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S330"/>
+  <dimension ref="A1:S331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1285,13 +1288,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1321,7 +1324,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1341,13 +1344,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1377,7 +1380,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1400,13 +1403,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1436,7 +1439,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1456,13 +1459,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1492,7 +1495,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1512,13 +1515,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1548,7 +1551,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1568,13 +1571,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1604,7 +1607,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1624,13 +1627,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1660,7 +1663,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1680,13 +1683,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1716,7 +1719,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1736,13 +1739,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1772,7 +1775,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1792,13 +1795,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1819,7 +1822,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1828,7 +1831,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1843,7 +1846,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1851,13 +1854,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1887,7 +1890,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1910,13 +1913,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1946,7 +1949,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1966,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2002,7 +2005,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2022,13 +2025,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2058,7 +2061,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2078,13 +2081,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2114,7 +2117,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2134,13 +2137,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2170,7 +2173,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2190,13 +2193,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2226,7 +2229,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2246,13 +2249,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2282,7 +2285,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2302,13 +2305,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2338,7 +2341,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2358,13 +2361,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2385,7 +2388,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2394,7 +2397,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2414,13 +2417,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2441,7 +2444,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2450,7 +2453,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2470,13 +2473,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2506,7 +2509,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2526,13 +2529,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2562,7 +2565,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2582,13 +2585,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2618,7 +2621,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2638,13 +2641,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2665,7 +2668,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2674,7 +2677,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2694,13 +2697,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2730,7 +2733,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2750,13 +2753,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2786,7 +2789,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2806,13 +2809,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2842,7 +2845,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2862,13 +2865,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2898,7 +2901,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2918,13 +2921,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2945,7 +2948,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2954,7 +2957,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2974,13 +2977,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3010,7 +3013,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3030,13 +3033,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3066,7 +3069,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3086,13 +3089,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3113,7 +3116,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3122,7 +3125,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3142,13 +3145,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3169,7 +3172,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3178,7 +3181,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3198,13 +3201,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3234,7 +3237,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3254,13 +3257,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3290,7 +3293,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3310,13 +3313,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3346,7 +3349,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3369,13 +3372,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3405,7 +3408,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3425,13 +3428,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3461,7 +3464,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3481,13 +3484,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3517,7 +3520,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3537,13 +3540,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3564,7 +3567,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3573,7 +3576,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3593,13 +3596,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3620,7 +3623,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3629,7 +3632,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3649,13 +3652,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D44" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3685,7 +3688,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3705,13 +3708,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3741,7 +3744,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3761,13 +3764,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3797,7 +3800,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3820,13 +3823,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3856,7 +3859,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3876,13 +3879,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3912,7 +3915,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3932,13 +3935,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3968,7 +3971,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3991,13 +3994,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4027,7 +4030,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4047,13 +4050,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4083,7 +4086,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4103,13 +4106,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4139,7 +4142,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4162,13 +4165,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4198,7 +4201,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4218,13 +4221,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4254,7 +4257,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4277,13 +4280,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4313,7 +4316,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4336,13 +4339,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4372,7 +4375,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4392,13 +4395,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4419,7 +4422,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4428,7 +4431,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4448,13 +4451,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C58" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4484,7 +4487,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4504,13 +4507,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4540,7 +4543,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4563,13 +4566,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4599,7 +4602,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4619,13 +4622,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C61" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4655,7 +4658,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4678,13 +4681,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4714,7 +4717,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4729,7 +4732,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4737,13 +4740,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4773,7 +4776,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4793,13 +4796,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C64" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4829,7 +4832,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4849,13 +4852,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4885,7 +4888,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4905,13 +4908,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4941,7 +4944,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4961,13 +4964,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4997,7 +5000,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5017,13 +5020,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5053,7 +5056,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5073,13 +5076,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5100,7 +5103,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5109,7 +5112,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5129,13 +5132,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5165,7 +5168,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5185,13 +5188,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5221,7 +5224,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5241,13 +5244,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5277,7 +5280,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5297,13 +5300,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5333,7 +5336,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5353,13 +5356,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5389,7 +5392,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5409,13 +5412,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5445,7 +5448,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5465,13 +5468,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5501,7 +5504,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5521,13 +5524,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5557,7 +5560,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5577,13 +5580,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5613,7 +5616,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5633,13 +5636,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5669,7 +5672,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5689,13 +5692,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C80" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5725,7 +5728,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5745,13 +5748,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5781,7 +5784,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5801,13 +5804,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5837,7 +5840,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5860,13 +5863,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5896,7 +5899,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5916,13 +5919,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5952,7 +5955,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5972,13 +5975,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6008,7 +6011,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6028,13 +6031,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6064,7 +6067,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6084,13 +6087,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C87" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6120,7 +6123,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6140,13 +6143,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6176,7 +6179,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6196,13 +6199,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6232,7 +6235,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6252,13 +6255,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6288,7 +6291,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6308,13 +6311,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C91" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6344,7 +6347,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6367,13 +6370,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6403,7 +6406,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6423,13 +6426,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D93" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6459,7 +6462,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6479,13 +6482,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6515,7 +6518,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6535,13 +6538,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6571,7 +6574,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6591,13 +6594,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6627,7 +6630,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6647,13 +6650,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C97" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6683,7 +6686,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6703,13 +6706,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D98" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6739,7 +6742,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6762,13 +6765,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C99" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6798,7 +6801,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6818,13 +6821,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C100" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6854,7 +6857,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6874,13 +6877,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C101" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6910,7 +6913,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6930,13 +6933,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C102" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6966,7 +6969,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6986,13 +6989,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C103" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D103" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7022,7 +7025,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7042,13 +7045,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C104" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7078,7 +7081,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7098,13 +7101,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C105" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D105" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7134,7 +7137,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7154,13 +7157,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7181,7 +7184,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7190,7 +7193,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7210,13 +7213,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C107" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7246,7 +7249,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7266,13 +7269,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7302,7 +7305,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7322,13 +7325,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7349,7 +7352,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7358,7 +7361,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7378,13 +7381,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C110" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7414,7 +7417,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7434,13 +7437,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7470,7 +7473,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7490,13 +7493,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D112" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7526,7 +7529,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7546,13 +7549,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C113" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7582,7 +7585,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7602,13 +7605,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D114" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7638,7 +7641,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7658,13 +7661,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C115" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7694,7 +7697,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7714,13 +7717,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C116" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7750,7 +7753,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7770,13 +7773,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C117" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7806,7 +7809,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7826,13 +7829,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C118" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7862,7 +7865,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7885,13 +7888,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D119" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7921,7 +7924,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7941,13 +7944,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D120" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7977,7 +7980,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7997,13 +8000,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D121" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8033,7 +8036,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8053,13 +8056,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C122" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8089,7 +8092,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8109,13 +8112,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8136,7 +8139,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8145,7 +8148,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8165,13 +8168,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8201,7 +8204,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8221,13 +8224,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8257,7 +8260,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8277,13 +8280,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8313,7 +8316,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8336,13 +8339,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C127" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8372,7 +8375,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8392,13 +8395,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C128" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8428,7 +8431,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8451,13 +8454,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C129" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D129" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8487,7 +8490,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8507,13 +8510,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C130" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D130" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8543,7 +8546,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8563,13 +8566,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C131" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D131" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8599,7 +8602,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8619,13 +8622,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C132" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8655,7 +8658,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8675,13 +8678,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C133" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D133" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8702,7 +8705,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8711,7 +8714,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8731,13 +8734,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C134" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8767,7 +8770,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8787,13 +8790,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C135" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8823,7 +8826,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8843,13 +8846,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C136" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D136" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8879,7 +8882,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8899,13 +8902,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C137" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8935,7 +8938,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8958,13 +8961,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C138" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D138" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8994,7 +8997,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9014,13 +9017,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C139" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9050,7 +9053,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9070,13 +9073,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C140" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D140" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9106,7 +9109,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9126,13 +9129,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C141" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D141" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9162,7 +9165,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9182,13 +9185,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D142" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9218,7 +9221,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9238,13 +9241,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C143" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9274,7 +9277,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9294,13 +9297,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D144" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9330,7 +9333,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9350,13 +9353,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C145" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9386,7 +9389,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9406,13 +9409,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C146" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9442,7 +9445,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9465,13 +9468,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C147" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D147" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9501,7 +9504,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9524,13 +9527,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D148" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9560,7 +9563,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9583,13 +9586,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D149" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9610,7 +9613,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9619,7 +9622,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9642,13 +9645,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C150" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9678,7 +9681,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9701,13 +9704,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C151" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9737,7 +9740,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9757,13 +9760,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C152" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D152" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9793,7 +9796,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9816,13 +9819,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C153" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D153" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9852,7 +9855,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9875,13 +9878,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C154" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D154" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9911,7 +9914,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9926,7 +9929,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9934,13 +9937,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C155" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D155" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9970,7 +9973,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -9993,13 +9996,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C156" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D156" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10029,7 +10032,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10049,13 +10052,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C157" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D157" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10085,7 +10088,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10105,13 +10108,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C158" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D158" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10141,7 +10144,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10161,13 +10164,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C159" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D159" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10197,7 +10200,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10220,13 +10223,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C160" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D160" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10256,7 +10259,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10276,13 +10279,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C161" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D161" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10312,7 +10315,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10335,13 +10338,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C162" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D162" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10371,7 +10374,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10391,13 +10394,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C163" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D163" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10427,7 +10430,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10450,13 +10453,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C164" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D164" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10477,7 +10480,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10486,7 +10489,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10509,13 +10512,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C165" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D165" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10536,7 +10539,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10545,7 +10548,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10565,13 +10568,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C166" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D166" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10601,7 +10604,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10624,13 +10627,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C167" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D167" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10660,7 +10663,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10680,13 +10683,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C168" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D168" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10716,7 +10719,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10736,13 +10739,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C169" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D169" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10772,7 +10775,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10795,13 +10798,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C170" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D170" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10831,7 +10834,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10854,13 +10857,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C171" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D171" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10890,7 +10893,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10910,13 +10913,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C172" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D172" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10946,7 +10949,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10969,13 +10972,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C173" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D173" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11005,7 +11008,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11025,13 +11028,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C174" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D174" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11061,7 +11064,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11084,13 +11087,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C175" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D175" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11120,7 +11123,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11140,13 +11143,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C176" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D176" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11176,7 +11179,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11196,13 +11199,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C177" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D177" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11232,7 +11235,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11255,13 +11258,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C178" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D178" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11282,7 +11285,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11291,7 +11294,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11311,13 +11314,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C179" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D179" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11347,7 +11350,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11367,13 +11370,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C180" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D180" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11403,7 +11406,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11423,13 +11426,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C181" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D181" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11459,7 +11462,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11479,13 +11482,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C182" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D182" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11515,7 +11518,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11538,13 +11541,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C183" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D183" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11574,7 +11577,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11594,13 +11597,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C184" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D184" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11630,7 +11633,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11653,13 +11656,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C185" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D185" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11689,7 +11692,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11709,13 +11712,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C186" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D186" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11736,7 +11739,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11745,7 +11748,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11765,13 +11768,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C187" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D187" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11792,7 +11795,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11801,7 +11804,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11824,13 +11827,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C188" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D188" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11851,7 +11854,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11860,7 +11863,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11880,13 +11883,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C189" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D189" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11916,7 +11919,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11936,13 +11939,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C190" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D190" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11972,7 +11975,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -11992,13 +11995,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D191" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12019,7 +12022,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12028,7 +12031,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12043,7 +12046,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12051,13 +12054,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C192" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D192" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12087,7 +12090,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12107,13 +12110,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C193" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D193" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12143,7 +12146,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12163,13 +12166,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C194" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D194" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12190,7 +12193,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12199,7 +12202,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12219,13 +12222,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C195" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D195" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12255,7 +12258,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12270,7 +12273,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12278,13 +12281,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C196" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D196" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12314,7 +12317,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12337,13 +12340,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C197" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D197" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12364,7 +12367,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12373,7 +12376,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12393,13 +12396,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C198" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D198" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12429,7 +12432,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12449,13 +12452,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C199" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D199" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12485,7 +12488,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12505,13 +12508,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C200" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D200" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12541,7 +12544,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12561,13 +12564,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C201" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D201" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12597,7 +12600,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12617,13 +12620,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C202" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D202" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12653,7 +12656,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12673,13 +12676,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D203" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12709,7 +12712,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12724,7 +12727,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12732,13 +12735,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C204" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D204" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12768,7 +12771,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12788,13 +12791,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C205" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D205" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12824,7 +12827,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12844,13 +12847,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C206" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D206" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12880,7 +12883,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12900,13 +12903,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C207" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D207" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12936,7 +12939,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12959,13 +12962,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C208" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D208" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -12995,7 +12998,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13015,13 +13018,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C209" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D209" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13051,7 +13054,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13071,13 +13074,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D210" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13098,7 +13101,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13107,7 +13110,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13127,13 +13130,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C211" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D211" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13163,7 +13166,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13183,13 +13186,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C212" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D212" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13219,7 +13222,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13239,13 +13242,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C213" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D213" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13275,7 +13278,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13295,13 +13298,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C214" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D214" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13331,7 +13334,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13346,7 +13349,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13354,13 +13357,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C215" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D215" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13390,7 +13393,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13410,13 +13413,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D216" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13446,7 +13449,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13466,13 +13469,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C217" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D217" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13502,7 +13505,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13522,13 +13525,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C218" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D218" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13558,7 +13561,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13578,13 +13581,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C219" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D219" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13614,7 +13617,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13634,13 +13637,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C220" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D220" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13661,7 +13664,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13670,7 +13673,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13690,13 +13693,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C221" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D221" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13717,7 +13720,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13726,7 +13729,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13746,13 +13749,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C222" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D222" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13782,7 +13785,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13802,13 +13805,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C223" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D223" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13829,7 +13832,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13838,7 +13841,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13858,13 +13861,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C224" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13894,7 +13897,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13914,13 +13917,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C225" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D225" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13950,7 +13953,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13970,13 +13973,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C226" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D226" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14006,7 +14009,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14026,13 +14029,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D227" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14062,7 +14065,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14082,13 +14085,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C228" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D228" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14118,7 +14121,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14138,13 +14141,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C229" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14162,7 +14165,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8714</v>
+        <v>8696.5</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14174,13 +14177,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>423.5</v>
+        <v>406</v>
       </c>
       <c r="Q229">
-        <v>423.5</v>
+        <v>406</v>
       </c>
       <c r="R229">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14188,13 +14191,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C230" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D230" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14224,7 +14227,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14244,13 +14247,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D231" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14271,7 +14274,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14280,7 +14283,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14295,7 +14298,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14303,13 +14306,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C232" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D232" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14339,7 +14342,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14359,13 +14362,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C233" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D233" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14395,7 +14398,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14415,13 +14418,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C234" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D234" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14451,7 +14454,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14471,13 +14474,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C235" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D235" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14498,7 +14501,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14507,7 +14510,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14530,13 +14533,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C236" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D236" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14557,7 +14560,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14566,7 +14569,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14589,13 +14592,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C237" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D237" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14625,7 +14628,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14645,13 +14648,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C238" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D238" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14681,7 +14684,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14701,13 +14704,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C239" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D239" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14737,7 +14740,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14757,13 +14760,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C240" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D240" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14793,7 +14796,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14813,13 +14816,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C241" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D241" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14849,7 +14852,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14869,13 +14872,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C242" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D242" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14905,7 +14908,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14925,13 +14928,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C243" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D243" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14961,7 +14964,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14984,13 +14987,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C244" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D244" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15020,7 +15023,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15035,7 +15038,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15043,13 +15046,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C245" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D245" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15070,7 +15073,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15079,7 +15082,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15099,13 +15102,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C246" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D246" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15135,7 +15138,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15155,13 +15158,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C247" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D247" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15191,7 +15194,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15211,13 +15214,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C248" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D248" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15247,7 +15250,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15267,13 +15270,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C249" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D249" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15303,7 +15306,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15323,13 +15326,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C250" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D250" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15359,7 +15362,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15379,13 +15382,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C251" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D251" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15415,7 +15418,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15435,13 +15438,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C252" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D252" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15471,7 +15474,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15494,13 +15497,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C253" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D253" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15530,7 +15533,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15550,13 +15553,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C254" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15574,7 +15577,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>715</v>
+        <v>713.4</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15586,13 +15589,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>111.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q254">
-        <v>111.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R254">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15600,13 +15603,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C255" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D255" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15636,7 +15639,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15656,13 +15659,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C256" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D256" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15692,7 +15695,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15712,13 +15715,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C257" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D257" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15739,7 +15742,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15748,7 +15751,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15768,13 +15771,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C258" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D258" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15804,7 +15807,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15824,13 +15827,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C259" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D259" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15860,7 +15863,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15883,13 +15886,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C260" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D260" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15907,7 +15910,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15919,13 +15922,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-284.2</v>
+        <v>-251.3</v>
       </c>
       <c r="Q260">
-        <v>-284.2</v>
+        <v>-251.3</v>
       </c>
       <c r="R260">
-        <v>-3.18</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15933,13 +15936,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C261" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D261" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15957,7 +15960,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1350.4</v>
+        <v>1358.8</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15969,13 +15972,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-211.4</v>
+        <v>-152.6</v>
       </c>
       <c r="Q261">
-        <v>-211.4</v>
+        <v>-152.6</v>
       </c>
       <c r="R261">
-        <v>-2.19</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15983,13 +15986,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C262" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D262" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16019,7 +16022,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16042,13 +16045,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C263" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D263" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16078,7 +16081,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16098,13 +16101,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C264" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D264" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16134,7 +16137,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16157,13 +16160,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C265" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D265" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16193,7 +16196,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16216,13 +16219,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C266" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D266" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16252,7 +16255,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16272,13 +16275,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C267" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D267" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16308,7 +16311,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16328,13 +16331,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C268" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D268" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16364,7 +16367,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16384,13 +16387,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C269" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D269" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16420,7 +16423,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16440,13 +16443,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C270" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D270" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16476,7 +16479,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16496,13 +16499,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C271" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D271" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16520,7 +16523,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1521.1</v>
+        <v>1543.8</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16532,13 +16535,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-421.2</v>
+        <v>-285</v>
       </c>
       <c r="Q271">
-        <v>-421.2</v>
+        <v>-285</v>
       </c>
       <c r="R271">
-        <v>-4.41</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16546,13 +16549,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C272" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D272" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16582,7 +16585,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16602,13 +16605,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C273" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D273" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16638,7 +16641,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16658,13 +16661,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C274" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D274" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16685,7 +16688,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16694,7 +16697,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16714,13 +16717,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C275" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D275" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16750,7 +16753,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16770,13 +16773,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C276" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D276" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16806,7 +16809,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16826,13 +16829,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C277" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D277" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16862,7 +16865,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16882,13 +16885,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C278" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D278" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16918,7 +16921,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16938,13 +16941,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C279" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D279" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16974,7 +16977,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -16994,13 +16997,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C280" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D280" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17030,7 +17033,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17050,13 +17053,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C281" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D281" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17086,7 +17089,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17106,13 +17109,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C282" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D282" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17142,7 +17145,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17162,13 +17165,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C283" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D283" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17198,7 +17201,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17218,13 +17221,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C284" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D284" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17254,7 +17257,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17274,13 +17277,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C285" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D285" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17310,7 +17313,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17330,13 +17333,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C286" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D286" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17366,7 +17369,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17386,13 +17389,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C287" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D287" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17422,7 +17425,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17442,13 +17445,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C288" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D288" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17478,7 +17481,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17498,13 +17501,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C289" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D289" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17525,7 +17528,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17534,7 +17537,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17554,13 +17557,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C290" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D290" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17590,7 +17593,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17610,13 +17613,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C291" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D291" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17634,7 +17637,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>560.8</v>
+        <v>550.6</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17646,13 +17649,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-105.4</v>
+        <v>-278.8</v>
       </c>
       <c r="Q291">
-        <v>-105.4</v>
+        <v>-278.8</v>
       </c>
       <c r="R291">
-        <v>-1.09</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17660,13 +17663,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C292" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D292" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17687,7 +17690,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17696,7 +17699,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17716,13 +17719,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C293" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D293" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17752,7 +17755,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17772,13 +17775,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C294" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D294" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17808,7 +17811,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17831,13 +17834,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C295" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D295" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17867,7 +17870,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17887,13 +17890,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C296" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D296" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17923,7 +17926,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17943,13 +17946,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C297" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D297" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17967,7 +17970,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>114.7</v>
+        <v>116.8</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17979,13 +17982,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>-153</v>
+        <v>25.5</v>
       </c>
       <c r="Q297">
-        <v>-153</v>
+        <v>25.5</v>
       </c>
       <c r="R297">
-        <v>-1.55</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -17993,10 +17996,10 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C298" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D298" t="s">
         <v>254</v>
@@ -18011,7 +18014,7 @@
         <v>16</v>
       </c>
       <c r="H298">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I298">
         <v>9840</v>
@@ -18019,23 +18022,29 @@
       <c r="J298">
         <v>618.6</v>
       </c>
+      <c r="K298" t="s">
+        <v>159</v>
+      </c>
       <c r="L298">
         <v>615</v>
       </c>
       <c r="M298">
-        <v>0</v>
+        <v>615</v>
+      </c>
+      <c r="N298" t="s">
+        <v>272</v>
       </c>
       <c r="O298">
         <v>0</v>
       </c>
       <c r="P298">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="Q298">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="R298">
-        <v>0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:19">
@@ -18043,13 +18052,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C299" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D299" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18079,7 +18088,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18099,13 +18108,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C300" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D300" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18135,7 +18144,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18155,13 +18164,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C301" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D301" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18191,7 +18200,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18211,13 +18220,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C302" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D302" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18247,7 +18256,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18267,13 +18276,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C303" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D303" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18294,7 +18303,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18303,7 +18312,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18323,13 +18332,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C304" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D304" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18359,7 +18368,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18379,13 +18388,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C305" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D305" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18415,7 +18424,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18435,13 +18444,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C306" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D306" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18459,7 +18468,7 @@
         <v>9080</v>
       </c>
       <c r="J306">
-        <v>2251</v>
+        <v>2188.8</v>
       </c>
       <c r="L306">
         <v>2156.5</v>
@@ -18471,13 +18480,13 @@
         <v>0</v>
       </c>
       <c r="P306">
-        <v>-76</v>
+        <v>-324.8</v>
       </c>
       <c r="Q306">
-        <v>-76</v>
+        <v>-324.8</v>
       </c>
       <c r="R306">
-        <v>-0.84</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -18485,13 +18494,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C307" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D307" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18521,7 +18530,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18541,13 +18550,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C308" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D308" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18577,7 +18586,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18597,13 +18606,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C309" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D309" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18624,7 +18633,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18633,7 +18642,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18653,13 +18662,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C310" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D310" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18689,7 +18698,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18709,13 +18718,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C311" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D311" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18745,7 +18754,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18765,13 +18774,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C312" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D312" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18801,7 +18810,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18821,13 +18830,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C313" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D313" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18857,7 +18866,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18877,13 +18886,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C314" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D314" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18901,7 +18910,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18913,13 +18922,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-420.3</v>
+        <v>-447.3</v>
       </c>
       <c r="Q314">
-        <v>-420.3</v>
+        <v>-447.3</v>
       </c>
       <c r="R314">
-        <v>-4.42</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18927,13 +18936,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C315" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D315" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18951,7 +18960,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4695</v>
+        <v>4695.6</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18963,13 +18972,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>-141.2</v>
+        <v>-140</v>
       </c>
       <c r="Q315">
-        <v>-141.2</v>
+        <v>-140</v>
       </c>
       <c r="R315">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -18977,13 +18986,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C316" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D316" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19001,7 +19010,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19013,13 +19022,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-28.2</v>
+        <v>-54</v>
       </c>
       <c r="Q316">
-        <v>-28.2</v>
+        <v>-54</v>
       </c>
       <c r="R316">
-        <v>-0.32</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19027,13 +19036,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C317" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D317" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19051,7 +19060,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>308.5</v>
+        <v>312.65</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19063,13 +19072,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-316.2</v>
+        <v>-187.55</v>
       </c>
       <c r="Q317">
-        <v>-316.2</v>
+        <v>-187.55</v>
       </c>
       <c r="R317">
-        <v>-3.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19077,13 +19086,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C318" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D318" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19104,7 +19113,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19113,7 +19122,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19133,13 +19142,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C319" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D319" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19157,7 +19166,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19169,13 +19178,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>6.4</v>
+        <v>-33.6</v>
       </c>
       <c r="Q319">
-        <v>6.4</v>
+        <v>-33.6</v>
       </c>
       <c r="R319">
-        <v>0.07000000000000001</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19183,13 +19192,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C320" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D320" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19207,7 +19216,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>409.8</v>
+        <v>415</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19219,13 +19228,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-217.35</v>
+        <v>-97.75</v>
       </c>
       <c r="Q320">
-        <v>-217.35</v>
+        <v>-97.75</v>
       </c>
       <c r="R320">
-        <v>-2.25</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19233,13 +19242,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C321" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D321" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19257,7 +19266,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2730</v>
+        <v>2769.7</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19269,13 +19278,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-270</v>
+        <v>-150.9</v>
       </c>
       <c r="Q321">
-        <v>-270</v>
+        <v>-150.9</v>
       </c>
       <c r="R321">
-        <v>-3.19</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19283,13 +19292,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C322" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D322" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19307,7 +19316,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19319,13 +19328,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>-306</v>
+        <v>-256</v>
       </c>
       <c r="Q322">
-        <v>-306</v>
+        <v>-256</v>
       </c>
       <c r="R322">
-        <v>-3.45</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19333,13 +19342,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C323" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D323" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19357,7 +19366,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1253.7</v>
+        <v>1253</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19369,13 +19378,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>191.2</v>
+        <v>185.6</v>
       </c>
       <c r="Q323">
-        <v>191.2</v>
+        <v>185.6</v>
       </c>
       <c r="R323">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19383,13 +19392,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C324" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D324" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19407,7 +19416,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>457.6</v>
+        <v>470</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19419,13 +19428,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>-281.4</v>
+        <v>-21</v>
       </c>
       <c r="Q324">
-        <v>-281.4</v>
+        <v>-21</v>
       </c>
       <c r="R324">
-        <v>-2.85</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19433,13 +19442,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C325" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D325" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19457,7 +19466,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1028</v>
+        <v>1033.2</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19469,13 +19478,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>-240.3</v>
+        <v>-193.5</v>
       </c>
       <c r="Q325">
-        <v>-240.3</v>
+        <v>-193.5</v>
       </c>
       <c r="R325">
-        <v>-2.53</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19483,13 +19492,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C326" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D326" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19507,7 +19516,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>158.15</v>
+        <v>158.27</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19519,13 +19528,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="Q326">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="R326">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19533,13 +19542,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C327" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D327" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19557,7 +19566,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1820.3</v>
+        <v>1860</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19569,13 +19578,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>198.5</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>198.5</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19583,13 +19592,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C328" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D328" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19607,7 +19616,7 @@
         <v>9693</v>
       </c>
       <c r="J328">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19619,13 +19628,13 @@
         <v>0</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>-153</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>-153</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -19633,13 +19642,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C329" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D329" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -19657,7 +19666,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>315.25</v>
+        <v>317</v>
       </c>
       <c r="L329">
         <v>299.49</v>
@@ -19669,13 +19678,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>54.25</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>54.25</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19683,13 +19692,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C330" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D330" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19707,7 +19716,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4856</v>
+        <v>4908.5</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19719,12 +19728,62 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="R330">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18">
+      <c r="A331" t="s">
+        <v>159</v>
+      </c>
+      <c r="B331" t="s">
+        <v>163</v>
+      </c>
+      <c r="C331" t="s">
+        <v>252</v>
+      </c>
+      <c r="D331" t="s">
+        <v>255</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>3187</v>
+      </c>
+      <c r="G331">
+        <v>3</v>
+      </c>
+      <c r="H331">
+        <v>3</v>
+      </c>
+      <c r="I331">
+        <v>9561</v>
+      </c>
+      <c r="J331">
+        <v>3187</v>
+      </c>
+      <c r="L331">
+        <v>3027.65</v>
+      </c>
+      <c r="M331">
+        <v>0</v>
+      </c>
+      <c r="O331">
+        <v>0</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>0</v>
+      </c>
+      <c r="R331">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14165,7 +14165,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8696.5</v>
+        <v>8768.5</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14177,13 +14177,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>406</v>
+        <v>478</v>
       </c>
       <c r="Q229">
-        <v>406</v>
+        <v>478</v>
       </c>
       <c r="R229">
-        <v>4.9</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -15577,7 +15577,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>713.4</v>
+        <v>726.65</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15589,13 +15589,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>88.90000000000001</v>
+        <v>274.4</v>
       </c>
       <c r="Q254">
-        <v>88.90000000000001</v>
+        <v>274.4</v>
       </c>
       <c r="R254">
-        <v>0.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15910,7 +15910,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15922,13 +15922,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-251.3</v>
+        <v>-224</v>
       </c>
       <c r="Q260">
-        <v>-251.3</v>
+        <v>-224</v>
       </c>
       <c r="R260">
-        <v>-2.81</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15960,7 +15960,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1358.8</v>
+        <v>1347.6</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15972,13 +15972,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-152.6</v>
+        <v>-231</v>
       </c>
       <c r="Q261">
-        <v>-152.6</v>
+        <v>-231</v>
       </c>
       <c r="R261">
-        <v>-1.58</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -16523,7 +16523,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1543.8</v>
+        <v>1551.5</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16535,13 +16535,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-285</v>
+        <v>-238.8</v>
       </c>
       <c r="Q271">
-        <v>-285</v>
+        <v>-238.8</v>
       </c>
       <c r="R271">
-        <v>-2.98</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -17637,7 +17637,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>550.6</v>
+        <v>554.75</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17649,13 +17649,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-278.8</v>
+        <v>-208.25</v>
       </c>
       <c r="Q291">
-        <v>-278.8</v>
+        <v>-208.25</v>
       </c>
       <c r="R291">
-        <v>-2.89</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17970,7 +17970,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>116.8</v>
+        <v>116.47</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17982,13 +17982,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>25.5</v>
+        <v>-2.55</v>
       </c>
       <c r="Q297">
-        <v>25.5</v>
+        <v>-2.55</v>
       </c>
       <c r="R297">
-        <v>0.26</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18468,7 +18468,7 @@
         <v>9080</v>
       </c>
       <c r="J306">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="L306">
         <v>2156.5</v>
@@ -18480,13 +18480,13 @@
         <v>0</v>
       </c>
       <c r="P306">
-        <v>-324.8</v>
+        <v>-320</v>
       </c>
       <c r="Q306">
-        <v>-324.8</v>
+        <v>-320</v>
       </c>
       <c r="R306">
-        <v>-3.58</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -18910,7 +18910,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1006.2</v>
+        <v>1015</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18922,13 +18922,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-447.3</v>
+        <v>-368.1</v>
       </c>
       <c r="Q314">
-        <v>-447.3</v>
+        <v>-368.1</v>
       </c>
       <c r="R314">
-        <v>-4.71</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18960,7 +18960,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4695.6</v>
+        <v>4788</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18972,13 +18972,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>-140</v>
+        <v>44.8</v>
       </c>
       <c r="Q315">
-        <v>-140</v>
+        <v>44.8</v>
       </c>
       <c r="R315">
-        <v>-1.47</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19010,7 +19010,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19022,13 +19022,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-54</v>
+        <v>-44.4</v>
       </c>
       <c r="Q316">
-        <v>-54</v>
+        <v>-44.4</v>
       </c>
       <c r="R316">
-        <v>-0.61</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19060,7 +19060,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>312.65</v>
+        <v>310.5</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19072,13 +19072,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-187.55</v>
+        <v>-254.2</v>
       </c>
       <c r="Q317">
-        <v>-187.55</v>
+        <v>-254.2</v>
       </c>
       <c r="R317">
-        <v>-1.9</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19166,7 +19166,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19178,13 +19178,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>-33.6</v>
+        <v>246.4</v>
       </c>
       <c r="Q319">
-        <v>-33.6</v>
+        <v>246.4</v>
       </c>
       <c r="R319">
-        <v>-0.37</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19216,7 +19216,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>415</v>
+        <v>416.5</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19228,13 +19228,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-97.75</v>
+        <v>-63.25</v>
       </c>
       <c r="Q320">
-        <v>-97.75</v>
+        <v>-63.25</v>
       </c>
       <c r="R320">
-        <v>-1.01</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19266,7 +19266,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19278,13 +19278,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-150.9</v>
+        <v>-93</v>
       </c>
       <c r="Q321">
-        <v>-150.9</v>
+        <v>-93</v>
       </c>
       <c r="R321">
-        <v>-1.78</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19316,7 +19316,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19328,13 +19328,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>-256</v>
+        <v>-183.5</v>
       </c>
       <c r="Q322">
-        <v>-256</v>
+        <v>-183.5</v>
       </c>
       <c r="R322">
-        <v>-2.88</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19366,7 +19366,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1253</v>
+        <v>1258.3</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19378,13 +19378,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>185.6</v>
+        <v>228</v>
       </c>
       <c r="Q323">
-        <v>185.6</v>
+        <v>228</v>
       </c>
       <c r="R323">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19416,7 +19416,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>470</v>
+        <v>490.5</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19428,13 +19428,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>-21</v>
+        <v>409.5</v>
       </c>
       <c r="Q324">
-        <v>-21</v>
+        <v>409.5</v>
       </c>
       <c r="R324">
-        <v>-0.21</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19466,7 +19466,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1033.2</v>
+        <v>1039.3</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19478,13 +19478,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>-193.5</v>
+        <v>-138.6</v>
       </c>
       <c r="Q325">
-        <v>-193.5</v>
+        <v>-138.6</v>
       </c>
       <c r="R325">
-        <v>-2.04</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19516,7 +19516,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>158.27</v>
+        <v>161.87</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19528,13 +19528,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>7.56</v>
+        <v>234.36</v>
       </c>
       <c r="Q326">
-        <v>7.56</v>
+        <v>234.36</v>
       </c>
       <c r="R326">
-        <v>0.08</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19566,7 +19566,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1860</v>
+        <v>1840.3</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19578,13 +19578,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>198.5</v>
+        <v>100</v>
       </c>
       <c r="Q327">
-        <v>198.5</v>
+        <v>100</v>
       </c>
       <c r="R327">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19616,7 +19616,7 @@
         <v>9693</v>
       </c>
       <c r="J328">
-        <v>1060</v>
+        <v>1058.6</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19628,13 +19628,13 @@
         <v>0</v>
       </c>
       <c r="P328">
-        <v>-153</v>
+        <v>-165.6</v>
       </c>
       <c r="Q328">
-        <v>-153</v>
+        <v>-165.6</v>
       </c>
       <c r="R328">
-        <v>-1.58</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -19666,7 +19666,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>317</v>
+        <v>322.35</v>
       </c>
       <c r="L329">
         <v>299.49</v>
@@ -19678,13 +19678,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>54.25</v>
+        <v>220.1</v>
       </c>
       <c r="Q329">
-        <v>54.25</v>
+        <v>220.1</v>
       </c>
       <c r="R329">
-        <v>0.5600000000000001</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19716,7 +19716,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19728,13 +19728,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>105</v>
+        <v>-30</v>
       </c>
       <c r="Q330">
-        <v>105</v>
+        <v>-30</v>
       </c>
       <c r="R330">
-        <v>1.08</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19766,7 +19766,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19778,13 +19778,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>0</v>
+        <v>-41.7</v>
       </c>
       <c r="Q331">
-        <v>0</v>
+        <v>-41.7</v>
       </c>
       <c r="R331">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="279">
   <si>
     <t>Buy Date</t>
   </si>
@@ -494,6 +494,9 @@
   </si>
   <si>
     <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1211,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S331"/>
+  <dimension ref="A1:S333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1288,13 +1291,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1324,7 +1327,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1344,13 +1347,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1380,7 +1383,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1403,13 +1406,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1439,7 +1442,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1459,13 +1462,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1495,7 +1498,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1515,13 +1518,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1551,7 +1554,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1571,13 +1574,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1607,7 +1610,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1627,13 +1630,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1663,7 +1666,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1683,13 +1686,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1719,7 +1722,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1739,13 +1742,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1775,7 +1778,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1795,13 +1798,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1822,7 +1825,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1831,7 +1834,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1846,7 +1849,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1854,13 +1857,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1890,7 +1893,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1913,13 +1916,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1949,7 +1952,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1969,13 +1972,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2005,7 +2008,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2025,13 +2028,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2061,7 +2064,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2081,13 +2084,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2117,7 +2120,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2137,13 +2140,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2173,7 +2176,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2193,13 +2196,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2229,7 +2232,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2249,13 +2252,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2285,7 +2288,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2305,13 +2308,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2341,7 +2344,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2361,13 +2364,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2388,7 +2391,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2397,7 +2400,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2417,13 +2420,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2444,7 +2447,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2453,7 +2456,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2473,13 +2476,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2509,7 +2512,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2529,13 +2532,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2565,7 +2568,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2585,13 +2588,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2621,7 +2624,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2641,13 +2644,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2668,7 +2671,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2677,7 +2680,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2697,13 +2700,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2733,7 +2736,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2753,13 +2756,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2789,7 +2792,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2809,13 +2812,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2845,7 +2848,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2865,13 +2868,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2901,7 +2904,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2921,13 +2924,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2948,7 +2951,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2957,7 +2960,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2977,13 +2980,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3013,7 +3016,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3033,13 +3036,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3069,7 +3072,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3089,13 +3092,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3116,7 +3119,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3125,7 +3128,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3145,13 +3148,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3172,7 +3175,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3181,7 +3184,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3201,13 +3204,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C36" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3237,7 +3240,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3257,13 +3260,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3293,7 +3296,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3313,13 +3316,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3349,7 +3352,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3372,13 +3375,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3408,7 +3411,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3428,13 +3431,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3464,7 +3467,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3484,13 +3487,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3520,7 +3523,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3540,13 +3543,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3567,7 +3570,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3576,7 +3579,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3596,13 +3599,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3623,7 +3626,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3632,7 +3635,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3652,13 +3655,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3688,7 +3691,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3708,13 +3711,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3744,7 +3747,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3764,13 +3767,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3800,7 +3803,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3823,13 +3826,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3859,7 +3862,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3879,13 +3882,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3915,7 +3918,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3935,13 +3938,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3971,7 +3974,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3994,13 +3997,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4030,7 +4033,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4050,13 +4053,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4086,7 +4089,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4106,13 +4109,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D52" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4142,7 +4145,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4165,13 +4168,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4201,7 +4204,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4221,13 +4224,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4257,7 +4260,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4280,13 +4283,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4316,7 +4319,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4339,13 +4342,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4375,7 +4378,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4395,13 +4398,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4422,7 +4425,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4431,7 +4434,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4451,13 +4454,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4487,7 +4490,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4507,13 +4510,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4543,7 +4546,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4566,13 +4569,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4602,7 +4605,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4622,13 +4625,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C61" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4658,7 +4661,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4681,13 +4684,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4717,7 +4720,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4732,7 +4735,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4740,13 +4743,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4776,7 +4779,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4796,13 +4799,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4832,7 +4835,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4852,13 +4855,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4888,7 +4891,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4908,13 +4911,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4944,7 +4947,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4964,13 +4967,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5000,7 +5003,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5020,13 +5023,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5056,7 +5059,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5076,13 +5079,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5103,7 +5106,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5112,7 +5115,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5132,13 +5135,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5168,7 +5171,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5188,13 +5191,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5224,7 +5227,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5244,13 +5247,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5280,7 +5283,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5300,13 +5303,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D73" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5336,7 +5339,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5356,13 +5359,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5392,7 +5395,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5412,13 +5415,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5448,7 +5451,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5468,13 +5471,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5504,7 +5507,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5524,13 +5527,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5560,7 +5563,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5580,13 +5583,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5616,7 +5619,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5636,13 +5639,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5672,7 +5675,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5692,13 +5695,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5728,7 +5731,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5748,13 +5751,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5784,7 +5787,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5804,13 +5807,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5840,7 +5843,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5863,13 +5866,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5899,7 +5902,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5919,13 +5922,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D84" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5955,7 +5958,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5975,13 +5978,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6011,7 +6014,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6031,13 +6034,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6067,7 +6070,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6087,13 +6090,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6123,7 +6126,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6143,13 +6146,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6179,7 +6182,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6199,13 +6202,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6235,7 +6238,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6255,13 +6258,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C90" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D90" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6291,7 +6294,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6311,13 +6314,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6347,7 +6350,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6370,13 +6373,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6406,7 +6409,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6426,13 +6429,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6462,7 +6465,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6482,13 +6485,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6518,7 +6521,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6538,13 +6541,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6574,7 +6577,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6594,13 +6597,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D96" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6630,7 +6633,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6650,13 +6653,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D97" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6686,7 +6689,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6706,13 +6709,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D98" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6742,7 +6745,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6765,13 +6768,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C99" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D99" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6801,7 +6804,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6821,13 +6824,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6857,7 +6860,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6877,13 +6880,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C101" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6913,7 +6916,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6933,13 +6936,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C102" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D102" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6969,7 +6972,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6989,13 +6992,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C103" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7025,7 +7028,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7045,13 +7048,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C104" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D104" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7081,7 +7084,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7101,13 +7104,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C105" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D105" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7137,7 +7140,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7157,13 +7160,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7184,7 +7187,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7193,7 +7196,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7213,13 +7216,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7249,7 +7252,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7269,13 +7272,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D108" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7305,7 +7308,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7325,13 +7328,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D109" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7352,7 +7355,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7361,7 +7364,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7381,13 +7384,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7417,7 +7420,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7437,13 +7440,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D111" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7473,7 +7476,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7493,13 +7496,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D112" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7529,7 +7532,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7549,13 +7552,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C113" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7585,7 +7588,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7605,13 +7608,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D114" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7641,7 +7644,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7661,13 +7664,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7697,7 +7700,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7717,13 +7720,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C116" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D116" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7753,7 +7756,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7773,13 +7776,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C117" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7809,7 +7812,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7829,13 +7832,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D118" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7865,7 +7868,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7888,13 +7891,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C119" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D119" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7924,7 +7927,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7944,13 +7947,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D120" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7980,7 +7983,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8000,13 +8003,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C121" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D121" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8036,7 +8039,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8056,13 +8059,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8092,7 +8095,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8112,13 +8115,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C123" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8139,7 +8142,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8148,7 +8151,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8168,13 +8171,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8204,7 +8207,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8224,13 +8227,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8260,7 +8263,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8280,13 +8283,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8316,7 +8319,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8339,13 +8342,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8375,7 +8378,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8395,13 +8398,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C128" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8431,7 +8434,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8454,13 +8457,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C129" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8490,7 +8493,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8510,13 +8513,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C130" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8546,7 +8549,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8566,13 +8569,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D131" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8602,7 +8605,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8622,13 +8625,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D132" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8658,7 +8661,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8678,13 +8681,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C133" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D133" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8705,7 +8708,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8714,7 +8717,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8734,13 +8737,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C134" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D134" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8770,7 +8773,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8790,13 +8793,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8826,7 +8829,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8846,13 +8849,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C136" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D136" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8882,7 +8885,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8902,13 +8905,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C137" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8938,7 +8941,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8961,13 +8964,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C138" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D138" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8997,7 +9000,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9017,13 +9020,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C139" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D139" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9053,7 +9056,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9073,13 +9076,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C140" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D140" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9109,7 +9112,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9129,13 +9132,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C141" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D141" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9165,7 +9168,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9185,13 +9188,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D142" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9221,7 +9224,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9241,13 +9244,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D143" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9277,7 +9280,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9297,13 +9300,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C144" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D144" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9333,7 +9336,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9353,13 +9356,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C145" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D145" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9389,7 +9392,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9409,13 +9412,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C146" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D146" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9445,7 +9448,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9468,13 +9471,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C147" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D147" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9504,7 +9507,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9527,13 +9530,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D148" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9563,7 +9566,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9586,13 +9589,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D149" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9613,7 +9616,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9622,7 +9625,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9645,13 +9648,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9681,7 +9684,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9704,13 +9707,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9740,7 +9743,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9760,13 +9763,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C152" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D152" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9796,7 +9799,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9819,13 +9822,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C153" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D153" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9855,7 +9858,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9878,13 +9881,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C154" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D154" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9914,7 +9917,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9929,7 +9932,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9937,13 +9940,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D155" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9973,7 +9976,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -9996,13 +9999,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C156" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D156" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10032,7 +10035,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10052,13 +10055,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C157" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D157" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10088,7 +10091,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10108,13 +10111,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D158" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10144,7 +10147,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10164,13 +10167,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C159" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D159" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10200,7 +10203,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10223,13 +10226,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10259,7 +10262,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10279,13 +10282,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C161" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D161" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10315,7 +10318,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10338,13 +10341,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C162" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D162" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10374,7 +10377,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10394,13 +10397,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C163" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D163" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10430,7 +10433,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10453,13 +10456,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C164" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D164" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10480,7 +10483,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10489,7 +10492,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10512,13 +10515,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C165" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10539,7 +10542,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10548,7 +10551,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10568,13 +10571,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C166" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D166" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10604,7 +10607,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10627,13 +10630,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C167" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D167" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10663,7 +10666,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10683,13 +10686,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C168" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D168" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10719,7 +10722,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10739,13 +10742,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C169" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D169" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10775,7 +10778,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10798,13 +10801,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C170" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D170" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10834,7 +10837,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10857,13 +10860,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C171" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10893,7 +10896,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10913,13 +10916,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C172" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D172" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10949,7 +10952,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10972,13 +10975,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C173" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D173" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11008,7 +11011,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11028,13 +11031,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C174" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D174" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11064,7 +11067,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11087,13 +11090,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C175" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D175" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11123,7 +11126,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11143,13 +11146,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C176" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D176" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11179,7 +11182,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11199,13 +11202,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C177" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11235,7 +11238,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11258,13 +11261,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C178" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D178" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11285,7 +11288,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11294,7 +11297,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11314,13 +11317,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C179" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D179" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11350,7 +11353,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11370,13 +11373,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C180" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D180" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11406,7 +11409,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11426,13 +11429,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C181" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D181" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11462,7 +11465,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11482,13 +11485,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C182" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D182" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11518,7 +11521,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11541,13 +11544,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C183" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D183" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11577,7 +11580,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11597,13 +11600,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C184" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D184" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11633,7 +11636,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11656,13 +11659,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C185" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D185" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11692,7 +11695,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11712,13 +11715,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C186" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D186" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11739,7 +11742,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11748,7 +11751,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11768,13 +11771,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C187" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D187" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11795,7 +11798,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11804,7 +11807,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11827,13 +11830,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C188" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D188" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11854,7 +11857,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11863,7 +11866,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11883,13 +11886,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C189" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D189" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11919,7 +11922,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11939,13 +11942,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C190" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D190" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11975,7 +11978,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -11995,13 +11998,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D191" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12022,7 +12025,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12031,7 +12034,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12046,7 +12049,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12054,13 +12057,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D192" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12090,7 +12093,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12110,13 +12113,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C193" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D193" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12146,7 +12149,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12166,13 +12169,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C194" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D194" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12193,7 +12196,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12202,7 +12205,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12222,13 +12225,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C195" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D195" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12258,7 +12261,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12273,7 +12276,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12281,13 +12284,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C196" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D196" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12317,7 +12320,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12340,13 +12343,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C197" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D197" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12367,7 +12370,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12376,7 +12379,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12396,13 +12399,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C198" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D198" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12432,7 +12435,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12452,13 +12455,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C199" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D199" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12488,7 +12491,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12508,13 +12511,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C200" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D200" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12544,7 +12547,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12564,13 +12567,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C201" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D201" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12600,7 +12603,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12620,13 +12623,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C202" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D202" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12656,7 +12659,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12676,13 +12679,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C203" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D203" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12712,7 +12715,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12727,7 +12730,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12735,13 +12738,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C204" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D204" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12771,7 +12774,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12791,13 +12794,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C205" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D205" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12827,7 +12830,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12847,13 +12850,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C206" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D206" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12883,7 +12886,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12903,13 +12906,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C207" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D207" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12939,7 +12942,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12962,13 +12965,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C208" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D208" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -12998,7 +13001,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13018,13 +13021,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C209" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D209" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13054,7 +13057,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13074,13 +13077,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C210" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D210" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13101,7 +13104,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13110,7 +13113,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13130,13 +13133,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C211" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D211" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13166,7 +13169,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13186,13 +13189,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C212" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D212" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13222,7 +13225,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13242,13 +13245,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C213" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D213" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13278,7 +13281,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13298,13 +13301,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C214" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D214" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13334,7 +13337,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13349,7 +13352,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13357,13 +13360,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C215" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D215" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13393,7 +13396,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13413,13 +13416,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C216" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D216" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13449,7 +13452,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13469,13 +13472,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C217" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D217" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13505,7 +13508,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13525,13 +13528,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C218" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D218" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13561,7 +13564,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13581,13 +13584,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C219" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D219" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13617,7 +13620,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13637,13 +13640,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C220" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D220" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13664,7 +13667,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13673,7 +13676,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13693,13 +13696,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C221" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D221" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13720,7 +13723,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13729,7 +13732,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13749,13 +13752,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C222" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D222" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13785,7 +13788,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13805,13 +13808,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C223" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D223" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13832,7 +13835,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13841,7 +13844,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13861,13 +13864,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D224" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13897,7 +13900,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13917,13 +13920,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C225" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13953,7 +13956,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13973,13 +13976,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C226" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D226" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14009,7 +14012,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14029,13 +14032,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C227" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14065,7 +14068,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14085,13 +14088,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C228" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D228" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14121,7 +14124,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14141,13 +14144,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C229" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D229" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14165,7 +14168,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8768.5</v>
+        <v>8944.5</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14177,13 +14180,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>478</v>
+        <v>654</v>
       </c>
       <c r="Q229">
-        <v>478</v>
+        <v>654</v>
       </c>
       <c r="R229">
-        <v>5.77</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14191,13 +14194,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C230" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D230" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14227,7 +14230,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14247,13 +14250,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C231" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D231" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14274,7 +14277,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14283,7 +14286,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14298,7 +14301,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14306,13 +14309,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C232" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D232" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14342,7 +14345,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14362,13 +14365,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C233" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D233" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14398,7 +14401,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14418,13 +14421,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C234" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14454,7 +14457,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14474,13 +14477,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C235" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D235" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14501,7 +14504,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14510,7 +14513,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14533,13 +14536,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C236" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D236" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14560,7 +14563,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14569,7 +14572,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14592,13 +14595,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C237" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D237" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14628,7 +14631,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14648,13 +14651,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C238" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D238" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14684,7 +14687,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14704,13 +14707,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C239" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D239" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14740,7 +14743,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14760,13 +14763,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C240" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14796,7 +14799,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14816,13 +14819,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C241" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14852,7 +14855,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14872,13 +14875,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C242" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D242" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14908,7 +14911,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14928,13 +14931,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C243" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D243" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14964,7 +14967,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14987,13 +14990,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C244" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D244" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15023,7 +15026,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15038,7 +15041,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15046,13 +15049,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C245" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D245" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15073,7 +15076,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15082,7 +15085,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15102,13 +15105,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C246" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D246" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15138,7 +15141,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15158,13 +15161,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C247" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D247" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15194,7 +15197,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15214,13 +15217,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C248" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15250,7 +15253,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15270,13 +15273,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C249" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15306,7 +15309,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15326,13 +15329,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C250" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15362,7 +15365,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15382,13 +15385,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C251" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15418,7 +15421,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15438,13 +15441,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C252" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D252" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15474,7 +15477,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15497,13 +15500,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C253" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D253" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15533,7 +15536,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15553,13 +15556,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C254" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D254" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15577,7 +15580,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15589,13 +15592,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>274.4</v>
+        <v>359.8</v>
       </c>
       <c r="Q254">
-        <v>274.4</v>
+        <v>359.8</v>
       </c>
       <c r="R254">
-        <v>2.77</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15603,13 +15606,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C255" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D255" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15639,7 +15642,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15659,13 +15662,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C256" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D256" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15695,7 +15698,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15715,13 +15718,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C257" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15742,7 +15745,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15751,7 +15754,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15771,13 +15774,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C258" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D258" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15807,7 +15810,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15827,13 +15830,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C259" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D259" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15863,7 +15866,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15886,13 +15889,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C260" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D260" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15910,7 +15913,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15922,13 +15925,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-224</v>
+        <v>-346.5</v>
       </c>
       <c r="Q260">
-        <v>-224</v>
+        <v>-346.5</v>
       </c>
       <c r="R260">
-        <v>-2.51</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15936,13 +15939,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C261" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D261" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15960,7 +15963,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1347.6</v>
+        <v>1338.9</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15972,13 +15975,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-231</v>
+        <v>-291.9</v>
       </c>
       <c r="Q261">
-        <v>-231</v>
+        <v>-291.9</v>
       </c>
       <c r="R261">
-        <v>-2.39</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15986,13 +15989,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C262" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D262" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16022,7 +16025,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16045,13 +16048,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C263" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D263" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16081,7 +16084,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16101,13 +16104,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C264" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D264" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16137,7 +16140,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16160,13 +16163,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C265" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D265" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16196,7 +16199,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16219,13 +16222,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C266" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16255,7 +16258,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16275,13 +16278,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C267" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D267" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16311,7 +16314,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16331,13 +16334,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C268" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D268" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16367,7 +16370,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16387,13 +16390,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C269" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D269" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16423,7 +16426,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16443,13 +16446,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C270" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D270" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16479,7 +16482,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16499,13 +16502,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C271" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D271" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16523,7 +16526,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1551.5</v>
+        <v>1572.1</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16535,13 +16538,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-238.8</v>
+        <v>-115.2</v>
       </c>
       <c r="Q271">
-        <v>-238.8</v>
+        <v>-115.2</v>
       </c>
       <c r="R271">
-        <v>-2.5</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16549,13 +16552,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C272" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D272" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16585,7 +16588,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16605,13 +16608,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C273" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D273" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16641,7 +16644,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16661,13 +16664,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C274" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D274" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16688,7 +16691,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16697,7 +16700,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16717,13 +16720,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C275" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D275" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16753,7 +16756,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16773,13 +16776,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C276" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D276" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16809,7 +16812,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16829,13 +16832,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C277" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D277" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16865,7 +16868,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16885,13 +16888,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C278" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D278" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16921,7 +16924,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16941,13 +16944,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C279" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D279" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16977,7 +16980,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -16997,13 +17000,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C280" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D280" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17033,7 +17036,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17053,13 +17056,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C281" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D281" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17089,7 +17092,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17109,13 +17112,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C282" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D282" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17145,7 +17148,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17165,13 +17168,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C283" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D283" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17201,7 +17204,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17221,13 +17224,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C284" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D284" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17257,7 +17260,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17277,13 +17280,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C285" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D285" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17313,7 +17316,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17333,13 +17336,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C286" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D286" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17369,7 +17372,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17389,13 +17392,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C287" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D287" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17425,7 +17428,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17445,13 +17448,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C288" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D288" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17481,7 +17484,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17501,13 +17504,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C289" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D289" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17528,7 +17531,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17537,7 +17540,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17557,13 +17560,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C290" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D290" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17593,7 +17596,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17613,13 +17616,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C291" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D291" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17637,7 +17640,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>554.75</v>
+        <v>580</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17649,13 +17652,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-208.25</v>
+        <v>221</v>
       </c>
       <c r="Q291">
-        <v>-208.25</v>
+        <v>221</v>
       </c>
       <c r="R291">
-        <v>-2.16</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17663,13 +17666,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C292" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D292" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17690,7 +17693,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17699,7 +17702,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17719,13 +17722,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C293" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D293" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17755,7 +17758,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17775,13 +17778,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C294" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D294" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17811,7 +17814,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17834,13 +17837,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C295" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D295" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17870,7 +17873,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17890,13 +17893,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C296" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D296" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17926,7 +17929,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17946,13 +17949,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C297" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D297" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17970,7 +17973,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>116.47</v>
+        <v>117.27</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17982,13 +17985,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>-2.55</v>
+        <v>65.45</v>
       </c>
       <c r="Q297">
-        <v>-2.55</v>
+        <v>65.45</v>
       </c>
       <c r="R297">
-        <v>-0.03</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -17996,13 +17999,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C298" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D298" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18032,7 +18035,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18052,13 +18055,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C299" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D299" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18088,7 +18091,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18108,13 +18111,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C300" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D300" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18144,7 +18147,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18164,13 +18167,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C301" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D301" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18200,7 +18203,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18220,13 +18223,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C302" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D302" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18256,7 +18259,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18276,13 +18279,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C303" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D303" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18303,7 +18306,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18312,7 +18315,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18332,13 +18335,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C304" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D304" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18368,7 +18371,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18388,13 +18391,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C305" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D305" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18424,7 +18427,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18444,10 +18447,10 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C306" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D306" t="s">
         <v>255</v>
@@ -18462,7 +18465,7 @@
         <v>4</v>
       </c>
       <c r="H306">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I306">
         <v>9080</v>
@@ -18470,23 +18473,29 @@
       <c r="J306">
         <v>2190</v>
       </c>
+      <c r="K306" t="s">
+        <v>160</v>
+      </c>
       <c r="L306">
         <v>2156.5</v>
       </c>
       <c r="M306">
-        <v>0</v>
+        <v>2156.5</v>
+      </c>
+      <c r="N306" t="s">
+        <v>273</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>-454</v>
       </c>
       <c r="P306">
-        <v>-320</v>
+        <v>0</v>
       </c>
       <c r="Q306">
-        <v>-320</v>
+        <v>-454</v>
       </c>
       <c r="R306">
-        <v>-3.52</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -18494,13 +18503,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C307" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D307" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18530,7 +18539,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18550,13 +18559,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C308" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D308" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18586,7 +18595,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18606,13 +18615,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C309" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D309" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18633,7 +18642,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18642,7 +18651,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18662,13 +18671,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C310" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D310" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18698,7 +18707,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18718,13 +18727,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C311" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D311" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18754,7 +18763,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18774,13 +18783,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C312" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D312" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18810,7 +18819,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18830,13 +18839,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C313" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D313" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18866,7 +18875,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18886,13 +18895,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C314" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D314" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18910,7 +18919,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1015</v>
+        <v>1040.3</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18922,13 +18931,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-368.1</v>
+        <v>-140.4</v>
       </c>
       <c r="Q314">
-        <v>-368.1</v>
+        <v>-140.4</v>
       </c>
       <c r="R314">
-        <v>-3.87</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18936,13 +18945,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C315" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D315" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18960,7 +18969,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4788</v>
+        <v>4800.3</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18972,13 +18981,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>44.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q315">
-        <v>44.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="R315">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -18986,13 +18995,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C316" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D316" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19010,7 +19019,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19022,13 +19031,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-44.4</v>
+        <v>246</v>
       </c>
       <c r="Q316">
-        <v>-44.4</v>
+        <v>246</v>
       </c>
       <c r="R316">
-        <v>-0.5</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19036,13 +19045,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C317" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D317" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19060,7 +19069,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>310.5</v>
+        <v>312</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19072,13 +19081,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-254.2</v>
+        <v>-207.7</v>
       </c>
       <c r="Q317">
-        <v>-254.2</v>
+        <v>-207.7</v>
       </c>
       <c r="R317">
-        <v>-2.57</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19086,13 +19095,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C318" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D318" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19113,7 +19122,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19122,7 +19131,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19142,13 +19151,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C319" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D319" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19166,7 +19175,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19178,13 +19187,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>246.4</v>
+        <v>326.4</v>
       </c>
       <c r="Q319">
-        <v>246.4</v>
+        <v>326.4</v>
       </c>
       <c r="R319">
-        <v>2.69</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19192,13 +19201,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C320" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D320" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19216,7 +19225,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19228,13 +19237,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-63.25</v>
+        <v>-155.25</v>
       </c>
       <c r="Q320">
-        <v>-63.25</v>
+        <v>-155.25</v>
       </c>
       <c r="R320">
-        <v>-0.66</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19242,13 +19251,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C321" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D321" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19266,7 +19275,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2789</v>
+        <v>2824</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19278,13 +19287,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-93</v>
+        <v>12</v>
       </c>
       <c r="Q321">
-        <v>-93</v>
+        <v>12</v>
       </c>
       <c r="R321">
-        <v>-1.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19292,13 +19301,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C322" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D322" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19316,7 +19325,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19328,13 +19337,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>-183.5</v>
+        <v>245</v>
       </c>
       <c r="Q322">
-        <v>-183.5</v>
+        <v>245</v>
       </c>
       <c r="R322">
-        <v>-2.07</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19342,13 +19351,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C323" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D323" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19366,7 +19375,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1258.3</v>
+        <v>1249.3</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19378,13 +19387,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="Q323">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="R323">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19392,13 +19401,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C324" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D324" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19416,7 +19425,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>490.5</v>
+        <v>492</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19428,13 +19437,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>409.5</v>
+        <v>441</v>
       </c>
       <c r="Q324">
-        <v>409.5</v>
+        <v>441</v>
       </c>
       <c r="R324">
-        <v>4.14</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19442,13 +19451,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C325" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D325" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19466,7 +19475,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1039.3</v>
+        <v>1058.6</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19478,13 +19487,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>-138.6</v>
+        <v>35.1</v>
       </c>
       <c r="Q325">
-        <v>-138.6</v>
+        <v>35.1</v>
       </c>
       <c r="R325">
-        <v>-1.46</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19492,13 +19501,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C326" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D326" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19516,7 +19525,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>161.87</v>
+        <v>162.57</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19528,13 +19537,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>234.36</v>
+        <v>278.46</v>
       </c>
       <c r="Q326">
-        <v>234.36</v>
+        <v>278.46</v>
       </c>
       <c r="R326">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19542,13 +19551,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C327" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D327" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19566,7 +19575,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1840.3</v>
+        <v>1917.8</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19578,13 +19587,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>100</v>
+        <v>487.5</v>
       </c>
       <c r="Q327">
-        <v>100</v>
+        <v>487.5</v>
       </c>
       <c r="R327">
-        <v>1.1</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19592,13 +19601,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C328" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D328" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19616,7 +19625,7 @@
         <v>9693</v>
       </c>
       <c r="J328">
-        <v>1058.6</v>
+        <v>1051.4</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19628,13 +19637,13 @@
         <v>0</v>
       </c>
       <c r="P328">
-        <v>-165.6</v>
+        <v>-230.4</v>
       </c>
       <c r="Q328">
-        <v>-165.6</v>
+        <v>-230.4</v>
       </c>
       <c r="R328">
-        <v>-1.71</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -19642,13 +19651,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C329" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D329" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -19666,7 +19675,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="L329">
         <v>299.49</v>
@@ -19678,13 +19687,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>220.1</v>
+        <v>359.6</v>
       </c>
       <c r="Q329">
-        <v>220.1</v>
+        <v>359.6</v>
       </c>
       <c r="R329">
-        <v>2.25</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19692,13 +19701,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C330" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D330" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19716,7 +19725,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4841</v>
+        <v>4798.5</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19728,13 +19737,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>-30</v>
+        <v>-115</v>
       </c>
       <c r="Q330">
-        <v>-30</v>
+        <v>-115</v>
       </c>
       <c r="R330">
-        <v>-0.31</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19742,13 +19751,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C331" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D331" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19766,7 +19775,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19778,13 +19787,113 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-41.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Q331">
-        <v>-41.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R331">
-        <v>-0.44</v>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18">
+      <c r="A332" t="s">
+        <v>160</v>
+      </c>
+      <c r="B332" t="s">
+        <v>178</v>
+      </c>
+      <c r="C332" t="s">
+        <v>252</v>
+      </c>
+      <c r="D332" t="s">
+        <v>256</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>1132.4</v>
+      </c>
+      <c r="G332">
+        <v>8</v>
+      </c>
+      <c r="H332">
+        <v>8</v>
+      </c>
+      <c r="I332">
+        <v>9059.200000000001</v>
+      </c>
+      <c r="J332">
+        <v>1132.4</v>
+      </c>
+      <c r="L332">
+        <v>1075.78</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="O332">
+        <v>0</v>
+      </c>
+      <c r="P332">
+        <v>0</v>
+      </c>
+      <c r="Q332">
+        <v>0</v>
+      </c>
+      <c r="R332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18">
+      <c r="A333" t="s">
+        <v>160</v>
+      </c>
+      <c r="B333" t="s">
+        <v>215</v>
+      </c>
+      <c r="C333" t="s">
+        <v>253</v>
+      </c>
+      <c r="D333" t="s">
+        <v>256</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>1800</v>
+      </c>
+      <c r="G333">
+        <v>5</v>
+      </c>
+      <c r="H333">
+        <v>5</v>
+      </c>
+      <c r="I333">
+        <v>9000</v>
+      </c>
+      <c r="J333">
+        <v>1800</v>
+      </c>
+      <c r="L333">
+        <v>1710</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="O333">
+        <v>0</v>
+      </c>
+      <c r="P333">
+        <v>0</v>
+      </c>
+      <c r="Q333">
+        <v>0</v>
+      </c>
+      <c r="R333">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="280">
   <si>
     <t>Buy Date</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1214,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S333"/>
+  <dimension ref="A1:S335"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1291,13 +1294,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1327,7 +1330,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1347,13 +1350,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1383,7 +1386,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1406,13 +1409,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1442,7 +1445,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1462,13 +1465,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1498,7 +1501,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1518,13 +1521,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1554,7 +1557,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1574,13 +1577,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1610,7 +1613,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1630,13 +1633,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1666,7 +1669,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1686,13 +1689,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1722,7 +1725,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1742,13 +1745,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1778,7 +1781,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1798,13 +1801,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1825,7 +1828,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1834,7 +1837,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1849,7 +1852,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1857,13 +1860,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1893,7 +1896,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1916,13 +1919,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1952,7 +1955,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1972,13 +1975,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2008,7 +2011,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2028,13 +2031,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2064,7 +2067,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2084,13 +2087,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2120,7 +2123,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2140,13 +2143,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2176,7 +2179,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2196,13 +2199,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2232,7 +2235,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2252,13 +2255,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2288,7 +2291,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2308,13 +2311,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2344,7 +2347,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2364,13 +2367,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2391,7 +2394,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2400,7 +2403,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2420,13 +2423,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2447,7 +2450,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2456,7 +2459,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2476,13 +2479,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2512,7 +2515,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2532,13 +2535,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2568,7 +2571,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2588,13 +2591,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2624,7 +2627,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2644,13 +2647,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2671,7 +2674,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2680,7 +2683,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2700,13 +2703,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2736,7 +2739,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2756,13 +2759,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2792,7 +2795,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2812,13 +2815,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2848,7 +2851,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2868,13 +2871,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2904,7 +2907,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2924,13 +2927,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2951,7 +2954,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2960,7 +2963,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2980,13 +2983,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3016,7 +3019,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3036,13 +3039,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3072,7 +3075,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3092,13 +3095,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3119,7 +3122,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3128,7 +3131,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3148,13 +3151,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3175,7 +3178,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3184,7 +3187,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3204,13 +3207,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3240,7 +3243,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3260,13 +3263,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3296,7 +3299,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3316,13 +3319,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3352,7 +3355,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3375,13 +3378,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3411,7 +3414,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3431,13 +3434,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3467,7 +3470,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3487,13 +3490,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3523,7 +3526,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3543,13 +3546,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3570,7 +3573,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3579,7 +3582,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3599,13 +3602,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3626,7 +3629,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3635,7 +3638,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3655,13 +3658,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3691,7 +3694,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3711,13 +3714,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3747,7 +3750,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3767,13 +3770,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3803,7 +3806,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3826,13 +3829,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3862,7 +3865,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3882,13 +3885,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3918,7 +3921,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3938,13 +3941,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3974,7 +3977,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3997,13 +4000,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4033,7 +4036,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4053,13 +4056,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4089,7 +4092,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4109,13 +4112,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D52" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4145,7 +4148,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4168,13 +4171,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D53" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4204,7 +4207,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4224,13 +4227,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4260,7 +4263,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4283,13 +4286,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4319,7 +4322,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4342,13 +4345,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4378,7 +4381,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4398,13 +4401,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4425,7 +4428,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4434,7 +4437,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4454,13 +4457,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4490,7 +4493,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4510,13 +4513,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4546,7 +4549,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4569,13 +4572,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D60" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4605,7 +4608,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4625,13 +4628,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4661,7 +4664,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4684,13 +4687,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4720,7 +4723,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4735,7 +4738,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4743,13 +4746,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4779,7 +4782,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4799,13 +4802,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D64" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4835,7 +4838,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4855,13 +4858,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4891,7 +4894,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4911,13 +4914,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D66" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4947,7 +4950,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4967,13 +4970,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5003,7 +5006,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5023,13 +5026,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5059,7 +5062,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5079,13 +5082,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5106,7 +5109,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5115,7 +5118,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5135,13 +5138,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5171,7 +5174,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5191,13 +5194,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5227,7 +5230,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5247,13 +5250,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D72" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5283,7 +5286,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5303,13 +5306,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D73" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5339,7 +5342,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5359,13 +5362,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5395,7 +5398,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5415,13 +5418,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5451,7 +5454,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5471,13 +5474,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5507,7 +5510,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5527,13 +5530,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5563,7 +5566,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5583,13 +5586,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5619,7 +5622,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5639,13 +5642,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C79" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5675,7 +5678,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5695,13 +5698,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5731,7 +5734,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5751,13 +5754,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5787,7 +5790,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5807,13 +5810,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5843,7 +5846,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5866,13 +5869,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5902,7 +5905,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5922,13 +5925,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C84" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D84" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5958,7 +5961,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5978,13 +5981,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D85" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6014,7 +6017,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6034,13 +6037,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6070,7 +6073,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6090,13 +6093,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6126,7 +6129,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6146,13 +6149,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6182,7 +6185,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6202,13 +6205,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6238,7 +6241,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6258,13 +6261,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6294,7 +6297,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6314,13 +6317,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6350,7 +6353,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6373,13 +6376,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6409,7 +6412,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6429,13 +6432,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6465,7 +6468,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6485,13 +6488,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6521,7 +6524,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6541,13 +6544,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6577,7 +6580,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6597,13 +6600,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C96" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D96" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6633,7 +6636,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6653,13 +6656,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D97" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6689,7 +6692,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6709,13 +6712,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C98" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D98" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6745,7 +6748,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6768,13 +6771,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C99" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6804,7 +6807,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6824,13 +6827,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6860,7 +6863,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6880,13 +6883,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C101" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D101" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6916,7 +6919,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6936,13 +6939,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6972,7 +6975,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6992,13 +6995,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C103" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D103" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7028,7 +7031,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7048,13 +7051,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C104" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D104" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7084,7 +7087,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7104,13 +7107,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D105" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7140,7 +7143,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7160,13 +7163,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D106" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7187,7 +7190,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7196,7 +7199,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7216,13 +7219,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7252,7 +7255,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7272,13 +7275,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7308,7 +7311,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7328,13 +7331,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D109" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7355,7 +7358,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7364,7 +7367,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7384,13 +7387,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D110" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7420,7 +7423,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7440,13 +7443,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C111" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7476,7 +7479,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7496,13 +7499,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D112" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7532,7 +7535,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7552,13 +7555,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D113" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7588,7 +7591,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7608,13 +7611,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C114" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D114" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7644,7 +7647,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7664,13 +7667,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D115" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7700,7 +7703,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7720,13 +7723,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D116" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7756,7 +7759,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7776,13 +7779,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7812,7 +7815,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7832,13 +7835,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D118" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7868,7 +7871,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7891,13 +7894,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7927,7 +7930,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7947,13 +7950,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C120" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D120" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7983,7 +7986,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8003,13 +8006,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C121" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D121" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8039,7 +8042,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8059,13 +8062,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D122" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8095,7 +8098,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8115,13 +8118,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C123" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D123" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8142,7 +8145,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8151,7 +8154,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8171,13 +8174,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8207,7 +8210,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8227,13 +8230,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D125" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8263,7 +8266,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8283,13 +8286,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D126" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8319,7 +8322,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8342,13 +8345,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8378,7 +8381,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8398,13 +8401,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8434,7 +8437,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8457,13 +8460,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C129" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8493,7 +8496,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8513,13 +8516,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C130" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D130" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8549,7 +8552,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8569,13 +8572,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8605,7 +8608,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8625,13 +8628,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C132" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8661,7 +8664,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8681,13 +8684,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C133" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D133" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8708,7 +8711,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8717,7 +8720,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8737,13 +8740,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C134" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8773,7 +8776,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8793,13 +8796,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C135" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D135" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8829,7 +8832,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8849,13 +8852,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D136" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8885,7 +8888,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8905,13 +8908,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C137" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8941,7 +8944,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8964,13 +8967,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C138" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D138" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9000,7 +9003,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9020,13 +9023,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C139" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D139" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9056,7 +9059,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9076,13 +9079,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C140" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D140" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9112,7 +9115,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9132,13 +9135,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C141" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D141" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9168,7 +9171,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9188,13 +9191,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C142" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D142" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9224,7 +9227,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9244,13 +9247,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C143" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D143" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9280,7 +9283,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9300,13 +9303,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D144" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9336,7 +9339,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9356,13 +9359,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C145" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D145" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9392,7 +9395,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9412,13 +9415,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D146" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9448,7 +9451,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9471,13 +9474,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C147" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D147" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9507,7 +9510,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9530,13 +9533,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C148" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D148" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9566,7 +9569,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9589,13 +9592,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9616,7 +9619,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9625,7 +9628,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9648,13 +9651,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D150" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9684,7 +9687,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9707,13 +9710,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9743,7 +9746,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9763,13 +9766,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C152" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9799,7 +9802,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9822,13 +9825,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C153" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D153" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9858,7 +9861,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9881,13 +9884,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C154" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D154" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9917,7 +9920,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9932,7 +9935,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9940,13 +9943,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C155" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D155" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9976,7 +9979,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -9999,13 +10002,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C156" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D156" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10035,7 +10038,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10055,13 +10058,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C157" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D157" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10091,7 +10094,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10111,13 +10114,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C158" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D158" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10147,7 +10150,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10167,13 +10170,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C159" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D159" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10203,7 +10206,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10226,13 +10229,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C160" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D160" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10262,7 +10265,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10282,13 +10285,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C161" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10318,7 +10321,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10341,13 +10344,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C162" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D162" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10377,7 +10380,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10397,13 +10400,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C163" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D163" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10433,7 +10436,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10456,13 +10459,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C164" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D164" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10483,7 +10486,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10492,7 +10495,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10515,13 +10518,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10542,7 +10545,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10551,7 +10554,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10571,13 +10574,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C166" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D166" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10607,7 +10610,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10630,13 +10633,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C167" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D167" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10666,7 +10669,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10686,13 +10689,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C168" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D168" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10722,7 +10725,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10742,13 +10745,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C169" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D169" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10778,7 +10781,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10801,13 +10804,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C170" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D170" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10837,7 +10840,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10860,13 +10863,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D171" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10896,7 +10899,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10916,13 +10919,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C172" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D172" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10952,7 +10955,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10975,13 +10978,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C173" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D173" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11011,7 +11014,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11031,13 +11034,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C174" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D174" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11067,7 +11070,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11090,13 +11093,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C175" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D175" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11126,7 +11129,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11146,13 +11149,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C176" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D176" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11182,7 +11185,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11202,13 +11205,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11238,7 +11241,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11261,13 +11264,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C178" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D178" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11288,7 +11291,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11297,7 +11300,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11317,13 +11320,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C179" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D179" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11353,7 +11356,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11373,13 +11376,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C180" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D180" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11409,7 +11412,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11429,13 +11432,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C181" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11465,7 +11468,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11485,13 +11488,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C182" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D182" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11521,7 +11524,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11544,13 +11547,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C183" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D183" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11580,7 +11583,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11600,13 +11603,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D184" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11636,7 +11639,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11659,13 +11662,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C185" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D185" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11695,7 +11698,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11715,13 +11718,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C186" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D186" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11742,7 +11745,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11751,7 +11754,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11771,13 +11774,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C187" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D187" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11798,7 +11801,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11807,7 +11810,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11830,13 +11833,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C188" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D188" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11857,7 +11860,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11866,7 +11869,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11886,13 +11889,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C189" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D189" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11922,7 +11925,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11942,13 +11945,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C190" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D190" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11978,7 +11981,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -11998,13 +12001,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C191" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D191" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12025,7 +12028,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12034,7 +12037,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12049,7 +12052,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12057,13 +12060,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C192" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D192" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12093,7 +12096,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12113,13 +12116,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C193" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D193" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12149,7 +12152,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12169,13 +12172,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C194" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D194" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12196,7 +12199,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12205,7 +12208,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12225,13 +12228,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C195" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D195" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12261,7 +12264,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12276,7 +12279,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12284,13 +12287,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C196" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D196" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12320,7 +12323,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12343,13 +12346,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C197" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D197" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12370,7 +12373,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12379,7 +12382,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12399,13 +12402,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C198" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D198" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12435,7 +12438,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12455,13 +12458,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C199" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D199" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12491,7 +12494,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12511,13 +12514,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C200" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D200" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12547,7 +12550,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12567,13 +12570,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C201" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D201" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12603,7 +12606,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12623,13 +12626,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C202" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D202" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12659,7 +12662,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12679,13 +12682,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C203" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D203" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12715,7 +12718,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12730,7 +12733,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12738,13 +12741,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C204" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D204" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12774,7 +12777,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12794,13 +12797,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C205" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D205" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12830,7 +12833,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12850,13 +12853,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C206" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D206" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12886,7 +12889,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12906,13 +12909,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C207" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D207" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12942,7 +12945,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12965,13 +12968,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C208" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D208" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13001,7 +13004,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13021,13 +13024,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C209" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D209" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13057,7 +13060,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13077,13 +13080,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C210" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D210" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13104,7 +13107,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13113,7 +13116,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13133,13 +13136,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C211" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D211" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13169,7 +13172,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13189,13 +13192,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C212" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D212" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13225,7 +13228,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13245,13 +13248,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C213" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D213" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13281,7 +13284,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13301,13 +13304,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C214" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D214" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13337,7 +13340,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13352,7 +13355,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13360,13 +13363,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C215" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D215" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13396,7 +13399,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13416,13 +13419,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C216" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D216" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13452,7 +13455,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13472,13 +13475,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C217" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D217" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13508,7 +13511,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13528,13 +13531,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C218" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D218" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13564,7 +13567,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13584,13 +13587,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C219" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D219" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13620,7 +13623,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13640,13 +13643,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C220" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D220" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13667,7 +13670,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13676,7 +13679,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13696,13 +13699,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C221" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D221" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13723,7 +13726,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13732,7 +13735,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13752,13 +13755,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C222" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D222" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13788,7 +13791,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13808,13 +13811,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C223" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D223" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13835,7 +13838,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13844,7 +13847,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13864,13 +13867,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C224" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D224" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13900,7 +13903,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13920,13 +13923,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D225" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13956,7 +13959,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13976,13 +13979,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C226" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D226" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14012,7 +14015,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14032,13 +14035,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C227" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D227" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14068,7 +14071,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14088,13 +14091,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C228" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D228" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14124,7 +14127,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14144,13 +14147,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D229" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14168,7 +14171,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8944.5</v>
+        <v>8912</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14180,13 +14183,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>654</v>
+        <v>621.5</v>
       </c>
       <c r="Q229">
-        <v>654</v>
+        <v>621.5</v>
       </c>
       <c r="R229">
-        <v>7.89</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14194,13 +14197,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C230" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D230" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14230,7 +14233,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14250,13 +14253,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C231" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D231" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14277,7 +14280,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14286,7 +14289,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14301,7 +14304,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14309,13 +14312,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C232" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D232" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14345,7 +14348,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14365,13 +14368,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C233" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D233" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14401,7 +14404,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14421,13 +14424,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C234" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D234" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14457,7 +14460,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14477,13 +14480,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C235" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D235" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14504,7 +14507,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14513,7 +14516,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14536,13 +14539,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C236" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D236" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14563,7 +14566,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14572,7 +14575,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14595,13 +14598,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C237" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D237" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14631,7 +14634,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14651,13 +14654,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C238" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D238" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14687,7 +14690,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14707,13 +14710,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C239" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D239" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14743,7 +14746,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14763,13 +14766,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C240" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D240" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14799,7 +14802,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14819,13 +14822,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C241" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D241" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14855,7 +14858,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14875,13 +14878,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C242" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D242" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14911,7 +14914,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14931,13 +14934,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C243" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D243" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14967,7 +14970,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14990,13 +14993,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C244" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D244" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15026,7 +15029,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15041,7 +15044,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15049,13 +15052,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C245" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D245" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15076,7 +15079,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15085,7 +15088,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15105,13 +15108,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C246" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D246" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15141,7 +15144,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15161,13 +15164,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C247" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D247" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15197,7 +15200,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15217,13 +15220,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D248" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15253,7 +15256,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15273,13 +15276,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D249" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15309,7 +15312,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15329,13 +15332,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D250" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15365,7 +15368,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15385,13 +15388,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C251" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D251" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15421,7 +15424,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15441,13 +15444,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C252" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D252" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15477,7 +15480,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15500,13 +15503,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C253" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D253" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15536,7 +15539,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15556,13 +15559,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D254" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15580,7 +15583,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>732.75</v>
+        <v>745</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15592,13 +15595,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>359.8</v>
+        <v>531.3</v>
       </c>
       <c r="Q254">
-        <v>359.8</v>
+        <v>531.3</v>
       </c>
       <c r="R254">
-        <v>3.63</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15606,13 +15609,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C255" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D255" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15642,7 +15645,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15662,13 +15665,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C256" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D256" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15698,7 +15701,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15718,13 +15721,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C257" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D257" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15745,7 +15748,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15754,7 +15757,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15774,13 +15777,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C258" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15810,7 +15813,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15830,13 +15833,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C259" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D259" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15866,7 +15869,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15889,13 +15892,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C260" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D260" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15913,7 +15916,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1226.4</v>
+        <v>1247.4</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15925,13 +15928,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-346.5</v>
+        <v>-199.5</v>
       </c>
       <c r="Q260">
-        <v>-346.5</v>
+        <v>-199.5</v>
       </c>
       <c r="R260">
-        <v>-3.88</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15939,13 +15942,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C261" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D261" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15963,7 +15966,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1338.9</v>
+        <v>1345</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15975,13 +15978,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-291.9</v>
+        <v>-249.2</v>
       </c>
       <c r="Q261">
-        <v>-291.9</v>
+        <v>-249.2</v>
       </c>
       <c r="R261">
-        <v>-3.02</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15989,13 +15992,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C262" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D262" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16025,7 +16028,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16048,13 +16051,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C263" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D263" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16084,7 +16087,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16104,13 +16107,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C264" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D264" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16140,7 +16143,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16163,13 +16166,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C265" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D265" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16199,7 +16202,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16222,13 +16225,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D266" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16258,7 +16261,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16278,13 +16281,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C267" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D267" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16314,7 +16317,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16334,13 +16337,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C268" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D268" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16370,7 +16373,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16390,13 +16393,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C269" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D269" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16426,7 +16429,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16446,13 +16449,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C270" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D270" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16482,7 +16485,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16502,13 +16505,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C271" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D271" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16526,7 +16529,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1572.1</v>
+        <v>1573.2</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16538,13 +16541,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-115.2</v>
+        <v>-108.6</v>
       </c>
       <c r="Q271">
-        <v>-115.2</v>
+        <v>-108.6</v>
       </c>
       <c r="R271">
-        <v>-1.21</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16552,13 +16555,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C272" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D272" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16588,7 +16591,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16608,13 +16611,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C273" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D273" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16644,7 +16647,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16664,13 +16667,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C274" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D274" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16691,7 +16694,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16700,7 +16703,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16720,13 +16723,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C275" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D275" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16756,7 +16759,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16776,13 +16779,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C276" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D276" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16812,7 +16815,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16832,13 +16835,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C277" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D277" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16868,7 +16871,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16888,13 +16891,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C278" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D278" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16924,7 +16927,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16944,13 +16947,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C279" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D279" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16980,7 +16983,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17000,13 +17003,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C280" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D280" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17036,7 +17039,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17056,13 +17059,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C281" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D281" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17092,7 +17095,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17112,13 +17115,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C282" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D282" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17148,7 +17151,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17168,13 +17171,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C283" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D283" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17204,7 +17207,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17224,13 +17227,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C284" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D284" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17260,7 +17263,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17280,13 +17283,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C285" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D285" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17316,7 +17319,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17336,13 +17339,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C286" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D286" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17372,7 +17375,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17392,13 +17395,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C287" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D287" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17428,7 +17431,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17448,13 +17451,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C288" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D288" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17484,7 +17487,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17504,13 +17507,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C289" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D289" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17531,7 +17534,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17540,7 +17543,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17560,13 +17563,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C290" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D290" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17596,7 +17599,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17616,13 +17619,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C291" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D291" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17640,7 +17643,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>580</v>
+        <v>559.9</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17652,13 +17655,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>221</v>
+        <v>-120.7</v>
       </c>
       <c r="Q291">
-        <v>221</v>
+        <v>-120.7</v>
       </c>
       <c r="R291">
-        <v>2.29</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17666,13 +17669,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C292" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D292" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17693,7 +17696,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17702,7 +17705,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17722,13 +17725,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C293" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D293" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17758,7 +17761,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17778,13 +17781,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C294" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D294" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17814,7 +17817,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17837,13 +17840,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C295" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D295" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17873,7 +17876,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17893,13 +17896,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C296" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D296" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17929,7 +17932,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17949,13 +17952,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C297" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D297" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17973,7 +17976,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>117.27</v>
+        <v>118</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17985,13 +17988,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>65.45</v>
+        <v>127.5</v>
       </c>
       <c r="Q297">
-        <v>65.45</v>
+        <v>127.5</v>
       </c>
       <c r="R297">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -17999,13 +18002,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C298" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D298" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18035,7 +18038,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18055,13 +18058,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C299" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D299" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18091,7 +18094,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18111,13 +18114,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C300" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D300" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18147,7 +18150,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18167,13 +18170,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C301" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D301" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18203,7 +18206,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18223,13 +18226,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C302" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D302" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18259,7 +18262,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18279,13 +18282,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C303" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D303" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18306,7 +18309,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18315,7 +18318,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18335,13 +18338,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C304" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D304" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18371,7 +18374,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18391,13 +18394,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C305" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D305" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18427,7 +18430,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18447,13 +18450,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C306" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D306" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18483,7 +18486,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18503,13 +18506,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C307" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D307" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18539,7 +18542,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18559,13 +18562,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C308" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D308" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18595,7 +18598,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18615,13 +18618,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C309" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D309" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18642,7 +18645,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18651,7 +18654,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18671,13 +18674,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C310" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D310" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18707,7 +18710,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18727,13 +18730,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C311" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D311" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18763,7 +18766,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18783,13 +18786,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C312" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D312" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18819,7 +18822,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18839,13 +18842,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C313" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D313" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18875,7 +18878,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18895,13 +18898,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C314" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D314" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18919,7 +18922,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1040.3</v>
+        <v>1021.3</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18931,13 +18934,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-140.4</v>
+        <v>-311.4</v>
       </c>
       <c r="Q314">
-        <v>-140.4</v>
+        <v>-311.4</v>
       </c>
       <c r="R314">
-        <v>-1.48</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18945,13 +18948,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C315" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D315" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18969,7 +18972,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4800.3</v>
+        <v>4826</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18981,13 +18984,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>69.40000000000001</v>
+        <v>120.8</v>
       </c>
       <c r="Q315">
-        <v>69.40000000000001</v>
+        <v>120.8</v>
       </c>
       <c r="R315">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -18995,13 +18998,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C316" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D316" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19019,7 +19022,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>3020</v>
+        <v>2975</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19031,13 +19034,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="Q316">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="R316">
-        <v>2.79</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19045,13 +19048,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C317" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D317" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19069,7 +19072,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>312</v>
+        <v>310.2</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19081,13 +19084,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-207.7</v>
+        <v>-263.5</v>
       </c>
       <c r="Q317">
-        <v>-207.7</v>
+        <v>-263.5</v>
       </c>
       <c r="R317">
-        <v>-2.1</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19095,13 +19098,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C318" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D318" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19122,7 +19125,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19131,7 +19134,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19151,13 +19154,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C319" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D319" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19175,7 +19178,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1185</v>
+        <v>1198.3</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19187,13 +19190,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>326.4</v>
+        <v>432.8</v>
       </c>
       <c r="Q319">
-        <v>326.4</v>
+        <v>432.8</v>
       </c>
       <c r="R319">
-        <v>3.57</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19201,13 +19204,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C320" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D320" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19225,7 +19228,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>412.5</v>
+        <v>414.8</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19237,13 +19240,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-155.25</v>
+        <v>-102.35</v>
       </c>
       <c r="Q320">
-        <v>-155.25</v>
+        <v>-102.35</v>
       </c>
       <c r="R320">
-        <v>-1.61</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19251,13 +19254,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C321" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D321" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19275,7 +19278,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2824</v>
+        <v>2815.5</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19287,13 +19290,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>12</v>
+        <v>-13.5</v>
       </c>
       <c r="Q321">
-        <v>12</v>
+        <v>-13.5</v>
       </c>
       <c r="R321">
-        <v>0.14</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19301,13 +19304,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C322" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D322" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19325,7 +19328,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1824</v>
+        <v>1787.1</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19337,13 +19340,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>245</v>
+        <v>60.5</v>
       </c>
       <c r="Q322">
-        <v>245</v>
+        <v>60.5</v>
       </c>
       <c r="R322">
-        <v>2.76</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19351,13 +19354,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C323" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D323" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19375,7 +19378,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1249.3</v>
+        <v>1281</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19387,13 +19390,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>156</v>
+        <v>409.6</v>
       </c>
       <c r="Q323">
-        <v>156</v>
+        <v>409.6</v>
       </c>
       <c r="R323">
-        <v>1.59</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19401,13 +19404,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C324" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D324" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19425,7 +19428,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19437,13 +19440,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="Q324">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="R324">
-        <v>4.46</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19451,13 +19454,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C325" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D325" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19475,7 +19478,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1058.6</v>
+        <v>1038</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19487,13 +19490,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>35.1</v>
+        <v>-150.3</v>
       </c>
       <c r="Q325">
-        <v>35.1</v>
+        <v>-150.3</v>
       </c>
       <c r="R325">
-        <v>0.37</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19501,13 +19504,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C326" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D326" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19525,7 +19528,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>162.57</v>
+        <v>162.91</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19537,13 +19540,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>278.46</v>
+        <v>299.88</v>
       </c>
       <c r="Q326">
-        <v>278.46</v>
+        <v>299.88</v>
       </c>
       <c r="R326">
-        <v>2.79</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19551,13 +19554,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C327" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D327" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19575,7 +19578,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1917.8</v>
+        <v>1892</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19587,13 +19590,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>487.5</v>
+        <v>358.5</v>
       </c>
       <c r="Q327">
-        <v>487.5</v>
+        <v>358.5</v>
       </c>
       <c r="R327">
-        <v>5.36</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19601,13 +19604,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C328" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D328" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19625,7 +19628,7 @@
         <v>9693</v>
       </c>
       <c r="J328">
-        <v>1051.4</v>
+        <v>1038.5</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19637,13 +19640,13 @@
         <v>0</v>
       </c>
       <c r="P328">
-        <v>-230.4</v>
+        <v>-346.5</v>
       </c>
       <c r="Q328">
-        <v>-230.4</v>
+        <v>-346.5</v>
       </c>
       <c r="R328">
-        <v>-2.38</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -19651,13 +19654,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C329" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D329" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -19675,7 +19678,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>326.85</v>
+        <v>335.9</v>
       </c>
       <c r="L329">
         <v>299.49</v>
@@ -19687,13 +19690,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>359.6</v>
+        <v>640.15</v>
       </c>
       <c r="Q329">
-        <v>359.6</v>
+        <v>640.15</v>
       </c>
       <c r="R329">
-        <v>3.68</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19701,13 +19704,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C330" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D330" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19725,7 +19728,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4798.5</v>
+        <v>4875</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19737,13 +19740,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>-115</v>
+        <v>38</v>
       </c>
       <c r="Q330">
-        <v>-115</v>
+        <v>38</v>
       </c>
       <c r="R330">
-        <v>-1.18</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19751,13 +19754,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C331" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D331" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19775,7 +19778,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19787,13 +19790,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>66.59999999999999</v>
+        <v>-63</v>
       </c>
       <c r="Q331">
-        <v>66.59999999999999</v>
+        <v>-63</v>
       </c>
       <c r="R331">
-        <v>0.7</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19801,13 +19804,13 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C332" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D332" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -19825,7 +19828,7 @@
         <v>9059.200000000001</v>
       </c>
       <c r="J332">
-        <v>1132.4</v>
+        <v>1103.1</v>
       </c>
       <c r="L332">
         <v>1075.78</v>
@@ -19837,13 +19840,13 @@
         <v>0</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>-234.4</v>
       </c>
       <c r="Q332">
-        <v>0</v>
+        <v>-234.4</v>
       </c>
       <c r="R332">
-        <v>0</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19851,13 +19854,13 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C333" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D333" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -19875,7 +19878,7 @@
         <v>9000</v>
       </c>
       <c r="J333">
-        <v>1800</v>
+        <v>1764</v>
       </c>
       <c r="L333">
         <v>1710</v>
@@ -19887,12 +19890,112 @@
         <v>0</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="Q333">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="R333">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18">
+      <c r="A334" t="s">
+        <v>161</v>
+      </c>
+      <c r="B334" t="s">
+        <v>188</v>
+      </c>
+      <c r="C334" t="s">
+        <v>253</v>
+      </c>
+      <c r="D334" t="s">
+        <v>257</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>1509.1</v>
+      </c>
+      <c r="G334">
+        <v>6</v>
+      </c>
+      <c r="H334">
+        <v>6</v>
+      </c>
+      <c r="I334">
+        <v>9054.599999999999</v>
+      </c>
+      <c r="J334">
+        <v>1509.1</v>
+      </c>
+      <c r="L334">
+        <v>1433.64</v>
+      </c>
+      <c r="M334">
+        <v>0</v>
+      </c>
+      <c r="O334">
+        <v>0</v>
+      </c>
+      <c r="P334">
+        <v>0</v>
+      </c>
+      <c r="Q334">
+        <v>0</v>
+      </c>
+      <c r="R334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18">
+      <c r="A335" t="s">
+        <v>161</v>
+      </c>
+      <c r="B335" t="s">
+        <v>164</v>
+      </c>
+      <c r="C335" t="s">
+        <v>253</v>
+      </c>
+      <c r="D335" t="s">
+        <v>257</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>5023</v>
+      </c>
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>5023</v>
+      </c>
+      <c r="J335">
+        <v>5023</v>
+      </c>
+      <c r="L335">
+        <v>4771.85</v>
+      </c>
+      <c r="M335">
+        <v>0</v>
+      </c>
+      <c r="O335">
+        <v>0</v>
+      </c>
+      <c r="P335">
+        <v>0</v>
+      </c>
+      <c r="Q335">
+        <v>0</v>
+      </c>
+      <c r="R335">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="281">
   <si>
     <t>Buy Date</t>
   </si>
@@ -836,6 +836,9 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -1330,7 +1333,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1386,7 +1389,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1445,7 +1448,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1501,7 +1504,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1557,7 +1560,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1613,7 +1616,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1669,7 +1672,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1725,7 +1728,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1781,7 +1784,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1837,7 +1840,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1896,7 +1899,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1955,7 +1958,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -2011,7 +2014,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2067,7 +2070,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2123,7 +2126,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2179,7 +2182,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2235,7 +2238,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2291,7 +2294,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2347,7 +2350,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2403,7 +2406,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2459,7 +2462,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2515,7 +2518,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2571,7 +2574,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2627,7 +2630,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2683,7 +2686,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2739,7 +2742,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2795,7 +2798,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2851,7 +2854,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2907,7 +2910,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2963,7 +2966,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -3019,7 +3022,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3075,7 +3078,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3131,7 +3134,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3187,7 +3190,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3243,7 +3246,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3299,7 +3302,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3355,7 +3358,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3414,7 +3417,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3470,7 +3473,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3526,7 +3529,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3582,7 +3585,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3638,7 +3641,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3694,7 +3697,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3750,7 +3753,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3806,7 +3809,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3865,7 +3868,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3921,7 +3924,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3977,7 +3980,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4036,7 +4039,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4092,7 +4095,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4148,7 +4151,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4207,7 +4210,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4263,7 +4266,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4322,7 +4325,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4381,7 +4384,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4437,7 +4440,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4493,7 +4496,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4549,7 +4552,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4608,7 +4611,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4664,7 +4667,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4723,7 +4726,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4738,7 +4741,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4782,7 +4785,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4838,7 +4841,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4894,7 +4897,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4950,7 +4953,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -5006,7 +5009,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5062,7 +5065,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5118,7 +5121,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5174,7 +5177,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5230,7 +5233,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5286,7 +5289,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5342,7 +5345,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5398,7 +5401,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5454,7 +5457,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5510,7 +5513,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5566,7 +5569,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5622,7 +5625,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5678,7 +5681,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5734,7 +5737,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5790,7 +5793,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5846,7 +5849,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5905,7 +5908,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5961,7 +5964,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -6017,7 +6020,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6073,7 +6076,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6129,7 +6132,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6185,7 +6188,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6241,7 +6244,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6297,7 +6300,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6353,7 +6356,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6412,7 +6415,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6468,7 +6471,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6524,7 +6527,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6580,7 +6583,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6636,7 +6639,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6692,7 +6695,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6748,7 +6751,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6807,7 +6810,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6863,7 +6866,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6919,7 +6922,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6975,7 +6978,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7031,7 +7034,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7087,7 +7090,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7143,7 +7146,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7199,7 +7202,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7255,7 +7258,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7311,7 +7314,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7367,7 +7370,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7423,7 +7426,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7479,7 +7482,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7535,7 +7538,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7591,7 +7594,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7647,7 +7650,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7703,7 +7706,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7759,7 +7762,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7815,7 +7818,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7871,7 +7874,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7930,7 +7933,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7986,7 +7989,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8042,7 +8045,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8098,7 +8101,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8154,7 +8157,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8210,7 +8213,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8266,7 +8269,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8322,7 +8325,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8381,7 +8384,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8437,7 +8440,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8496,7 +8499,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8552,7 +8555,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8608,7 +8611,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8664,7 +8667,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8720,7 +8723,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8776,7 +8779,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8832,7 +8835,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8888,7 +8891,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8944,7 +8947,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -9003,7 +9006,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9059,7 +9062,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9115,7 +9118,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9171,7 +9174,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9227,7 +9230,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9283,7 +9286,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9339,7 +9342,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9395,7 +9398,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9451,7 +9454,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9510,7 +9513,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9569,7 +9572,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9628,7 +9631,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9687,7 +9690,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9746,7 +9749,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9802,7 +9805,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9861,7 +9864,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9920,7 +9923,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9935,7 +9938,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9979,7 +9982,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10038,7 +10041,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10094,7 +10097,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10150,7 +10153,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10206,7 +10209,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10265,7 +10268,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10321,7 +10324,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10380,7 +10383,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10436,7 +10439,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10495,7 +10498,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10554,7 +10557,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10610,7 +10613,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10669,7 +10672,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10725,7 +10728,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10781,7 +10784,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10840,7 +10843,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10899,7 +10902,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10955,7 +10958,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -11014,7 +11017,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11070,7 +11073,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11129,7 +11132,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11185,7 +11188,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11241,7 +11244,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11300,7 +11303,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11356,7 +11359,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11412,7 +11415,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11468,7 +11471,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11524,7 +11527,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11583,7 +11586,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11639,7 +11642,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11698,7 +11701,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11754,7 +11757,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11810,7 +11813,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11869,7 +11872,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11925,7 +11928,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11981,7 +11984,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12037,7 +12040,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12096,7 +12099,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12152,7 +12155,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12208,7 +12211,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12264,7 +12267,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12279,7 +12282,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12323,7 +12326,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12382,7 +12385,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12438,7 +12441,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12494,7 +12497,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12550,7 +12553,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12606,7 +12609,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12662,7 +12665,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12718,7 +12721,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12777,7 +12780,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12833,7 +12836,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12889,7 +12892,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12945,7 +12948,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -13004,7 +13007,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13060,7 +13063,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13116,7 +13119,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13172,7 +13175,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13228,7 +13231,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13284,7 +13287,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13340,7 +13343,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13399,7 +13402,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13455,7 +13458,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13511,7 +13514,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13567,7 +13570,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13623,7 +13626,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13679,7 +13682,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13735,7 +13738,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13791,7 +13794,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13847,7 +13850,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13903,7 +13906,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13959,7 +13962,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -14015,7 +14018,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14071,7 +14074,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14127,7 +14130,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14171,7 +14174,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8912</v>
+        <v>8835.5</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14183,13 +14186,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>621.5</v>
+        <v>545</v>
       </c>
       <c r="Q229">
-        <v>621.5</v>
+        <v>545</v>
       </c>
       <c r="R229">
-        <v>7.5</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14233,7 +14236,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14289,7 +14292,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14348,7 +14351,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14404,7 +14407,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14460,7 +14463,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14516,7 +14519,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14575,7 +14578,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14634,7 +14637,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14690,7 +14693,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14746,7 +14749,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14802,7 +14805,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14858,7 +14861,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14914,7 +14917,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14970,7 +14973,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -15029,7 +15032,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15044,7 +15047,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15088,7 +15091,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15144,7 +15147,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15200,7 +15203,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15256,7 +15259,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15312,7 +15315,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15368,7 +15371,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15424,7 +15427,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15480,7 +15483,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15539,7 +15542,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15583,7 +15586,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>745</v>
+        <v>736.25</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15595,13 +15598,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>531.3</v>
+        <v>408.8</v>
       </c>
       <c r="Q254">
-        <v>531.3</v>
+        <v>408.8</v>
       </c>
       <c r="R254">
-        <v>5.37</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15645,7 +15648,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15701,7 +15704,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15757,7 +15760,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15813,7 +15816,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15869,7 +15872,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15916,7 +15919,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15928,13 +15931,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-199.5</v>
+        <v>-248.5</v>
       </c>
       <c r="Q260">
-        <v>-199.5</v>
+        <v>-248.5</v>
       </c>
       <c r="R260">
-        <v>-2.23</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15966,7 +15969,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1345</v>
+        <v>1339.6</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15978,13 +15981,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-249.2</v>
+        <v>-287</v>
       </c>
       <c r="Q261">
-        <v>-249.2</v>
+        <v>-287</v>
       </c>
       <c r="R261">
-        <v>-2.58</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -16028,7 +16031,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16087,7 +16090,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16143,7 +16146,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16202,7 +16205,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16261,7 +16264,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16317,7 +16320,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16373,7 +16376,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16429,7 +16432,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16485,7 +16488,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16529,7 +16532,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1573.2</v>
+        <v>1572.7</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16541,13 +16544,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-108.6</v>
+        <v>-111.6</v>
       </c>
       <c r="Q271">
-        <v>-108.6</v>
+        <v>-111.6</v>
       </c>
       <c r="R271">
-        <v>-1.14</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16591,7 +16594,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16647,7 +16650,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16703,7 +16706,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16759,7 +16762,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16815,7 +16818,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16871,7 +16874,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16927,7 +16930,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16983,7 +16986,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17039,7 +17042,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17095,7 +17098,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17151,7 +17154,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17207,7 +17210,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17263,7 +17266,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17319,7 +17322,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17375,7 +17378,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17431,7 +17434,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17487,7 +17490,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17543,7 +17546,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17599,7 +17602,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17705,7 +17708,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17761,7 +17764,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17817,7 +17820,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17876,7 +17879,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17932,7 +17935,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17976,7 +17979,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17988,13 +17991,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>127.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q297">
-        <v>127.5</v>
+        <v>42.5</v>
       </c>
       <c r="R297">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18038,7 +18041,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18094,7 +18097,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18150,7 +18153,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18206,7 +18209,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18262,7 +18265,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18318,7 +18321,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18374,7 +18377,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18430,7 +18433,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18486,7 +18489,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18542,7 +18545,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18598,7 +18601,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18654,7 +18657,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18710,7 +18713,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18766,7 +18769,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18822,7 +18825,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18878,7 +18881,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18922,7 +18925,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1021.3</v>
+        <v>1008.8</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18934,13 +18937,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-311.4</v>
+        <v>-423.9</v>
       </c>
       <c r="Q314">
-        <v>-311.4</v>
+        <v>-423.9</v>
       </c>
       <c r="R314">
-        <v>-3.28</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18972,7 +18975,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4826</v>
+        <v>4800</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18984,13 +18987,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>120.8</v>
+        <v>68.8</v>
       </c>
       <c r="Q315">
-        <v>120.8</v>
+        <v>68.8</v>
       </c>
       <c r="R315">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19022,7 +19025,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2975</v>
+        <v>2997</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19034,13 +19037,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="Q316">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="R316">
-        <v>1.26</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19072,7 +19075,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>310.2</v>
+        <v>307.1</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19084,13 +19087,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-263.5</v>
+        <v>-359.6</v>
       </c>
       <c r="Q317">
-        <v>-263.5</v>
+        <v>-359.6</v>
       </c>
       <c r="R317">
-        <v>-2.67</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19134,7 +19137,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19178,7 +19181,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1198.3</v>
+        <v>1211</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19190,13 +19193,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>432.8</v>
+        <v>534.4</v>
       </c>
       <c r="Q319">
-        <v>432.8</v>
+        <v>534.4</v>
       </c>
       <c r="R319">
-        <v>4.73</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19228,7 +19231,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>414.8</v>
+        <v>412.65</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19240,13 +19243,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-102.35</v>
+        <v>-151.8</v>
       </c>
       <c r="Q320">
-        <v>-102.35</v>
+        <v>-151.8</v>
       </c>
       <c r="R320">
-        <v>-1.06</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19278,7 +19281,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2815.5</v>
+        <v>2782.9</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19290,13 +19293,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-13.5</v>
+        <v>-111.3</v>
       </c>
       <c r="Q321">
-        <v>-13.5</v>
+        <v>-111.3</v>
       </c>
       <c r="R321">
-        <v>-0.16</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19328,7 +19331,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1787.1</v>
+        <v>1795</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19340,13 +19343,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="Q322">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="R322">
-        <v>0.68</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19378,7 +19381,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1281</v>
+        <v>1270.4</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19390,13 +19393,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>409.6</v>
+        <v>324.8</v>
       </c>
       <c r="Q323">
-        <v>409.6</v>
+        <v>324.8</v>
       </c>
       <c r="R323">
-        <v>4.16</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19428,7 +19431,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>493</v>
+        <v>486.65</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19440,13 +19443,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>462</v>
+        <v>328.65</v>
       </c>
       <c r="Q324">
-        <v>462</v>
+        <v>328.65</v>
       </c>
       <c r="R324">
-        <v>4.67</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19478,7 +19481,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1038</v>
+        <v>1036.4</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19490,13 +19493,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>-150.3</v>
+        <v>-164.7</v>
       </c>
       <c r="Q325">
-        <v>-150.3</v>
+        <v>-164.7</v>
       </c>
       <c r="R325">
-        <v>-1.58</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19528,7 +19531,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>162.91</v>
+        <v>161.77</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19540,13 +19543,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>299.88</v>
+        <v>228.06</v>
       </c>
       <c r="Q326">
-        <v>299.88</v>
+        <v>228.06</v>
       </c>
       <c r="R326">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19578,7 +19581,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1892</v>
+        <v>1869</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19590,13 +19593,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>358.5</v>
+        <v>243.5</v>
       </c>
       <c r="Q327">
-        <v>358.5</v>
+        <v>243.5</v>
       </c>
       <c r="R327">
-        <v>3.94</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19610,7 +19613,7 @@
         <v>253</v>
       </c>
       <c r="D328" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19622,7 +19625,7 @@
         <v>9</v>
       </c>
       <c r="H328">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I328">
         <v>9693</v>
@@ -19630,23 +19633,29 @@
       <c r="J328">
         <v>1038.5</v>
       </c>
+      <c r="K328" t="s">
+        <v>274</v>
+      </c>
       <c r="L328">
         <v>1023.15</v>
       </c>
       <c r="M328">
-        <v>0</v>
+        <v>1023.15</v>
+      </c>
+      <c r="N328" t="s">
+        <v>275</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>-484.6500000000002</v>
       </c>
       <c r="P328">
-        <v>-346.5</v>
+        <v>0</v>
       </c>
       <c r="Q328">
-        <v>-346.5</v>
+        <v>-484.6500000000002</v>
       </c>
       <c r="R328">
-        <v>-3.57</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -19663,7 +19672,7 @@
         <v>257</v>
       </c>
       <c r="E329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329">
         <v>315.25</v>
@@ -19678,10 +19687,10 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>335.9</v>
+        <v>342</v>
       </c>
       <c r="L329">
-        <v>299.49</v>
+        <v>315.25</v>
       </c>
       <c r="M329">
         <v>0</v>
@@ -19690,13 +19699,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>640.15</v>
+        <v>829.25</v>
       </c>
       <c r="Q329">
-        <v>640.15</v>
+        <v>829.25</v>
       </c>
       <c r="R329">
-        <v>6.55</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19728,7 +19737,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4875</v>
+        <v>4928.5</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19740,13 +19749,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="Q330">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="R330">
-        <v>0.39</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19778,7 +19787,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19790,13 +19799,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-63</v>
+        <v>-176.4</v>
       </c>
       <c r="Q331">
-        <v>-63</v>
+        <v>-176.4</v>
       </c>
       <c r="R331">
-        <v>-0.66</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19828,7 +19837,7 @@
         <v>9059.200000000001</v>
       </c>
       <c r="J332">
-        <v>1103.1</v>
+        <v>1088.9</v>
       </c>
       <c r="L332">
         <v>1075.78</v>
@@ -19840,13 +19849,13 @@
         <v>0</v>
       </c>
       <c r="P332">
-        <v>-234.4</v>
+        <v>-348</v>
       </c>
       <c r="Q332">
-        <v>-234.4</v>
+        <v>-348</v>
       </c>
       <c r="R332">
-        <v>-2.59</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19878,7 +19887,7 @@
         <v>9000</v>
       </c>
       <c r="J333">
-        <v>1764</v>
+        <v>1759.1</v>
       </c>
       <c r="L333">
         <v>1710</v>
@@ -19890,13 +19899,13 @@
         <v>0</v>
       </c>
       <c r="P333">
-        <v>-180</v>
+        <v>-204.5</v>
       </c>
       <c r="Q333">
-        <v>-180</v>
+        <v>-204.5</v>
       </c>
       <c r="R333">
-        <v>-2</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -19925,10 +19934,10 @@
         <v>6</v>
       </c>
       <c r="I334">
-        <v>9054.599999999999</v>
+        <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1509.1</v>
+        <v>1480</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -19940,13 +19949,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>-174.6</v>
       </c>
       <c r="Q334">
-        <v>0</v>
+        <v>-174.6</v>
       </c>
       <c r="R334">
-        <v>0</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -19978,7 +19987,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>5023</v>
+        <v>4918</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -19990,13 +19999,13 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="Q335">
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="R335">
-        <v>0</v>
+        <v>-2.09</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="282">
   <si>
     <t>Buy Date</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1220,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S335"/>
+  <dimension ref="A1:S337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1297,13 +1300,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1333,7 +1336,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1353,13 +1356,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1389,7 +1392,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1412,13 +1415,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1448,7 +1451,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1468,13 +1471,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1504,7 +1507,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1524,13 +1527,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1560,7 +1563,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1580,13 +1583,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1616,7 +1619,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1636,13 +1639,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1672,7 +1675,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1692,13 +1695,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1728,7 +1731,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1748,13 +1751,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1784,7 +1787,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1804,13 +1807,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1831,7 +1834,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1840,7 +1843,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1855,7 +1858,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1863,13 +1866,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1899,7 +1902,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1922,13 +1925,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1958,7 +1961,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1978,13 +1981,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2014,7 +2017,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2034,13 +2037,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2070,7 +2073,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2090,13 +2093,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2126,7 +2129,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2146,13 +2149,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2182,7 +2185,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2202,13 +2205,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2238,7 +2241,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2258,13 +2261,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2294,7 +2297,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2314,13 +2317,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2350,7 +2353,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2370,13 +2373,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2397,7 +2400,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2406,7 +2409,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2426,13 +2429,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2453,7 +2456,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2462,7 +2465,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2482,13 +2485,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2518,7 +2521,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2538,13 +2541,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2574,7 +2577,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2594,13 +2597,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2630,7 +2633,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2650,13 +2653,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2677,7 +2680,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2686,7 +2689,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2706,13 +2709,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2742,7 +2745,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2762,13 +2765,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2798,7 +2801,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2818,13 +2821,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2854,7 +2857,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2874,13 +2877,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2910,7 +2913,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2930,13 +2933,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2957,7 +2960,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2966,7 +2969,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2986,13 +2989,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3022,7 +3025,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3042,13 +3045,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3078,7 +3081,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3098,13 +3101,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3125,7 +3128,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3134,7 +3137,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3154,13 +3157,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3181,7 +3184,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3190,7 +3193,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3210,13 +3213,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3246,7 +3249,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3266,13 +3269,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3302,7 +3305,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3322,13 +3325,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3358,7 +3361,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3381,13 +3384,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3417,7 +3420,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3437,13 +3440,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3473,7 +3476,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3493,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3529,7 +3532,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3549,13 +3552,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3576,7 +3579,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3585,7 +3588,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3605,13 +3608,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3632,7 +3635,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3641,7 +3644,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3661,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3697,7 +3700,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3717,13 +3720,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3753,7 +3756,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3773,13 +3776,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3809,7 +3812,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3832,13 +3835,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3868,7 +3871,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3888,13 +3891,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3924,7 +3927,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3944,13 +3947,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3980,7 +3983,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4003,13 +4006,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4039,7 +4042,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4059,13 +4062,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4095,7 +4098,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4115,13 +4118,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C52" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D52" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4151,7 +4154,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4174,13 +4177,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4210,7 +4213,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4230,13 +4233,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4266,7 +4269,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4289,13 +4292,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4325,7 +4328,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4348,13 +4351,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4384,7 +4387,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4404,13 +4407,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4431,7 +4434,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4440,7 +4443,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4460,13 +4463,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4496,7 +4499,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4516,13 +4519,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4552,7 +4555,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4575,13 +4578,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4611,7 +4614,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4631,13 +4634,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D61" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4667,7 +4670,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4690,13 +4693,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4726,7 +4729,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4741,7 +4744,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4749,13 +4752,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4785,7 +4788,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4805,13 +4808,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C64" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4841,7 +4844,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4861,13 +4864,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D65" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4897,7 +4900,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4917,13 +4920,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4953,7 +4956,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4973,13 +4976,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5009,7 +5012,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5029,13 +5032,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5065,7 +5068,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5085,13 +5088,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5112,7 +5115,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5121,7 +5124,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5141,13 +5144,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5177,7 +5180,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5197,13 +5200,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5233,7 +5236,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5253,13 +5256,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C72" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5289,7 +5292,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5309,13 +5312,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D73" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5345,7 +5348,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5365,13 +5368,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5401,7 +5404,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5421,13 +5424,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5457,7 +5460,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5477,13 +5480,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5513,7 +5516,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5533,13 +5536,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5569,7 +5572,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5589,13 +5592,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D78" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5625,7 +5628,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5645,13 +5648,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5681,7 +5684,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5701,13 +5704,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5737,7 +5740,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5757,13 +5760,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5793,7 +5796,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5813,13 +5816,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D82" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5849,7 +5852,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5872,13 +5875,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5908,7 +5911,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5928,13 +5931,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C84" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5964,7 +5967,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5984,13 +5987,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6020,7 +6023,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6040,13 +6043,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6076,7 +6079,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6096,13 +6099,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6132,7 +6135,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6152,13 +6155,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6188,7 +6191,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6208,13 +6211,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6244,7 +6247,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6264,13 +6267,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6300,7 +6303,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6320,13 +6323,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6356,7 +6359,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6379,13 +6382,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6415,7 +6418,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6435,13 +6438,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6471,7 +6474,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6491,13 +6494,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6527,7 +6530,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6547,13 +6550,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6583,7 +6586,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6603,13 +6606,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6639,7 +6642,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6659,13 +6662,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C97" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D97" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6695,7 +6698,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6715,13 +6718,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C98" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6751,7 +6754,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6774,13 +6777,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6810,7 +6813,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6830,13 +6833,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6866,7 +6869,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6886,13 +6889,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6922,7 +6925,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6942,13 +6945,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6978,7 +6981,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6998,13 +7001,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D103" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7034,7 +7037,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7054,13 +7057,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D104" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7090,7 +7093,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7110,13 +7113,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7146,7 +7149,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7166,13 +7169,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7193,7 +7196,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7202,7 +7205,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7222,13 +7225,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7258,7 +7261,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7278,13 +7281,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C108" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7314,7 +7317,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7334,13 +7337,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C109" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7361,7 +7364,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7370,7 +7373,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7390,13 +7393,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7426,7 +7429,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7446,13 +7449,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7482,7 +7485,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7502,13 +7505,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C112" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D112" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7538,7 +7541,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7558,13 +7561,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D113" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7594,7 +7597,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7614,13 +7617,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C114" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7650,7 +7653,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7670,13 +7673,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D115" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7706,7 +7709,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7726,13 +7729,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7762,7 +7765,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7782,13 +7785,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7818,7 +7821,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7838,13 +7841,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C118" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7874,7 +7877,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7897,13 +7900,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C119" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D119" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7933,7 +7936,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7953,13 +7956,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D120" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7989,7 +7992,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8009,13 +8012,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C121" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8045,7 +8048,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8065,13 +8068,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D122" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8101,7 +8104,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8121,13 +8124,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8148,7 +8151,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8157,7 +8160,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8177,13 +8180,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8213,7 +8216,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8233,13 +8236,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C125" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D125" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8269,7 +8272,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8289,13 +8292,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C126" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8325,7 +8328,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8348,13 +8351,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8384,7 +8387,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8404,13 +8407,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8440,7 +8443,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8463,13 +8466,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C129" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8499,7 +8502,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8519,13 +8522,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C130" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8555,7 +8558,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8575,13 +8578,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C131" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8611,7 +8614,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8631,13 +8634,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D132" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8667,7 +8670,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8687,13 +8690,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C133" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8714,7 +8717,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8723,7 +8726,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8743,13 +8746,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D134" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8779,7 +8782,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8799,13 +8802,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8835,7 +8838,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8855,13 +8858,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C136" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D136" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8891,7 +8894,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8911,13 +8914,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D137" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8947,7 +8950,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8970,13 +8973,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C138" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9006,7 +9009,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9026,13 +9029,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9062,7 +9065,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9082,13 +9085,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C140" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9118,7 +9121,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9138,13 +9141,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C141" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D141" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9174,7 +9177,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9194,13 +9197,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C142" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D142" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9230,7 +9233,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9250,13 +9253,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C143" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9286,7 +9289,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9306,13 +9309,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C144" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D144" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9342,7 +9345,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9362,13 +9365,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D145" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9398,7 +9401,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9418,13 +9421,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D146" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9454,7 +9457,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9477,13 +9480,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C147" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D147" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9513,7 +9516,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9536,13 +9539,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C148" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D148" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9572,7 +9575,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9595,13 +9598,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C149" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9622,7 +9625,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9631,7 +9634,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9654,13 +9657,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D150" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9690,7 +9693,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9713,13 +9716,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9749,7 +9752,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9769,13 +9772,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C152" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9805,7 +9808,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9828,13 +9831,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C153" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D153" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9864,7 +9867,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9887,13 +9890,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C154" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D154" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9923,7 +9926,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9938,7 +9941,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9946,13 +9949,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C155" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9982,7 +9985,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10005,13 +10008,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C156" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D156" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10041,7 +10044,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10061,13 +10064,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C157" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D157" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10097,7 +10100,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10117,13 +10120,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C158" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D158" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10153,7 +10156,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10173,13 +10176,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C159" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D159" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10209,7 +10212,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10232,13 +10235,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C160" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D160" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10268,7 +10271,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10288,13 +10291,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D161" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10324,7 +10327,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10347,13 +10350,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C162" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D162" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10383,7 +10386,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10403,13 +10406,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C163" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D163" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10439,7 +10442,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10462,13 +10465,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C164" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10489,7 +10492,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10498,7 +10501,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10521,13 +10524,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10548,7 +10551,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10557,7 +10560,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10577,13 +10580,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C166" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D166" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10613,7 +10616,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10636,13 +10639,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D167" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10672,7 +10675,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10692,13 +10695,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C168" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D168" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10728,7 +10731,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10748,13 +10751,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C169" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D169" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10784,7 +10787,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10807,13 +10810,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C170" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D170" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10843,7 +10846,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10866,13 +10869,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C171" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D171" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10902,7 +10905,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10922,13 +10925,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D172" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10958,7 +10961,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10981,13 +10984,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C173" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D173" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11017,7 +11020,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11037,13 +11040,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C174" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D174" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11073,7 +11076,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11096,13 +11099,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C175" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D175" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11132,7 +11135,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11152,13 +11155,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C176" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D176" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11188,7 +11191,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11208,13 +11211,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D177" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11244,7 +11247,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11267,13 +11270,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C178" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D178" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11294,7 +11297,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11303,7 +11306,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11323,13 +11326,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C179" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D179" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11359,7 +11362,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11379,13 +11382,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C180" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D180" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11415,7 +11418,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11435,13 +11438,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D181" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11471,7 +11474,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11491,13 +11494,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C182" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D182" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11527,7 +11530,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11550,13 +11553,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C183" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D183" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11586,7 +11589,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11606,13 +11609,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C184" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D184" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11642,7 +11645,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11665,13 +11668,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C185" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D185" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11701,7 +11704,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11721,13 +11724,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C186" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D186" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11748,7 +11751,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11757,7 +11760,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11777,13 +11780,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C187" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D187" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11804,7 +11807,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11813,7 +11816,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11836,13 +11839,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C188" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D188" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11863,7 +11866,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11872,7 +11875,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11892,13 +11895,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C189" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D189" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11928,7 +11931,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11948,13 +11951,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C190" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D190" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11984,7 +11987,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12004,13 +12007,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C191" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D191" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12031,7 +12034,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12040,7 +12043,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12055,7 +12058,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12063,13 +12066,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C192" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D192" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12099,7 +12102,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12119,13 +12122,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C193" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D193" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12155,7 +12158,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12175,13 +12178,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C194" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D194" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12202,7 +12205,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12211,7 +12214,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12231,13 +12234,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C195" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D195" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12267,7 +12270,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12282,7 +12285,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12290,13 +12293,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C196" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D196" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12326,7 +12329,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12349,13 +12352,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C197" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D197" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12376,7 +12379,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12385,7 +12388,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12405,13 +12408,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C198" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D198" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12441,7 +12444,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12461,13 +12464,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C199" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D199" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12497,7 +12500,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12517,13 +12520,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C200" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D200" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12553,7 +12556,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12573,13 +12576,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C201" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D201" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12609,7 +12612,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12629,13 +12632,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C202" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D202" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12665,7 +12668,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12685,13 +12688,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C203" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D203" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12721,7 +12724,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12736,7 +12739,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12744,13 +12747,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C204" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D204" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12780,7 +12783,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12800,13 +12803,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C205" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D205" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12836,7 +12839,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12856,13 +12859,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C206" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D206" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12892,7 +12895,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12912,13 +12915,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C207" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D207" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12948,7 +12951,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12971,13 +12974,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C208" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D208" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13007,7 +13010,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13027,13 +13030,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C209" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D209" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13063,7 +13066,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13083,13 +13086,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C210" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D210" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13110,7 +13113,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13119,7 +13122,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13139,13 +13142,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C211" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D211" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13175,7 +13178,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13195,13 +13198,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C212" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D212" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13231,7 +13234,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13251,13 +13254,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C213" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D213" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13287,7 +13290,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13307,13 +13310,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C214" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D214" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13343,7 +13346,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13358,7 +13361,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13366,13 +13369,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C215" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D215" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13402,7 +13405,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13422,13 +13425,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C216" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D216" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13458,7 +13461,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13478,13 +13481,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C217" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D217" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13514,7 +13517,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13534,13 +13537,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C218" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D218" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13570,7 +13573,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13590,13 +13593,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C219" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D219" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13626,7 +13629,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13646,13 +13649,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D220" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13673,7 +13676,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13682,7 +13685,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13702,13 +13705,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C221" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D221" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13729,7 +13732,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13738,7 +13741,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13758,13 +13761,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C222" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D222" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13794,7 +13797,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13814,13 +13817,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C223" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D223" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13841,7 +13844,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13850,7 +13853,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13870,13 +13873,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C224" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D224" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13906,7 +13909,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13926,13 +13929,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C225" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D225" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13962,7 +13965,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13982,13 +13985,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C226" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D226" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14018,7 +14021,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14038,13 +14041,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C227" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14074,7 +14077,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14094,13 +14097,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C228" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D228" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14130,7 +14133,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14150,13 +14153,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D229" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14174,7 +14177,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8835.5</v>
+        <v>9069</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14186,13 +14189,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>545</v>
+        <v>778.5</v>
       </c>
       <c r="Q229">
-        <v>545</v>
+        <v>778.5</v>
       </c>
       <c r="R229">
-        <v>6.57</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14200,13 +14203,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D230" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14236,7 +14239,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14256,13 +14259,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C231" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D231" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14283,7 +14286,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14292,7 +14295,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14307,7 +14310,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14315,13 +14318,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C232" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D232" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14351,7 +14354,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14371,13 +14374,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C233" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D233" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14407,7 +14410,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14427,13 +14430,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C234" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D234" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14463,7 +14466,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14483,13 +14486,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C235" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D235" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14510,7 +14513,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14519,7 +14522,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14542,13 +14545,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C236" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D236" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14569,7 +14572,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14578,7 +14581,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14601,13 +14604,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C237" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D237" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14637,7 +14640,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14657,13 +14660,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C238" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D238" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14693,7 +14696,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14713,13 +14716,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C239" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D239" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14749,7 +14752,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14769,13 +14772,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D240" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14805,7 +14808,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14825,13 +14828,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C241" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D241" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14861,7 +14864,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14881,13 +14884,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C242" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D242" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14917,7 +14920,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14937,13 +14940,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C243" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D243" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14973,7 +14976,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14996,13 +14999,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C244" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D244" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15032,7 +15035,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15047,7 +15050,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15055,13 +15058,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C245" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D245" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15082,7 +15085,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15091,7 +15094,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15111,13 +15114,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C246" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D246" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15147,7 +15150,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15167,13 +15170,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C247" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D247" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15203,7 +15206,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15223,13 +15226,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C248" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D248" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15259,7 +15262,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15279,13 +15282,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C249" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D249" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15315,7 +15318,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15335,13 +15338,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C250" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D250" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15371,7 +15374,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15391,13 +15394,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C251" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D251" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15427,7 +15430,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15447,13 +15450,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C252" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D252" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15483,7 +15486,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15506,13 +15509,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C253" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15542,7 +15545,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15562,13 +15565,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C254" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15586,7 +15589,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15598,13 +15601,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>408.8</v>
+        <v>513.1</v>
       </c>
       <c r="Q254">
-        <v>408.8</v>
+        <v>513.1</v>
       </c>
       <c r="R254">
-        <v>4.13</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15612,13 +15615,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C255" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D255" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15648,7 +15651,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15668,13 +15671,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C256" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D256" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15704,7 +15707,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15724,13 +15727,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C257" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D257" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15751,7 +15754,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15760,7 +15763,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15780,13 +15783,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D258" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15816,7 +15819,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15836,13 +15839,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C259" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D259" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15872,7 +15875,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15895,13 +15898,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C260" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D260" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15919,7 +15922,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15931,13 +15934,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-248.5</v>
+        <v>-195.3</v>
       </c>
       <c r="Q260">
-        <v>-248.5</v>
+        <v>-195.3</v>
       </c>
       <c r="R260">
-        <v>-2.78</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15945,13 +15948,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C261" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D261" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15969,7 +15972,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1339.6</v>
+        <v>1340</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15981,13 +15984,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-287</v>
+        <v>-284.2</v>
       </c>
       <c r="Q261">
-        <v>-287</v>
+        <v>-284.2</v>
       </c>
       <c r="R261">
-        <v>-2.97</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15995,13 +15998,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C262" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D262" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16031,7 +16034,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16054,13 +16057,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C263" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D263" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16090,7 +16093,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16110,13 +16113,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C264" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D264" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16146,7 +16149,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16169,13 +16172,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C265" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D265" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16205,7 +16208,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16228,13 +16231,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C266" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D266" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16264,7 +16267,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16284,13 +16287,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C267" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D267" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16320,7 +16323,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16340,13 +16343,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C268" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D268" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16376,7 +16379,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16396,13 +16399,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C269" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D269" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16432,7 +16435,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16452,13 +16455,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C270" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D270" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16488,7 +16491,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16508,13 +16511,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C271" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D271" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16532,7 +16535,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1572.7</v>
+        <v>1588.1</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16544,13 +16547,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-111.6</v>
+        <v>-19.2</v>
       </c>
       <c r="Q271">
-        <v>-111.6</v>
+        <v>-19.2</v>
       </c>
       <c r="R271">
-        <v>-1.17</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16558,13 +16561,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C272" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D272" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16594,7 +16597,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16614,13 +16617,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C273" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D273" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16650,7 +16653,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16670,13 +16673,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C274" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D274" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16697,7 +16700,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16706,7 +16709,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16726,13 +16729,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C275" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D275" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16762,7 +16765,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16782,13 +16785,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C276" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D276" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16818,7 +16821,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16838,13 +16841,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C277" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D277" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16874,7 +16877,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16894,13 +16897,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C278" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D278" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16930,7 +16933,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16950,13 +16953,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C279" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D279" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16986,7 +16989,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17006,13 +17009,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C280" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D280" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17042,7 +17045,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17062,13 +17065,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C281" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D281" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17098,7 +17101,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17118,13 +17121,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C282" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D282" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17154,7 +17157,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17174,13 +17177,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C283" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D283" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17210,7 +17213,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17230,13 +17233,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C284" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D284" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17266,7 +17269,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17286,13 +17289,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C285" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D285" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17322,7 +17325,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17342,13 +17345,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C286" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D286" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17378,7 +17381,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17398,13 +17401,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C287" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D287" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17434,7 +17437,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17454,13 +17457,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C288" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D288" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17490,7 +17493,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17510,13 +17513,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C289" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D289" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17537,7 +17540,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17546,7 +17549,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17566,13 +17569,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C290" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D290" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17602,7 +17605,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17622,13 +17625,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C291" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D291" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17646,7 +17649,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>559.9</v>
+        <v>553.15</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17658,13 +17661,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-120.7</v>
+        <v>-235.45</v>
       </c>
       <c r="Q291">
-        <v>-120.7</v>
+        <v>-235.45</v>
       </c>
       <c r="R291">
-        <v>-1.25</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17672,13 +17675,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C292" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D292" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17699,7 +17702,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17708,7 +17711,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17728,13 +17731,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C293" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D293" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17764,7 +17767,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17784,13 +17787,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C294" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D294" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17820,7 +17823,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17843,13 +17846,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C295" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D295" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17879,7 +17882,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17899,13 +17902,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C296" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D296" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17935,7 +17938,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17955,13 +17958,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C297" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D297" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17979,7 +17982,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>117</v>
+        <v>118.3</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17991,13 +17994,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>42.5</v>
+        <v>153</v>
       </c>
       <c r="Q297">
-        <v>42.5</v>
+        <v>153</v>
       </c>
       <c r="R297">
-        <v>0.43</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18005,13 +18008,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C298" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D298" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18041,7 +18044,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18061,13 +18064,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C299" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D299" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18097,7 +18100,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18117,13 +18120,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C300" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D300" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18153,7 +18156,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18173,13 +18176,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C301" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D301" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18209,7 +18212,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18229,13 +18232,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C302" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D302" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18265,7 +18268,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18285,13 +18288,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C303" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D303" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18312,7 +18315,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18321,7 +18324,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18341,13 +18344,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C304" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D304" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18377,7 +18380,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18397,13 +18400,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C305" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D305" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18433,7 +18436,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18453,13 +18456,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C306" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D306" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18489,7 +18492,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18509,13 +18512,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C307" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D307" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18545,7 +18548,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18565,13 +18568,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C308" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D308" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18601,7 +18604,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18621,13 +18624,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C309" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D309" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18648,7 +18651,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18657,7 +18660,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18677,13 +18680,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C310" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D310" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18713,7 +18716,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18733,13 +18736,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C311" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D311" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18769,7 +18772,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18789,13 +18792,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C312" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D312" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18825,7 +18828,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18845,13 +18848,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C313" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D313" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18881,7 +18884,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18901,13 +18904,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C314" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D314" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18925,7 +18928,7 @@
         <v>9503.1</v>
       </c>
       <c r="J314">
-        <v>1008.8</v>
+        <v>1043.2</v>
       </c>
       <c r="L314">
         <v>1003.11</v>
@@ -18937,13 +18940,13 @@
         <v>0</v>
       </c>
       <c r="P314">
-        <v>-423.9</v>
+        <v>-114.3</v>
       </c>
       <c r="Q314">
-        <v>-423.9</v>
+        <v>-114.3</v>
       </c>
       <c r="R314">
-        <v>-4.46</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18951,13 +18954,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C315" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D315" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18975,7 +18978,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4800</v>
+        <v>4836</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18987,13 +18990,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>68.8</v>
+        <v>140.8</v>
       </c>
       <c r="Q315">
-        <v>68.8</v>
+        <v>140.8</v>
       </c>
       <c r="R315">
-        <v>0.72</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19001,13 +19004,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C316" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D316" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19025,7 +19028,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2997</v>
+        <v>2993.2</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19037,13 +19040,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>177</v>
+        <v>165.6</v>
       </c>
       <c r="Q316">
-        <v>177</v>
+        <v>165.6</v>
       </c>
       <c r="R316">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19051,13 +19054,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C317" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D317" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19075,7 +19078,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>307.1</v>
+        <v>311.5</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19087,13 +19090,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-359.6</v>
+        <v>-223.2</v>
       </c>
       <c r="Q317">
-        <v>-359.6</v>
+        <v>-223.2</v>
       </c>
       <c r="R317">
-        <v>-3.64</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19101,13 +19104,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C318" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D318" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19128,7 +19131,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19137,7 +19140,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19157,13 +19160,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C319" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D319" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19181,7 +19184,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1211</v>
+        <v>1211.2</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19193,13 +19196,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>534.4</v>
+        <v>536</v>
       </c>
       <c r="Q319">
-        <v>534.4</v>
+        <v>536</v>
       </c>
       <c r="R319">
-        <v>5.84</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19207,13 +19210,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C320" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D320" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19231,7 +19234,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>412.65</v>
+        <v>413.25</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19243,13 +19246,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-151.8</v>
+        <v>-138</v>
       </c>
       <c r="Q320">
-        <v>-151.8</v>
+        <v>-138</v>
       </c>
       <c r="R320">
-        <v>-1.57</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19257,13 +19260,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C321" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D321" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19281,7 +19284,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19293,13 +19296,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-111.3</v>
+        <v>-138</v>
       </c>
       <c r="Q321">
-        <v>-111.3</v>
+        <v>-138</v>
       </c>
       <c r="R321">
-        <v>-1.32</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19307,13 +19310,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C322" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D322" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19331,7 +19334,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1795</v>
+        <v>1807.3</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19343,13 +19346,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>100</v>
+        <v>161.5</v>
       </c>
       <c r="Q322">
-        <v>100</v>
+        <v>161.5</v>
       </c>
       <c r="R322">
-        <v>1.13</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19357,13 +19360,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C323" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D323" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19381,7 +19384,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1270.4</v>
+        <v>1256.7</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19393,13 +19396,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>324.8</v>
+        <v>215.2</v>
       </c>
       <c r="Q323">
-        <v>324.8</v>
+        <v>215.2</v>
       </c>
       <c r="R323">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19407,13 +19410,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C324" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D324" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19431,7 +19434,7 @@
         <v>9891</v>
       </c>
       <c r="J324">
-        <v>486.65</v>
+        <v>484.5</v>
       </c>
       <c r="L324">
         <v>447.45</v>
@@ -19443,13 +19446,13 @@
         <v>0</v>
       </c>
       <c r="P324">
-        <v>328.65</v>
+        <v>283.5</v>
       </c>
       <c r="Q324">
-        <v>328.65</v>
+        <v>283.5</v>
       </c>
       <c r="R324">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19457,13 +19460,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C325" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D325" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19481,7 +19484,7 @@
         <v>9492.299999999999</v>
       </c>
       <c r="J325">
-        <v>1036.4</v>
+        <v>1053</v>
       </c>
       <c r="L325">
         <v>1001.97</v>
@@ -19493,13 +19496,13 @@
         <v>0</v>
       </c>
       <c r="P325">
-        <v>-164.7</v>
+        <v>-15.3</v>
       </c>
       <c r="Q325">
-        <v>-164.7</v>
+        <v>-15.3</v>
       </c>
       <c r="R325">
-        <v>-1.74</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19507,13 +19510,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C326" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D326" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19531,7 +19534,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>161.77</v>
+        <v>164.4</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19543,13 +19546,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>228.06</v>
+        <v>393.75</v>
       </c>
       <c r="Q326">
-        <v>228.06</v>
+        <v>393.75</v>
       </c>
       <c r="R326">
-        <v>2.29</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19557,13 +19560,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C327" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D327" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19581,7 +19584,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1869</v>
+        <v>1886.7</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19593,13 +19596,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>243.5</v>
+        <v>332</v>
       </c>
       <c r="Q327">
-        <v>243.5</v>
+        <v>332</v>
       </c>
       <c r="R327">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19607,13 +19610,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C328" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D328" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19634,7 +19637,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19643,7 +19646,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19663,13 +19666,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C329" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D329" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -19687,7 +19690,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>342</v>
+        <v>342.65</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19699,13 +19702,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>829.25</v>
+        <v>849.4</v>
       </c>
       <c r="Q329">
-        <v>829.25</v>
+        <v>849.4</v>
       </c>
       <c r="R329">
-        <v>8.49</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19713,13 +19716,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C330" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D330" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19737,7 +19740,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19749,13 +19752,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="Q330">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="R330">
-        <v>1.49</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19763,13 +19766,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C331" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D331" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19787,7 +19790,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3128.2</v>
+        <v>3188.5</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19799,13 +19802,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-176.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q331">
-        <v>-176.4</v>
+        <v>4.5</v>
       </c>
       <c r="R331">
-        <v>-1.84</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19813,13 +19816,13 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C332" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D332" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -19837,7 +19840,7 @@
         <v>9059.200000000001</v>
       </c>
       <c r="J332">
-        <v>1088.9</v>
+        <v>1096.5</v>
       </c>
       <c r="L332">
         <v>1075.78</v>
@@ -19849,13 +19852,13 @@
         <v>0</v>
       </c>
       <c r="P332">
-        <v>-348</v>
+        <v>-287.2</v>
       </c>
       <c r="Q332">
-        <v>-348</v>
+        <v>-287.2</v>
       </c>
       <c r="R332">
-        <v>-3.84</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19863,13 +19866,13 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C333" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D333" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -19887,7 +19890,7 @@
         <v>9000</v>
       </c>
       <c r="J333">
-        <v>1759.1</v>
+        <v>1774</v>
       </c>
       <c r="L333">
         <v>1710</v>
@@ -19899,13 +19902,13 @@
         <v>0</v>
       </c>
       <c r="P333">
-        <v>-204.5</v>
+        <v>-130</v>
       </c>
       <c r="Q333">
-        <v>-204.5</v>
+        <v>-130</v>
       </c>
       <c r="R333">
-        <v>-2.27</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -19913,13 +19916,13 @@
         <v>161</v>
       </c>
       <c r="B334" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C334" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D334" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -19937,7 +19940,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1480</v>
+        <v>1500.6</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -19949,13 +19952,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>-174.6</v>
+        <v>-51</v>
       </c>
       <c r="Q334">
-        <v>-174.6</v>
+        <v>-51</v>
       </c>
       <c r="R334">
-        <v>-1.93</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -19963,13 +19966,13 @@
         <v>161</v>
       </c>
       <c r="B335" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C335" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D335" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -19987,7 +19990,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>4918</v>
+        <v>4929</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -19999,13 +20002,113 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>-105</v>
+        <v>-94</v>
       </c>
       <c r="Q335">
-        <v>-105</v>
+        <v>-94</v>
       </c>
       <c r="R335">
-        <v>-2.09</v>
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18">
+      <c r="A336" t="s">
+        <v>162</v>
+      </c>
+      <c r="B336" t="s">
+        <v>216</v>
+      </c>
+      <c r="C336" t="s">
+        <v>254</v>
+      </c>
+      <c r="D336" t="s">
+        <v>258</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>459.75</v>
+      </c>
+      <c r="G336">
+        <v>21</v>
+      </c>
+      <c r="H336">
+        <v>21</v>
+      </c>
+      <c r="I336">
+        <v>9654.75</v>
+      </c>
+      <c r="J336">
+        <v>459.75</v>
+      </c>
+      <c r="L336">
+        <v>436.76</v>
+      </c>
+      <c r="M336">
+        <v>0</v>
+      </c>
+      <c r="O336">
+        <v>0</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>0</v>
+      </c>
+      <c r="R336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18">
+      <c r="A337" t="s">
+        <v>162</v>
+      </c>
+      <c r="B337" t="s">
+        <v>186</v>
+      </c>
+      <c r="C337" t="s">
+        <v>256</v>
+      </c>
+      <c r="D337" t="s">
+        <v>258</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>1175.3</v>
+      </c>
+      <c r="G337">
+        <v>8</v>
+      </c>
+      <c r="H337">
+        <v>8</v>
+      </c>
+      <c r="I337">
+        <v>9402.4</v>
+      </c>
+      <c r="J337">
+        <v>1175.3</v>
+      </c>
+      <c r="L337">
+        <v>1116.53</v>
+      </c>
+      <c r="M337">
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="283">
   <si>
     <t>Buy Date</t>
   </si>
@@ -503,6 +503,9 @@
   </si>
   <si>
     <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1223,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S337"/>
+  <dimension ref="A1:S338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1300,13 +1303,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1336,7 +1339,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1356,13 +1359,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1392,7 +1395,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1415,13 +1418,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1451,7 +1454,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1471,13 +1474,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1507,7 +1510,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1527,13 +1530,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1563,7 +1566,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1583,13 +1586,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1619,7 +1622,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1639,13 +1642,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1675,7 +1678,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1695,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1731,7 +1734,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1751,13 +1754,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1787,7 +1790,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1807,13 +1810,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1834,7 +1837,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1843,7 +1846,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1858,7 +1861,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1866,13 +1869,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1902,7 +1905,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1925,13 +1928,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1961,7 +1964,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1981,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2017,7 +2020,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2037,13 +2040,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2073,7 +2076,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2093,13 +2096,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2129,7 +2132,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2149,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2185,7 +2188,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2205,13 +2208,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2241,7 +2244,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2261,13 +2264,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2297,7 +2300,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2317,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2353,7 +2356,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2373,13 +2376,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2400,7 +2403,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2409,7 +2412,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2429,13 +2432,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2456,7 +2459,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2465,7 +2468,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2485,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2521,7 +2524,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2541,13 +2544,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2577,7 +2580,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2597,13 +2600,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2633,7 +2636,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2653,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2680,7 +2683,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2689,7 +2692,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2709,13 +2712,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2745,7 +2748,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2765,13 +2768,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2801,7 +2804,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2821,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2857,7 +2860,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2877,13 +2880,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2913,7 +2916,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2933,13 +2936,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2960,7 +2963,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2969,7 +2972,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2989,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3025,7 +3028,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3045,13 +3048,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3081,7 +3084,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3101,13 +3104,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3128,7 +3131,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3137,7 +3140,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3157,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3184,7 +3187,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3193,7 +3196,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3213,13 +3216,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D36" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3249,7 +3252,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3269,13 +3272,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3305,7 +3308,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3325,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3361,7 +3364,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3384,13 +3387,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3420,7 +3423,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3440,13 +3443,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3476,7 +3479,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3496,13 +3499,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3532,7 +3535,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3552,13 +3555,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D42" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3579,7 +3582,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3588,7 +3591,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3608,13 +3611,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3635,7 +3638,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3644,7 +3647,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3664,13 +3667,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3700,7 +3703,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3720,13 +3723,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3756,7 +3759,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3776,13 +3779,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3812,7 +3815,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3835,13 +3838,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3871,7 +3874,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3891,13 +3894,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3927,7 +3930,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3947,13 +3950,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3983,7 +3986,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4006,13 +4009,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4042,7 +4045,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4062,13 +4065,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D51" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4098,7 +4101,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4118,13 +4121,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C52" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4154,7 +4157,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4177,13 +4180,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4213,7 +4216,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4233,13 +4236,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4269,7 +4272,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4292,13 +4295,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D55" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4328,7 +4331,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4351,13 +4354,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4387,7 +4390,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4407,13 +4410,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4434,7 +4437,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4443,7 +4446,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4463,13 +4466,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4499,7 +4502,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4519,13 +4522,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4555,7 +4558,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4578,13 +4581,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4614,7 +4617,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4634,13 +4637,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4670,7 +4673,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4693,13 +4696,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4729,7 +4732,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4744,7 +4747,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4752,13 +4755,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D63" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4788,7 +4791,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4808,13 +4811,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4844,7 +4847,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4864,13 +4867,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C65" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D65" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4900,7 +4903,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4920,13 +4923,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4956,7 +4959,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4976,13 +4979,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5012,7 +5015,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5032,13 +5035,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5068,7 +5071,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5088,13 +5091,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5115,7 +5118,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5124,7 +5127,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5144,13 +5147,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5180,7 +5183,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5200,13 +5203,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5236,7 +5239,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5256,13 +5259,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D72" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5292,7 +5295,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5312,13 +5315,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C73" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D73" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5348,7 +5351,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5368,13 +5371,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D74" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5404,7 +5407,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5424,13 +5427,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D75" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5460,7 +5463,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5480,13 +5483,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5516,7 +5519,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5536,13 +5539,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5572,7 +5575,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5592,13 +5595,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D78" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5628,7 +5631,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5648,13 +5651,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5684,7 +5687,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5704,13 +5707,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5740,7 +5743,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5760,13 +5763,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5796,7 +5799,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5816,13 +5819,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5852,7 +5855,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5875,13 +5878,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5911,7 +5914,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5931,13 +5934,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5967,7 +5970,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5987,13 +5990,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6023,7 +6026,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6043,13 +6046,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6079,7 +6082,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6099,13 +6102,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D87" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6135,7 +6138,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6155,13 +6158,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6191,7 +6194,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6211,13 +6214,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6247,7 +6250,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6267,13 +6270,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6303,7 +6306,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6323,13 +6326,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6359,7 +6362,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6382,13 +6385,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6418,7 +6421,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6438,13 +6441,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6474,7 +6477,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6494,13 +6497,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6530,7 +6533,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6550,13 +6553,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6586,7 +6589,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6606,13 +6609,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6642,7 +6645,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6662,13 +6665,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D97" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6698,7 +6701,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6718,13 +6721,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D98" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6754,7 +6757,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6777,13 +6780,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C99" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6813,7 +6816,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6833,13 +6836,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D100" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6869,7 +6872,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6889,13 +6892,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6925,7 +6928,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6945,13 +6948,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C102" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6981,7 +6984,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7001,13 +7004,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D103" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7037,7 +7040,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7057,13 +7060,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C104" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D104" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7093,7 +7096,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7113,13 +7116,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D105" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7149,7 +7152,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7169,13 +7172,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7196,7 +7199,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7205,7 +7208,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7225,13 +7228,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C107" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D107" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7261,7 +7264,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7281,13 +7284,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D108" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7317,7 +7320,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7337,13 +7340,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C109" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D109" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7364,7 +7367,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7373,7 +7376,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7393,13 +7396,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C110" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7429,7 +7432,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7449,13 +7452,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7485,7 +7488,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7505,13 +7508,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C112" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D112" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7541,7 +7544,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7561,13 +7564,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C113" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D113" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7597,7 +7600,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7617,13 +7620,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C114" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D114" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7653,7 +7656,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7673,13 +7676,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D115" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7709,7 +7712,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7729,13 +7732,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D116" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7765,7 +7768,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7785,13 +7788,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D117" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7821,7 +7824,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7841,13 +7844,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C118" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7877,7 +7880,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7900,13 +7903,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C119" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D119" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7936,7 +7939,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7956,13 +7959,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C120" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D120" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7992,7 +7995,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8012,13 +8015,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C121" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D121" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8048,7 +8051,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8068,13 +8071,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D122" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8104,7 +8107,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8124,13 +8127,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D123" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8151,7 +8154,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8160,7 +8163,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8180,13 +8183,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D124" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8216,7 +8219,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8236,13 +8239,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C125" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8272,7 +8275,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8292,13 +8295,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8328,7 +8331,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8351,13 +8354,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8387,7 +8390,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8407,13 +8410,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8443,7 +8446,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8466,13 +8469,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8502,7 +8505,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8522,13 +8525,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8558,7 +8561,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8578,13 +8581,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C131" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D131" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8614,7 +8617,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8634,13 +8637,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C132" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8670,7 +8673,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8690,13 +8693,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C133" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D133" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8717,7 +8720,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8726,7 +8729,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8746,13 +8749,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C134" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8782,7 +8785,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8802,13 +8805,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D135" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8838,7 +8841,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8858,13 +8861,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C136" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D136" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8894,7 +8897,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8914,13 +8917,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D137" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8950,7 +8953,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8973,13 +8976,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C138" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9009,7 +9012,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9029,13 +9032,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C139" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D139" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9065,7 +9068,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9085,13 +9088,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C140" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D140" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9121,7 +9124,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9141,13 +9144,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C141" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D141" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9177,7 +9180,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9197,13 +9200,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C142" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D142" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9233,7 +9236,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9253,13 +9256,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D143" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9289,7 +9292,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9309,13 +9312,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C144" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D144" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9345,7 +9348,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9365,13 +9368,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C145" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9401,7 +9404,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9421,13 +9424,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C146" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9457,7 +9460,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9480,13 +9483,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C147" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D147" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9516,7 +9519,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9539,13 +9542,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C148" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D148" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9575,7 +9578,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9598,13 +9601,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C149" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D149" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9625,7 +9628,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9634,7 +9637,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9657,13 +9660,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D150" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9693,7 +9696,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9716,13 +9719,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D151" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9752,7 +9755,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9772,13 +9775,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9808,7 +9811,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9831,13 +9834,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C153" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9867,7 +9870,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9890,13 +9893,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D154" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9926,7 +9929,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9941,7 +9944,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9949,13 +9952,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C155" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D155" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9985,7 +9988,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10008,13 +10011,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C156" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D156" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10044,7 +10047,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10064,13 +10067,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C157" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D157" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10100,7 +10103,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10120,13 +10123,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C158" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D158" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10156,7 +10159,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10176,13 +10179,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C159" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D159" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10212,7 +10215,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10235,13 +10238,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D160" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10271,7 +10274,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10291,13 +10294,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C161" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D161" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10327,7 +10330,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10350,13 +10353,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C162" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D162" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10386,7 +10389,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10406,13 +10409,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D163" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10442,7 +10445,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10465,13 +10468,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D164" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10492,7 +10495,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10501,7 +10504,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10524,13 +10527,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10551,7 +10554,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10560,7 +10563,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10580,13 +10583,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C166" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D166" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10616,7 +10619,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10639,13 +10642,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C167" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D167" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10675,7 +10678,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10695,13 +10698,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C168" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D168" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10731,7 +10734,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10751,13 +10754,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C169" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D169" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10787,7 +10790,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10810,13 +10813,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C170" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D170" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10846,7 +10849,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10869,13 +10872,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C171" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D171" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10905,7 +10908,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10925,13 +10928,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C172" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D172" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10961,7 +10964,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10984,13 +10987,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C173" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11020,7 +11023,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11040,13 +11043,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C174" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D174" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11076,7 +11079,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11099,13 +11102,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C175" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D175" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11135,7 +11138,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11155,13 +11158,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C176" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D176" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11191,7 +11194,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11211,13 +11214,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C177" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D177" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11247,7 +11250,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11270,13 +11273,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C178" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D178" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11297,7 +11300,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11306,7 +11309,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11326,13 +11329,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C179" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11362,7 +11365,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11382,13 +11385,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C180" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D180" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11418,7 +11421,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11438,13 +11441,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C181" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D181" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11474,7 +11477,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11494,13 +11497,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C182" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D182" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11530,7 +11533,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11553,13 +11556,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C183" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D183" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11589,7 +11592,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11609,13 +11612,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C184" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D184" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11645,7 +11648,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11668,13 +11671,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C185" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D185" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11704,7 +11707,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11724,13 +11727,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C186" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D186" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11751,7 +11754,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11760,7 +11763,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11780,13 +11783,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C187" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D187" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11807,7 +11810,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11816,7 +11819,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11839,13 +11842,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C188" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D188" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11866,7 +11869,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11875,7 +11878,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11895,13 +11898,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C189" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D189" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11931,7 +11934,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11951,13 +11954,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C190" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D190" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11987,7 +11990,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12007,13 +12010,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C191" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D191" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12034,7 +12037,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12043,7 +12046,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12058,7 +12061,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12066,13 +12069,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C192" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D192" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12102,7 +12105,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12122,13 +12125,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C193" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D193" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12158,7 +12161,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12178,13 +12181,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C194" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D194" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12205,7 +12208,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12214,7 +12217,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12234,13 +12237,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C195" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D195" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12270,7 +12273,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12285,7 +12288,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12293,13 +12296,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C196" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D196" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12329,7 +12332,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12352,13 +12355,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C197" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D197" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12379,7 +12382,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12388,7 +12391,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12408,13 +12411,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C198" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D198" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12444,7 +12447,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12464,13 +12467,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C199" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D199" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12500,7 +12503,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12520,13 +12523,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C200" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D200" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12556,7 +12559,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12576,13 +12579,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C201" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D201" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12612,7 +12615,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12632,13 +12635,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C202" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D202" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12668,7 +12671,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12688,13 +12691,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C203" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D203" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12724,7 +12727,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12739,7 +12742,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12747,13 +12750,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C204" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D204" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12783,7 +12786,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12803,13 +12806,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C205" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D205" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12839,7 +12842,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12859,13 +12862,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C206" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D206" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12895,7 +12898,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12915,13 +12918,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C207" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D207" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12951,7 +12954,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12974,13 +12977,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C208" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D208" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13010,7 +13013,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13030,13 +13033,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C209" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D209" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13066,7 +13069,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13086,13 +13089,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C210" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D210" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13113,7 +13116,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13122,7 +13125,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13142,13 +13145,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C211" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D211" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13178,7 +13181,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13198,13 +13201,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C212" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D212" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13234,7 +13237,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13254,13 +13257,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C213" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D213" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13290,7 +13293,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13310,13 +13313,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C214" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D214" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13346,7 +13349,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13361,7 +13364,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13369,13 +13372,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C215" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D215" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13405,7 +13408,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13425,13 +13428,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C216" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D216" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13461,7 +13464,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13481,13 +13484,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C217" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D217" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13517,7 +13520,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13537,13 +13540,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C218" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D218" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13573,7 +13576,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13593,13 +13596,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C219" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D219" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13629,7 +13632,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13649,13 +13652,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C220" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D220" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13676,7 +13679,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13685,7 +13688,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13705,13 +13708,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D221" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13732,7 +13735,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13741,7 +13744,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13761,13 +13764,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C222" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D222" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13797,7 +13800,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13817,13 +13820,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C223" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D223" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13844,7 +13847,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13853,7 +13856,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13873,13 +13876,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C224" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D224" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13909,7 +13912,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13929,13 +13932,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C225" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D225" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13965,7 +13968,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13985,13 +13988,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C226" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D226" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14021,7 +14024,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14041,13 +14044,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D227" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14077,7 +14080,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14097,13 +14100,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C228" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D228" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14133,7 +14136,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14153,13 +14156,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C229" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D229" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14177,7 +14180,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>9069</v>
+        <v>8888.5</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14189,13 +14192,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>778.5</v>
+        <v>598</v>
       </c>
       <c r="Q229">
-        <v>778.5</v>
+        <v>598</v>
       </c>
       <c r="R229">
-        <v>9.390000000000001</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14203,13 +14206,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C230" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D230" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14239,7 +14242,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14259,13 +14262,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C231" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14286,7 +14289,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14295,7 +14298,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14310,7 +14313,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14318,13 +14321,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C232" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D232" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14354,7 +14357,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14374,13 +14377,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C233" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D233" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14410,7 +14413,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14430,13 +14433,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D234" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14466,7 +14469,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14486,13 +14489,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C235" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D235" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14513,7 +14516,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14522,7 +14525,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14545,13 +14548,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C236" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D236" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14572,7 +14575,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14581,7 +14584,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14604,13 +14607,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C237" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D237" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14640,7 +14643,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14660,13 +14663,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C238" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D238" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14696,7 +14699,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14716,13 +14719,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C239" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D239" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14752,7 +14755,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14772,13 +14775,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C240" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D240" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14808,7 +14811,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14828,13 +14831,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D241" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14864,7 +14867,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14884,13 +14887,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C242" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D242" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14920,7 +14923,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14940,13 +14943,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C243" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D243" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14976,7 +14979,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -14999,13 +15002,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C244" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D244" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15035,7 +15038,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15050,7 +15053,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15058,13 +15061,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C245" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D245" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15085,7 +15088,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15094,7 +15097,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15114,13 +15117,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C246" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D246" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15150,7 +15153,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15170,13 +15173,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C247" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D247" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15206,7 +15209,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15226,13 +15229,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C248" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D248" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15262,7 +15265,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15282,13 +15285,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C249" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D249" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15318,7 +15321,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15338,13 +15341,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C250" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D250" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15374,7 +15377,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15394,13 +15397,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D251" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15430,7 +15433,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15450,13 +15453,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C252" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D252" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15486,7 +15489,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15509,13 +15512,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C253" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D253" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15545,7 +15548,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15565,13 +15568,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C254" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D254" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15589,7 +15592,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15601,13 +15604,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>513.1</v>
+        <v>304.5</v>
       </c>
       <c r="Q254">
-        <v>513.1</v>
+        <v>304.5</v>
       </c>
       <c r="R254">
-        <v>5.18</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15615,13 +15618,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C255" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15651,7 +15654,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15671,13 +15674,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C256" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15707,7 +15710,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15727,13 +15730,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15754,7 +15757,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15763,7 +15766,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15783,13 +15786,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C258" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15819,7 +15822,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15839,13 +15842,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C259" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D259" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15875,7 +15878,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15898,13 +15901,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C260" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D260" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15922,7 +15925,7 @@
         <v>8931.300000000001</v>
       </c>
       <c r="J260">
-        <v>1248</v>
+        <v>1219.2</v>
       </c>
       <c r="L260">
         <v>1212.11</v>
@@ -15934,13 +15937,13 @@
         <v>0</v>
       </c>
       <c r="P260">
-        <v>-195.3</v>
+        <v>-396.9</v>
       </c>
       <c r="Q260">
-        <v>-195.3</v>
+        <v>-396.9</v>
       </c>
       <c r="R260">
-        <v>-2.19</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15948,13 +15951,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C261" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D261" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15972,7 +15975,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1340</v>
+        <v>1334.5</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15984,13 +15987,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-284.2</v>
+        <v>-322.7</v>
       </c>
       <c r="Q261">
-        <v>-284.2</v>
+        <v>-322.7</v>
       </c>
       <c r="R261">
-        <v>-2.94</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -15998,13 +16001,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C262" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D262" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16034,7 +16037,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16057,13 +16060,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C263" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D263" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16093,7 +16096,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16113,13 +16116,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C264" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D264" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16149,7 +16152,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16172,13 +16175,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C265" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D265" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16208,7 +16211,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16231,13 +16234,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C266" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D266" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16267,7 +16270,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16287,13 +16290,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C267" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D267" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16323,7 +16326,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16343,13 +16346,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C268" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D268" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16379,7 +16382,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16399,13 +16402,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C269" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D269" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16435,7 +16438,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16455,13 +16458,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C270" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D270" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16491,7 +16494,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16511,13 +16514,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C271" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D271" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16535,7 +16538,7 @@
         <v>9547.799999999999</v>
       </c>
       <c r="J271">
-        <v>1588.1</v>
+        <v>1522</v>
       </c>
       <c r="L271">
         <v>1511.73</v>
@@ -16547,13 +16550,13 @@
         <v>0</v>
       </c>
       <c r="P271">
-        <v>-19.2</v>
+        <v>-415.8</v>
       </c>
       <c r="Q271">
-        <v>-19.2</v>
+        <v>-415.8</v>
       </c>
       <c r="R271">
-        <v>-0.2</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16561,13 +16564,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C272" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D272" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16597,7 +16600,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16617,13 +16620,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C273" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D273" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16653,7 +16656,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16673,13 +16676,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C274" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D274" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16700,7 +16703,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16709,7 +16712,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16729,13 +16732,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C275" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D275" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16765,7 +16768,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16785,13 +16788,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C276" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D276" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16821,7 +16824,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16841,13 +16844,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C277" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D277" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16877,7 +16880,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16897,13 +16900,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C278" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D278" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16933,7 +16936,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16953,13 +16956,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C279" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D279" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16989,7 +16992,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17009,13 +17012,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C280" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D280" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17045,7 +17048,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17065,13 +17068,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C281" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D281" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17101,7 +17104,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17121,13 +17124,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C282" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D282" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17157,7 +17160,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17177,13 +17180,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C283" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D283" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17213,7 +17216,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17233,13 +17236,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C284" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D284" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17269,7 +17272,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17289,13 +17292,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C285" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D285" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17325,7 +17328,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17345,13 +17348,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C286" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D286" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17381,7 +17384,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17401,13 +17404,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C287" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D287" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17437,7 +17440,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17457,13 +17460,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C288" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D288" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17493,7 +17496,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17513,13 +17516,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C289" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D289" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17540,7 +17543,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17549,7 +17552,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17569,13 +17572,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C290" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D290" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17605,7 +17608,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17625,13 +17628,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C291" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D291" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17649,7 +17652,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>553.15</v>
+        <v>549.6</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17661,13 +17664,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-235.45</v>
+        <v>-295.8</v>
       </c>
       <c r="Q291">
-        <v>-235.45</v>
+        <v>-295.8</v>
       </c>
       <c r="R291">
-        <v>-2.44</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17675,13 +17678,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C292" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D292" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17702,7 +17705,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17711,7 +17714,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17731,13 +17734,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C293" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D293" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17767,7 +17770,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17787,13 +17790,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C294" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D294" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17823,7 +17826,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17846,13 +17849,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C295" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D295" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17882,7 +17885,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17902,13 +17905,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C296" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D296" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17938,7 +17941,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17958,13 +17961,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C297" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D297" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17982,7 +17985,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>118.3</v>
+        <v>117.12</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17994,13 +17997,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>153</v>
+        <v>52.7</v>
       </c>
       <c r="Q297">
-        <v>153</v>
+        <v>52.7</v>
       </c>
       <c r="R297">
-        <v>1.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18008,13 +18011,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C298" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D298" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18044,7 +18047,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18064,13 +18067,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C299" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D299" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18100,7 +18103,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18120,13 +18123,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C300" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D300" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18156,7 +18159,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18176,13 +18179,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C301" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D301" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18212,7 +18215,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18232,13 +18235,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C302" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D302" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18268,7 +18271,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18288,13 +18291,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C303" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D303" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18315,7 +18318,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18324,7 +18327,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18344,13 +18347,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C304" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D304" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18380,7 +18383,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18400,13 +18403,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C305" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D305" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18436,7 +18439,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18456,13 +18459,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C306" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D306" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18492,7 +18495,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18512,13 +18515,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C307" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D307" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18548,7 +18551,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18568,13 +18571,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C308" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D308" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18604,7 +18607,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18624,13 +18627,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C309" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D309" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18651,7 +18654,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18660,7 +18663,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18680,13 +18683,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C310" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D310" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18716,7 +18719,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18736,13 +18739,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C311" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D311" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18772,7 +18775,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18792,13 +18795,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C312" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D312" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18828,7 +18831,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18848,13 +18851,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C313" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D313" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18884,7 +18887,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18904,10 +18907,10 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C314" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D314" t="s">
         <v>258</v>
@@ -18922,7 +18925,7 @@
         <v>9</v>
       </c>
       <c r="H314">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I314">
         <v>9503.1</v>
@@ -18930,23 +18933,29 @@
       <c r="J314">
         <v>1043.2</v>
       </c>
+      <c r="K314" t="s">
+        <v>163</v>
+      </c>
       <c r="L314">
         <v>1003.11</v>
       </c>
       <c r="M314">
-        <v>0</v>
+        <v>1003.11</v>
+      </c>
+      <c r="N314" t="s">
+        <v>277</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>-475.1100000000007</v>
       </c>
       <c r="P314">
-        <v>-114.3</v>
+        <v>0</v>
       </c>
       <c r="Q314">
-        <v>-114.3</v>
+        <v>-475.1100000000007</v>
       </c>
       <c r="R314">
-        <v>-1.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -18954,13 +18963,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C315" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D315" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18978,7 +18987,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4836</v>
+        <v>4774.2</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18990,13 +18999,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>140.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q315">
-        <v>140.8</v>
+        <v>17.2</v>
       </c>
       <c r="R315">
-        <v>1.48</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19004,13 +19013,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C316" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D316" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19028,7 +19037,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2993.2</v>
+        <v>2900</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19040,13 +19049,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>165.6</v>
+        <v>-114</v>
       </c>
       <c r="Q316">
-        <v>165.6</v>
+        <v>-114</v>
       </c>
       <c r="R316">
-        <v>1.88</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19054,13 +19063,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C317" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D317" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19078,7 +19087,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>311.5</v>
+        <v>308.25</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19090,13 +19099,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-223.2</v>
+        <v>-323.95</v>
       </c>
       <c r="Q317">
-        <v>-223.2</v>
+        <v>-323.95</v>
       </c>
       <c r="R317">
-        <v>-2.26</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19104,13 +19113,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C318" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D318" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19131,7 +19140,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19140,7 +19149,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19160,13 +19169,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C319" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D319" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19184,7 +19193,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1211.2</v>
+        <v>1200.4</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19196,13 +19205,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>536</v>
+        <v>449.6</v>
       </c>
       <c r="Q319">
-        <v>536</v>
+        <v>449.6</v>
       </c>
       <c r="R319">
-        <v>5.86</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19210,13 +19219,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C320" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D320" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19234,7 +19243,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>413.25</v>
+        <v>405</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19246,13 +19255,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-138</v>
+        <v>-327.75</v>
       </c>
       <c r="Q320">
-        <v>-138</v>
+        <v>-327.75</v>
       </c>
       <c r="R320">
-        <v>-1.43</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19260,13 +19269,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C321" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D321" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19284,7 +19293,7 @@
         <v>8460</v>
       </c>
       <c r="J321">
-        <v>2774</v>
+        <v>2700</v>
       </c>
       <c r="L321">
         <v>2679</v>
@@ -19296,13 +19305,13 @@
         <v>0</v>
       </c>
       <c r="P321">
-        <v>-138</v>
+        <v>-360</v>
       </c>
       <c r="Q321">
-        <v>-138</v>
+        <v>-360</v>
       </c>
       <c r="R321">
-        <v>-1.63</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19310,13 +19319,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C322" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D322" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19334,7 +19343,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1807.3</v>
+        <v>1785.3</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19346,13 +19355,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>161.5</v>
+        <v>51.5</v>
       </c>
       <c r="Q322">
-        <v>161.5</v>
+        <v>51.5</v>
       </c>
       <c r="R322">
-        <v>1.82</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19360,13 +19369,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C323" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D323" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19384,7 +19393,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1256.7</v>
+        <v>1243.6</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19396,13 +19405,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>215.2</v>
+        <v>110.4</v>
       </c>
       <c r="Q323">
-        <v>215.2</v>
+        <v>110.4</v>
       </c>
       <c r="R323">
-        <v>2.19</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19410,10 +19419,10 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C324" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D324" t="s">
         <v>258</v>
@@ -19428,7 +19437,7 @@
         <v>21</v>
       </c>
       <c r="H324">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I324">
         <v>9891</v>
@@ -19436,23 +19445,29 @@
       <c r="J324">
         <v>484.5</v>
       </c>
+      <c r="K324" t="s">
+        <v>163</v>
+      </c>
       <c r="L324">
         <v>447.45</v>
       </c>
       <c r="M324">
-        <v>0</v>
+        <v>447.45</v>
+      </c>
+      <c r="N324" t="s">
+        <v>277</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>-494.5500000000002</v>
       </c>
       <c r="P324">
-        <v>283.5</v>
+        <v>0</v>
       </c>
       <c r="Q324">
-        <v>283.5</v>
+        <v>-494.5500000000002</v>
       </c>
       <c r="R324">
-        <v>2.87</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -19460,10 +19475,10 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C325" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D325" t="s">
         <v>258</v>
@@ -19478,7 +19493,7 @@
         <v>9</v>
       </c>
       <c r="H325">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I325">
         <v>9492.299999999999</v>
@@ -19486,23 +19501,29 @@
       <c r="J325">
         <v>1053</v>
       </c>
+      <c r="K325" t="s">
+        <v>163</v>
+      </c>
       <c r="L325">
         <v>1001.97</v>
       </c>
       <c r="M325">
-        <v>0</v>
+        <v>1001.97</v>
+      </c>
+      <c r="N325" t="s">
+        <v>277</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>-474.5700000000002</v>
       </c>
       <c r="P325">
-        <v>-15.3</v>
+        <v>0</v>
       </c>
       <c r="Q325">
-        <v>-15.3</v>
+        <v>-474.5700000000002</v>
       </c>
       <c r="R325">
-        <v>-0.16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -19510,13 +19531,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C326" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D326" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19534,7 +19555,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>164.4</v>
+        <v>162.5</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19546,13 +19567,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>393.75</v>
+        <v>274.05</v>
       </c>
       <c r="Q326">
-        <v>393.75</v>
+        <v>274.05</v>
       </c>
       <c r="R326">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19560,13 +19581,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C327" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D327" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19584,7 +19605,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1886.7</v>
+        <v>1854.8</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19596,13 +19617,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>332</v>
+        <v>172.5</v>
       </c>
       <c r="Q327">
-        <v>332</v>
+        <v>172.5</v>
       </c>
       <c r="R327">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19610,13 +19631,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C328" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D328" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19637,7 +19658,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19646,7 +19667,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19666,13 +19687,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C329" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D329" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -19690,7 +19711,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>342.65</v>
+        <v>335.5</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19702,13 +19723,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>849.4</v>
+        <v>627.75</v>
       </c>
       <c r="Q329">
-        <v>849.4</v>
+        <v>627.75</v>
       </c>
       <c r="R329">
-        <v>8.69</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19716,13 +19737,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C330" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D330" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19740,7 +19761,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4880</v>
+        <v>4832.5</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19752,13 +19773,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>48</v>
+        <v>-47</v>
       </c>
       <c r="Q330">
-        <v>48</v>
+        <v>-47</v>
       </c>
       <c r="R330">
-        <v>0.49</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19766,13 +19787,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C331" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D331" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19790,7 +19811,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3188.5</v>
+        <v>3166.5</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19802,13 +19823,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>4.5</v>
+        <v>-61.5</v>
       </c>
       <c r="Q331">
-        <v>4.5</v>
+        <v>-61.5</v>
       </c>
       <c r="R331">
-        <v>0.05</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19816,13 +19837,13 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C332" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D332" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -19840,7 +19861,7 @@
         <v>9059.200000000001</v>
       </c>
       <c r="J332">
-        <v>1096.5</v>
+        <v>1090</v>
       </c>
       <c r="L332">
         <v>1075.78</v>
@@ -19852,13 +19873,13 @@
         <v>0</v>
       </c>
       <c r="P332">
-        <v>-287.2</v>
+        <v>-339.2</v>
       </c>
       <c r="Q332">
-        <v>-287.2</v>
+        <v>-339.2</v>
       </c>
       <c r="R332">
-        <v>-3.17</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19866,10 +19887,10 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C333" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D333" t="s">
         <v>258</v>
@@ -19884,7 +19905,7 @@
         <v>5</v>
       </c>
       <c r="H333">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I333">
         <v>9000</v>
@@ -19892,23 +19913,29 @@
       <c r="J333">
         <v>1774</v>
       </c>
+      <c r="K333" t="s">
+        <v>163</v>
+      </c>
       <c r="L333">
         <v>1710</v>
       </c>
       <c r="M333">
-        <v>0</v>
+        <v>1630</v>
+      </c>
+      <c r="N333" t="s">
+        <v>278</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>-850</v>
       </c>
       <c r="P333">
-        <v>-130</v>
+        <v>0</v>
       </c>
       <c r="Q333">
-        <v>-130</v>
+        <v>-850</v>
       </c>
       <c r="R333">
-        <v>-1.44</v>
+        <v>-9.44</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -19916,13 +19943,13 @@
         <v>161</v>
       </c>
       <c r="B334" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C334" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D334" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -19940,7 +19967,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1500.6</v>
+        <v>1577</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -19952,13 +19979,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>-51</v>
+        <v>407.4</v>
       </c>
       <c r="Q334">
-        <v>-51</v>
+        <v>407.4</v>
       </c>
       <c r="R334">
-        <v>-0.5600000000000001</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -19966,13 +19993,13 @@
         <v>161</v>
       </c>
       <c r="B335" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C335" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D335" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -19990,7 +20017,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>4929</v>
+        <v>4895</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -20002,13 +20029,13 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>-94</v>
+        <v>-128</v>
       </c>
       <c r="Q335">
-        <v>-94</v>
+        <v>-128</v>
       </c>
       <c r="R335">
-        <v>-1.87</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20016,13 +20043,13 @@
         <v>162</v>
       </c>
       <c r="B336" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C336" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D336" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -20040,7 +20067,7 @@
         <v>9654.75</v>
       </c>
       <c r="J336">
-        <v>459.75</v>
+        <v>449.4</v>
       </c>
       <c r="L336">
         <v>436.76</v>
@@ -20052,13 +20079,13 @@
         <v>0</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>-217.35</v>
       </c>
       <c r="Q336">
-        <v>0</v>
+        <v>-217.35</v>
       </c>
       <c r="R336">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -20066,13 +20093,13 @@
         <v>162</v>
       </c>
       <c r="B337" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C337" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D337" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -20090,7 +20117,7 @@
         <v>9402.4</v>
       </c>
       <c r="J337">
-        <v>1175.3</v>
+        <v>1157.8</v>
       </c>
       <c r="L337">
         <v>1116.53</v>
@@ -20102,12 +20129,62 @@
         <v>0</v>
       </c>
       <c r="P337">
-        <v>0</v>
+        <v>-140</v>
       </c>
       <c r="Q337">
-        <v>0</v>
+        <v>-140</v>
       </c>
       <c r="R337">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18">
+      <c r="A338" t="s">
+        <v>163</v>
+      </c>
+      <c r="B338" t="s">
+        <v>191</v>
+      </c>
+      <c r="C338" t="s">
+        <v>255</v>
+      </c>
+      <c r="D338" t="s">
+        <v>259</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>618.4</v>
+      </c>
+      <c r="G338">
+        <v>16</v>
+      </c>
+      <c r="H338">
+        <v>16</v>
+      </c>
+      <c r="I338">
+        <v>9894.4</v>
+      </c>
+      <c r="J338">
+        <v>618.4</v>
+      </c>
+      <c r="L338">
+        <v>587.48</v>
+      </c>
+      <c r="M338">
+        <v>0</v>
+      </c>
+      <c r="O338">
+        <v>0</v>
+      </c>
+      <c r="P338">
+        <v>0</v>
+      </c>
+      <c r="Q338">
+        <v>0</v>
+      </c>
+      <c r="R338">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="284">
   <si>
     <t>Buy Date</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1226,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S338"/>
+  <dimension ref="A1:S339"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1303,13 +1306,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1339,7 +1342,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1359,13 +1362,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1395,7 +1398,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1418,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1454,7 +1457,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1474,13 +1477,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1510,7 +1513,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1530,13 +1533,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1566,7 +1569,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1586,13 +1589,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1622,7 +1625,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1642,13 +1645,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1678,7 +1681,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1698,13 +1701,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1734,7 +1737,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1754,13 +1757,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1790,7 +1793,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1810,13 +1813,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1837,7 +1840,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1846,7 +1849,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1861,7 +1864,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1869,13 +1872,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1905,7 +1908,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1928,13 +1931,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1964,7 +1967,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1984,13 +1987,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2020,7 +2023,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2040,13 +2043,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2076,7 +2079,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2096,13 +2099,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2132,7 +2135,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2152,13 +2155,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2188,7 +2191,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2208,13 +2211,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2244,7 +2247,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2264,13 +2267,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2300,7 +2303,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2320,13 +2323,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2356,7 +2359,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2376,13 +2379,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2403,7 +2406,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2412,7 +2415,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2432,13 +2435,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2459,7 +2462,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2468,7 +2471,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2488,13 +2491,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2524,7 +2527,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2544,13 +2547,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2580,7 +2583,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2600,13 +2603,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2636,7 +2639,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2656,13 +2659,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2683,7 +2686,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2692,7 +2695,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2712,13 +2715,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2748,7 +2751,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2768,13 +2771,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2804,7 +2807,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2824,13 +2827,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2860,7 +2863,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2880,13 +2883,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2916,7 +2919,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2936,13 +2939,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2963,7 +2966,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2972,7 +2975,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2992,13 +2995,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3028,7 +3031,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3048,13 +3051,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3084,7 +3087,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3104,13 +3107,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3131,7 +3134,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3140,7 +3143,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3160,13 +3163,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3187,7 +3190,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3196,7 +3199,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3216,13 +3219,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3252,7 +3255,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3272,13 +3275,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D37" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3308,7 +3311,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3328,13 +3331,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3364,7 +3367,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3387,13 +3390,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3423,7 +3426,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3443,13 +3446,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3479,7 +3482,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3499,13 +3502,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3535,7 +3538,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3555,13 +3558,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3582,7 +3585,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3591,7 +3594,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3611,13 +3614,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3638,7 +3641,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3647,7 +3650,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3667,13 +3670,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3703,7 +3706,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3723,13 +3726,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3759,7 +3762,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3779,13 +3782,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3815,7 +3818,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3838,13 +3841,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3874,7 +3877,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3894,13 +3897,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3930,7 +3933,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3950,13 +3953,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3986,7 +3989,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4009,13 +4012,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4045,7 +4048,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4065,13 +4068,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4101,7 +4104,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4121,13 +4124,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D52" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4157,7 +4160,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4180,13 +4183,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4216,7 +4219,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4236,13 +4239,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4272,7 +4275,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4295,13 +4298,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4331,7 +4334,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4354,13 +4357,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D56" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4390,7 +4393,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4410,13 +4413,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4437,7 +4440,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4446,7 +4449,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4466,13 +4469,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D58" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4502,7 +4505,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4522,13 +4525,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4558,7 +4561,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4581,13 +4584,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4617,7 +4620,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4637,13 +4640,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4673,7 +4676,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4696,13 +4699,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4732,7 +4735,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4747,7 +4750,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4755,13 +4758,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C63" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D63" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4791,7 +4794,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4811,13 +4814,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4847,7 +4850,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4867,13 +4870,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C65" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4903,7 +4906,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4923,13 +4926,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D66" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4959,7 +4962,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4979,13 +4982,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5015,7 +5018,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5035,13 +5038,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5071,7 +5074,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5091,13 +5094,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5118,7 +5121,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5127,7 +5130,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5147,13 +5150,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5183,7 +5186,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5203,13 +5206,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5239,7 +5242,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5259,13 +5262,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C72" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5295,7 +5298,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5315,13 +5318,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C73" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5351,7 +5354,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5371,13 +5374,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C74" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D74" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5407,7 +5410,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5427,13 +5430,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C75" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D75" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5463,7 +5466,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5483,13 +5486,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5519,7 +5522,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5539,13 +5542,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5575,7 +5578,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5595,13 +5598,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5631,7 +5634,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5651,13 +5654,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D79" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5687,7 +5690,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5707,13 +5710,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5743,7 +5746,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5763,13 +5766,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5799,7 +5802,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5819,13 +5822,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C82" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D82" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5855,7 +5858,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5878,13 +5881,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5914,7 +5917,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5934,13 +5937,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5970,7 +5973,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5990,13 +5993,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C85" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D85" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6026,7 +6029,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6046,13 +6049,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6082,7 +6085,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6102,13 +6105,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D87" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6138,7 +6141,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6158,13 +6161,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6194,7 +6197,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6214,13 +6217,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D89" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6250,7 +6253,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6270,13 +6273,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6306,7 +6309,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6326,13 +6329,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6362,7 +6365,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6385,13 +6388,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6421,7 +6424,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6441,13 +6444,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D93" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6477,7 +6480,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6497,13 +6500,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6533,7 +6536,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6553,13 +6556,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6589,7 +6592,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6609,13 +6612,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D96" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6645,7 +6648,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6665,13 +6668,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D97" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6701,7 +6704,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6721,13 +6724,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C98" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6757,7 +6760,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6780,13 +6783,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6816,7 +6819,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6836,13 +6839,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C100" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6872,7 +6875,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6892,13 +6895,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C101" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6928,7 +6931,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6948,13 +6951,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6984,7 +6987,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7004,13 +7007,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C103" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7040,7 +7043,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7060,13 +7063,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C104" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D104" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7096,7 +7099,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7116,13 +7119,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C105" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D105" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7152,7 +7155,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7172,13 +7175,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D106" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7199,7 +7202,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7208,7 +7211,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7228,13 +7231,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D107" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7264,7 +7267,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7284,13 +7287,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D108" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7320,7 +7323,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7340,13 +7343,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D109" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7367,7 +7370,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7376,7 +7379,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7396,13 +7399,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D110" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7432,7 +7435,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7452,13 +7455,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D111" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7488,7 +7491,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7508,13 +7511,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C112" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D112" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7544,7 +7547,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7564,13 +7567,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C113" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7600,7 +7603,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7620,13 +7623,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D114" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7656,7 +7659,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7676,13 +7679,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C115" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D115" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7712,7 +7715,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7732,13 +7735,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C116" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D116" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7768,7 +7771,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7788,13 +7791,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7824,7 +7827,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7844,13 +7847,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D118" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7880,7 +7883,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7903,13 +7906,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7939,7 +7942,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7959,13 +7962,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C120" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D120" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7995,7 +7998,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8015,13 +8018,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C121" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D121" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8051,7 +8054,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8071,13 +8074,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C122" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8107,7 +8110,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8127,13 +8130,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C123" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D123" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8154,7 +8157,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8163,7 +8166,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8183,13 +8186,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D124" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8219,7 +8222,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8239,13 +8242,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D125" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8275,7 +8278,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8295,13 +8298,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8331,7 +8334,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8354,13 +8357,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8390,7 +8393,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8410,13 +8413,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D128" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8446,7 +8449,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8469,13 +8472,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8505,7 +8508,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8525,13 +8528,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C130" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D130" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8561,7 +8564,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8581,13 +8584,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D131" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8617,7 +8620,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8637,13 +8640,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8673,7 +8676,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8693,13 +8696,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C133" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D133" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8720,7 +8723,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8729,7 +8732,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8749,13 +8752,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8785,7 +8788,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8805,13 +8808,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8841,7 +8844,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8861,13 +8864,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C136" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D136" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8897,7 +8900,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8917,13 +8920,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D137" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8953,7 +8956,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8976,13 +8979,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D138" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9012,7 +9015,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9032,13 +9035,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C139" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9068,7 +9071,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9088,13 +9091,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C140" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D140" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9124,7 +9127,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9144,13 +9147,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C141" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9180,7 +9183,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9200,13 +9203,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C142" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D142" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9236,7 +9239,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9256,13 +9259,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C143" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D143" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9292,7 +9295,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9312,13 +9315,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C144" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D144" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9348,7 +9351,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9368,13 +9371,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C145" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D145" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9404,7 +9407,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9424,13 +9427,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C146" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D146" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9460,7 +9463,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9483,13 +9486,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C147" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D147" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9519,7 +9522,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9542,13 +9545,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C148" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D148" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9578,7 +9581,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9601,13 +9604,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D149" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9628,7 +9631,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9637,7 +9640,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9660,13 +9663,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C150" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D150" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9696,7 +9699,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9719,13 +9722,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C151" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D151" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9755,7 +9758,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9775,13 +9778,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9811,7 +9814,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9834,13 +9837,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C153" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9870,7 +9873,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9893,13 +9896,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C154" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D154" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9929,7 +9932,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9944,7 +9947,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9952,13 +9955,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C155" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D155" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9988,7 +9991,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10011,13 +10014,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C156" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D156" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10047,7 +10050,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10067,13 +10070,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C157" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D157" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10103,7 +10106,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10123,13 +10126,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C158" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D158" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10159,7 +10162,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10179,13 +10182,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C159" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D159" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10215,7 +10218,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10238,13 +10241,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C160" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D160" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10274,7 +10277,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10294,13 +10297,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C161" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D161" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10330,7 +10333,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10353,13 +10356,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C162" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D162" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10389,7 +10392,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10409,13 +10412,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C163" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D163" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10445,7 +10448,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10468,13 +10471,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C164" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D164" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10495,7 +10498,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10504,7 +10507,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10527,13 +10530,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10554,7 +10557,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10563,7 +10566,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10583,13 +10586,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C166" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D166" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10619,7 +10622,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10642,13 +10645,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C167" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D167" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10678,7 +10681,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10698,13 +10701,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C168" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D168" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10734,7 +10737,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10754,13 +10757,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C169" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D169" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10790,7 +10793,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10813,13 +10816,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C170" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D170" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10849,7 +10852,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10872,13 +10875,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C171" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D171" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10908,7 +10911,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10928,13 +10931,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C172" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D172" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10964,7 +10967,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10987,13 +10990,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D173" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11023,7 +11026,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11043,13 +11046,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C174" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D174" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11079,7 +11082,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11102,13 +11105,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C175" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D175" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11138,7 +11141,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11158,13 +11161,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C176" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D176" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11194,7 +11197,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11214,13 +11217,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C177" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D177" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11250,7 +11253,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11273,13 +11276,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D178" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11300,7 +11303,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11309,7 +11312,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11329,13 +11332,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D179" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11365,7 +11368,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11385,13 +11388,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C180" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11421,7 +11424,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11441,13 +11444,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C181" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D181" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11477,7 +11480,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11497,13 +11500,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C182" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D182" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11533,7 +11536,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11556,13 +11559,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C183" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D183" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11592,7 +11595,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11612,13 +11615,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C184" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D184" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11648,7 +11651,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11671,13 +11674,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C185" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D185" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11707,7 +11710,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11727,13 +11730,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C186" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D186" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11754,7 +11757,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11763,7 +11766,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11783,13 +11786,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C187" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D187" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11810,7 +11813,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11819,7 +11822,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11842,13 +11845,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C188" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D188" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11869,7 +11872,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11878,7 +11881,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11898,13 +11901,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C189" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D189" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11934,7 +11937,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11954,13 +11957,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C190" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D190" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11990,7 +11993,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12010,13 +12013,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C191" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D191" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12037,7 +12040,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12046,7 +12049,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12061,7 +12064,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12069,13 +12072,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C192" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D192" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12105,7 +12108,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12125,13 +12128,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C193" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D193" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12161,7 +12164,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12181,13 +12184,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D194" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12208,7 +12211,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12217,7 +12220,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12237,13 +12240,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C195" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D195" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12273,7 +12276,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12288,7 +12291,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12296,13 +12299,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C196" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D196" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12332,7 +12335,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12355,13 +12358,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C197" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D197" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12382,7 +12385,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12391,7 +12394,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12411,13 +12414,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C198" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D198" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12447,7 +12450,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12467,13 +12470,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C199" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D199" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12503,7 +12506,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12523,13 +12526,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C200" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D200" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12559,7 +12562,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12579,13 +12582,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C201" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D201" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12615,7 +12618,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12635,13 +12638,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C202" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D202" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12671,7 +12674,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12691,13 +12694,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D203" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12727,7 +12730,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12742,7 +12745,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12750,13 +12753,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C204" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D204" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12786,7 +12789,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12806,13 +12809,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C205" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D205" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12842,7 +12845,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12862,13 +12865,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C206" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D206" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12898,7 +12901,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12918,13 +12921,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C207" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D207" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12954,7 +12957,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12977,13 +12980,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C208" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D208" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13013,7 +13016,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13033,13 +13036,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C209" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D209" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13069,7 +13072,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13089,13 +13092,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C210" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D210" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13116,7 +13119,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13125,7 +13128,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13145,13 +13148,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C211" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D211" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13181,7 +13184,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13201,13 +13204,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C212" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D212" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13237,7 +13240,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13257,13 +13260,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C213" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D213" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13293,7 +13296,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13313,13 +13316,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C214" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D214" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13349,7 +13352,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13364,7 +13367,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13372,13 +13375,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C215" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D215" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13408,7 +13411,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13428,13 +13431,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C216" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D216" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13464,7 +13467,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13484,13 +13487,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C217" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D217" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13520,7 +13523,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13540,13 +13543,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C218" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D218" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13576,7 +13579,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13596,13 +13599,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C219" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D219" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13632,7 +13635,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13652,13 +13655,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C220" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D220" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13679,7 +13682,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13688,7 +13691,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13708,13 +13711,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C221" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D221" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13735,7 +13738,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13744,7 +13747,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13764,13 +13767,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C222" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D222" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13800,7 +13803,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13820,13 +13823,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C223" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D223" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13847,7 +13850,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13856,7 +13859,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13876,13 +13879,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C224" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D224" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13912,7 +13915,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13932,13 +13935,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C225" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D225" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13968,7 +13971,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13988,13 +13991,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C226" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D226" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14024,7 +14027,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14044,13 +14047,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C227" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D227" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14080,7 +14083,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14100,13 +14103,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C228" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D228" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14136,7 +14139,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14156,13 +14159,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C229" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D229" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14180,7 +14183,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8888.5</v>
+        <v>8889</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14192,13 +14195,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>598</v>
+        <v>598.5</v>
       </c>
       <c r="Q229">
-        <v>598</v>
+        <v>598.5</v>
       </c>
       <c r="R229">
-        <v>7.21</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14206,13 +14209,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C230" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D230" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14242,7 +14245,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14262,13 +14265,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C231" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D231" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14289,7 +14292,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14298,7 +14301,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14313,7 +14316,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14321,13 +14324,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C232" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D232" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14357,7 +14360,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14377,13 +14380,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C233" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D233" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14413,7 +14416,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14433,13 +14436,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C234" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D234" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14469,7 +14472,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14489,13 +14492,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C235" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D235" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14516,7 +14519,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14525,7 +14528,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14548,13 +14551,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C236" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D236" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14575,7 +14578,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14584,7 +14587,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14607,13 +14610,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C237" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D237" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14643,7 +14646,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14663,13 +14666,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C238" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D238" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14699,7 +14702,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14719,13 +14722,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C239" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D239" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14755,7 +14758,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14775,13 +14778,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C240" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D240" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14811,7 +14814,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14831,13 +14834,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C241" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D241" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14867,7 +14870,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14887,13 +14890,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C242" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D242" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14923,7 +14926,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14943,13 +14946,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C243" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D243" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14979,7 +14982,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -15002,13 +15005,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C244" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D244" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15038,7 +15041,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15053,7 +15056,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15061,13 +15064,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C245" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D245" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15088,7 +15091,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15097,7 +15100,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15117,13 +15120,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D246" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15153,7 +15156,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15173,13 +15176,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C247" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D247" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15209,7 +15212,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15229,13 +15232,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C248" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D248" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15265,7 +15268,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15285,13 +15288,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C249" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D249" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15321,7 +15324,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15341,13 +15344,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C250" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D250" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15377,7 +15380,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15397,13 +15400,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C251" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D251" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15433,7 +15436,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15453,13 +15456,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C252" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D252" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15489,7 +15492,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15512,13 +15515,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C253" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D253" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15548,7 +15551,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15568,13 +15571,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15592,7 +15595,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>728.8</v>
+        <v>726.8</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15604,13 +15607,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>304.5</v>
+        <v>276.5</v>
       </c>
       <c r="Q254">
-        <v>304.5</v>
+        <v>276.5</v>
       </c>
       <c r="R254">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15618,13 +15621,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C255" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D255" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15654,7 +15657,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15674,13 +15677,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C256" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D256" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15710,7 +15713,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15730,13 +15733,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C257" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D257" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15757,7 +15760,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15766,7 +15769,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15786,13 +15789,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D258" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15822,7 +15825,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15842,13 +15845,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C259" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D259" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15878,7 +15881,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15901,10 +15904,10 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C260" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D260" t="s">
         <v>259</v>
@@ -15919,7 +15922,7 @@
         <v>7</v>
       </c>
       <c r="H260">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I260">
         <v>8931.300000000001</v>
@@ -15927,23 +15930,29 @@
       <c r="J260">
         <v>1219.2</v>
       </c>
+      <c r="K260" t="s">
+        <v>164</v>
+      </c>
       <c r="L260">
         <v>1212.11</v>
       </c>
       <c r="M260">
-        <v>0</v>
+        <v>1210.5</v>
+      </c>
+      <c r="N260" t="s">
+        <v>279</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>-457.8000000000006</v>
       </c>
       <c r="P260">
-        <v>-396.9</v>
+        <v>0</v>
       </c>
       <c r="Q260">
-        <v>-396.9</v>
+        <v>-457.8000000000006</v>
       </c>
       <c r="R260">
-        <v>-4.44</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="261" spans="1:19">
@@ -15951,13 +15960,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C261" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D261" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -15975,7 +15984,7 @@
         <v>9664.200000000001</v>
       </c>
       <c r="J261">
-        <v>1334.5</v>
+        <v>1326.8</v>
       </c>
       <c r="L261">
         <v>1311.57</v>
@@ -15987,13 +15996,13 @@
         <v>0</v>
       </c>
       <c r="P261">
-        <v>-322.7</v>
+        <v>-376.6</v>
       </c>
       <c r="Q261">
-        <v>-322.7</v>
+        <v>-376.6</v>
       </c>
       <c r="R261">
-        <v>-3.34</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -16001,13 +16010,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C262" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D262" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16037,7 +16046,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16060,13 +16069,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C263" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D263" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16096,7 +16105,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16116,13 +16125,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C264" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D264" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16152,7 +16161,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16175,13 +16184,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C265" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D265" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16211,7 +16220,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16234,13 +16243,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C266" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D266" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16270,7 +16279,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16290,13 +16299,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C267" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D267" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16326,7 +16335,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16346,13 +16355,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C268" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D268" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16382,7 +16391,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16402,13 +16411,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C269" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D269" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16438,7 +16447,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16458,13 +16467,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C270" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D270" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16494,7 +16503,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16514,10 +16523,10 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C271" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D271" t="s">
         <v>259</v>
@@ -16532,7 +16541,7 @@
         <v>6</v>
       </c>
       <c r="H271">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I271">
         <v>9547.799999999999</v>
@@ -16540,23 +16549,29 @@
       <c r="J271">
         <v>1522</v>
       </c>
+      <c r="K271" t="s">
+        <v>164</v>
+      </c>
       <c r="L271">
         <v>1511.73</v>
       </c>
       <c r="M271">
-        <v>0</v>
+        <v>1511.73</v>
+      </c>
+      <c r="N271" t="s">
+        <v>278</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>-477.4199999999996</v>
       </c>
       <c r="P271">
-        <v>-415.8</v>
+        <v>0</v>
       </c>
       <c r="Q271">
-        <v>-415.8</v>
+        <v>-477.4199999999996</v>
       </c>
       <c r="R271">
-        <v>-4.35</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="272" spans="1:19">
@@ -16564,13 +16579,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C272" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D272" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16600,7 +16615,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16620,13 +16635,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C273" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D273" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16656,7 +16671,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16676,13 +16691,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C274" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D274" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16703,7 +16718,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16712,7 +16727,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16732,13 +16747,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C275" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D275" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16768,7 +16783,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16788,13 +16803,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C276" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D276" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16824,7 +16839,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16844,13 +16859,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C277" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D277" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16880,7 +16895,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16900,13 +16915,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C278" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D278" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16936,7 +16951,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16956,13 +16971,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C279" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D279" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -16992,7 +17007,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17012,13 +17027,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C280" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D280" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17048,7 +17063,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17068,13 +17083,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C281" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D281" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17104,7 +17119,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17124,13 +17139,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C282" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D282" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17160,7 +17175,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17180,13 +17195,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C283" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D283" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17216,7 +17231,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17236,13 +17251,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C284" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D284" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17272,7 +17287,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17292,13 +17307,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C285" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D285" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17328,7 +17343,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17348,13 +17363,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C286" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D286" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17384,7 +17399,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17404,13 +17419,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C287" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D287" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17440,7 +17455,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17460,13 +17475,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C288" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D288" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17496,7 +17511,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17516,13 +17531,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C289" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D289" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17543,7 +17558,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17552,7 +17567,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17572,13 +17587,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C290" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D290" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17608,7 +17623,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17628,13 +17643,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C291" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D291" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17652,7 +17667,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>549.6</v>
+        <v>550.05</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17664,13 +17679,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-295.8</v>
+        <v>-288.15</v>
       </c>
       <c r="Q291">
-        <v>-295.8</v>
+        <v>-288.15</v>
       </c>
       <c r="R291">
-        <v>-3.07</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17678,13 +17693,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C292" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D292" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17705,7 +17720,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17714,7 +17729,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17734,13 +17749,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C293" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D293" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17770,7 +17785,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17790,13 +17805,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C294" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D294" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17826,7 +17841,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17849,13 +17864,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C295" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D295" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17885,7 +17900,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17905,13 +17920,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C296" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D296" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17941,7 +17956,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17961,13 +17976,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C297" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D297" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -17985,7 +18000,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -17997,13 +18012,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>52.7</v>
+        <v>8.5</v>
       </c>
       <c r="Q297">
-        <v>52.7</v>
+        <v>8.5</v>
       </c>
       <c r="R297">
-        <v>0.53</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18011,13 +18026,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C298" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D298" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18047,7 +18062,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18067,13 +18082,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C299" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D299" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18103,7 +18118,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18123,13 +18138,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C300" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D300" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18159,7 +18174,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18179,13 +18194,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C301" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D301" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18215,7 +18230,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18235,13 +18250,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C302" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D302" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18271,7 +18286,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18291,13 +18306,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C303" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D303" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18318,7 +18333,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18327,7 +18342,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18347,13 +18362,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C304" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D304" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18383,7 +18398,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18403,13 +18418,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C305" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D305" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18439,7 +18454,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18459,13 +18474,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C306" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D306" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18495,7 +18510,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18515,13 +18530,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C307" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D307" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18551,7 +18566,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18571,13 +18586,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C308" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D308" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18607,7 +18622,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18627,13 +18642,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C309" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D309" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18654,7 +18669,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18663,7 +18678,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18683,13 +18698,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C310" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D310" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18719,7 +18734,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18739,13 +18754,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C311" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D311" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18775,7 +18790,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18795,13 +18810,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C312" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D312" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18831,7 +18846,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18851,13 +18866,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C313" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D313" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18887,7 +18902,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18907,13 +18922,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C314" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D314" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18943,7 +18958,7 @@
         <v>1003.11</v>
       </c>
       <c r="N314" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O314">
         <v>-475.1100000000007</v>
@@ -18963,13 +18978,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C315" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D315" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -18987,7 +19002,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4774.2</v>
+        <v>4800</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -18999,13 +19014,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>17.2</v>
+        <v>68.8</v>
       </c>
       <c r="Q315">
-        <v>17.2</v>
+        <v>68.8</v>
       </c>
       <c r="R315">
-        <v>0.18</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19013,13 +19028,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C316" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D316" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19037,7 +19052,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19049,13 +19064,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-114</v>
+        <v>-64.5</v>
       </c>
       <c r="Q316">
-        <v>-114</v>
+        <v>-64.5</v>
       </c>
       <c r="R316">
-        <v>-1.29</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19063,13 +19078,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C317" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D317" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19087,7 +19102,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>308.25</v>
+        <v>312.95</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19099,13 +19114,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-323.95</v>
+        <v>-178.25</v>
       </c>
       <c r="Q317">
-        <v>-323.95</v>
+        <v>-178.25</v>
       </c>
       <c r="R317">
-        <v>-3.28</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19113,13 +19128,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C318" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D318" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19140,7 +19155,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19149,7 +19164,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19169,13 +19184,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C319" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D319" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19193,7 +19208,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1200.4</v>
+        <v>1201</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19205,13 +19220,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>449.6</v>
+        <v>454.4</v>
       </c>
       <c r="Q319">
-        <v>449.6</v>
+        <v>454.4</v>
       </c>
       <c r="R319">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19219,13 +19234,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C320" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D320" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19243,7 +19258,7 @@
         <v>9642.75</v>
       </c>
       <c r="J320">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L320">
         <v>398.29</v>
@@ -19255,13 +19270,13 @@
         <v>0</v>
       </c>
       <c r="P320">
-        <v>-327.75</v>
+        <v>-350.75</v>
       </c>
       <c r="Q320">
-        <v>-327.75</v>
+        <v>-350.75</v>
       </c>
       <c r="R320">
-        <v>-3.4</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19269,10 +19284,10 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C321" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D321" t="s">
         <v>259</v>
@@ -19287,7 +19302,7 @@
         <v>3</v>
       </c>
       <c r="H321">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I321">
         <v>8460</v>
@@ -19295,23 +19310,29 @@
       <c r="J321">
         <v>2700</v>
       </c>
+      <c r="K321" t="s">
+        <v>164</v>
+      </c>
       <c r="L321">
         <v>2679</v>
       </c>
       <c r="M321">
-        <v>0</v>
+        <v>2679</v>
+      </c>
+      <c r="N321" t="s">
+        <v>278</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>-423</v>
       </c>
       <c r="P321">
-        <v>-360</v>
+        <v>0</v>
       </c>
       <c r="Q321">
-        <v>-360</v>
+        <v>-423</v>
       </c>
       <c r="R321">
-        <v>-4.26</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -19319,13 +19340,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C322" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D322" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19343,7 +19364,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19355,13 +19376,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>51.5</v>
+        <v>65</v>
       </c>
       <c r="Q322">
-        <v>51.5</v>
+        <v>65</v>
       </c>
       <c r="R322">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19369,13 +19390,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C323" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D323" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19393,7 +19414,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1243.6</v>
+        <v>1258</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19405,13 +19426,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>110.4</v>
+        <v>225.6</v>
       </c>
       <c r="Q323">
-        <v>110.4</v>
+        <v>225.6</v>
       </c>
       <c r="R323">
-        <v>1.12</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19419,13 +19440,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C324" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D324" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19455,7 +19476,7 @@
         <v>447.45</v>
       </c>
       <c r="N324" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O324">
         <v>-494.5500000000002</v>
@@ -19475,13 +19496,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C325" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D325" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19511,7 +19532,7 @@
         <v>1001.97</v>
       </c>
       <c r="N325" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O325">
         <v>-474.5700000000002</v>
@@ -19531,13 +19552,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C326" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D326" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19555,7 +19576,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>162.5</v>
+        <v>165.71</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19567,13 +19588,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>274.05</v>
+        <v>476.28</v>
       </c>
       <c r="Q326">
-        <v>274.05</v>
+        <v>476.28</v>
       </c>
       <c r="R326">
-        <v>2.75</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19581,13 +19602,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C327" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D327" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19605,7 +19626,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1854.8</v>
+        <v>1855.8</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19617,13 +19638,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>172.5</v>
+        <v>177.5</v>
       </c>
       <c r="Q327">
-        <v>172.5</v>
+        <v>177.5</v>
       </c>
       <c r="R327">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19631,13 +19652,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C328" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D328" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19658,7 +19679,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19667,7 +19688,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19687,13 +19708,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C329" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D329" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -19711,7 +19732,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19723,13 +19744,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>627.75</v>
+        <v>612.25</v>
       </c>
       <c r="Q329">
-        <v>627.75</v>
+        <v>612.25</v>
       </c>
       <c r="R329">
-        <v>6.42</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19737,13 +19758,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C330" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D330" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19761,7 +19782,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19773,13 +19794,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>-47</v>
+        <v>56</v>
       </c>
       <c r="Q330">
-        <v>-47</v>
+        <v>56</v>
       </c>
       <c r="R330">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19787,13 +19808,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C331" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D331" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19811,7 +19832,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19823,13 +19844,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-61.5</v>
+        <v>12</v>
       </c>
       <c r="Q331">
-        <v>-61.5</v>
+        <v>12</v>
       </c>
       <c r="R331">
-        <v>-0.64</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19837,13 +19858,13 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C332" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D332" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -19861,7 +19882,7 @@
         <v>9059.200000000001</v>
       </c>
       <c r="J332">
-        <v>1090</v>
+        <v>1096.5</v>
       </c>
       <c r="L332">
         <v>1075.78</v>
@@ -19873,13 +19894,13 @@
         <v>0</v>
       </c>
       <c r="P332">
-        <v>-339.2</v>
+        <v>-287.2</v>
       </c>
       <c r="Q332">
-        <v>-339.2</v>
+        <v>-287.2</v>
       </c>
       <c r="R332">
-        <v>-3.74</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19887,13 +19908,13 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C333" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D333" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -19923,7 +19944,7 @@
         <v>1630</v>
       </c>
       <c r="N333" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O333">
         <v>-850</v>
@@ -19943,13 +19964,13 @@
         <v>161</v>
       </c>
       <c r="B334" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C334" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D334" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -19967,7 +19988,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1577</v>
+        <v>1553.7</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -19979,13 +20000,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>407.4</v>
+        <v>267.6</v>
       </c>
       <c r="Q334">
-        <v>407.4</v>
+        <v>267.6</v>
       </c>
       <c r="R334">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -19993,13 +20014,13 @@
         <v>161</v>
       </c>
       <c r="B335" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C335" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D335" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -20017,7 +20038,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>4895</v>
+        <v>4937.5</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -20029,13 +20050,13 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>-128</v>
+        <v>-85.5</v>
       </c>
       <c r="Q335">
-        <v>-128</v>
+        <v>-85.5</v>
       </c>
       <c r="R335">
-        <v>-2.55</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20043,13 +20064,13 @@
         <v>162</v>
       </c>
       <c r="B336" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C336" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D336" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -20067,7 +20088,7 @@
         <v>9654.75</v>
       </c>
       <c r="J336">
-        <v>449.4</v>
+        <v>458.35</v>
       </c>
       <c r="L336">
         <v>436.76</v>
@@ -20079,13 +20100,13 @@
         <v>0</v>
       </c>
       <c r="P336">
-        <v>-217.35</v>
+        <v>-29.4</v>
       </c>
       <c r="Q336">
-        <v>-217.35</v>
+        <v>-29.4</v>
       </c>
       <c r="R336">
-        <v>-2.25</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -20093,13 +20114,13 @@
         <v>162</v>
       </c>
       <c r="B337" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C337" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D337" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -20117,7 +20138,7 @@
         <v>9402.4</v>
       </c>
       <c r="J337">
-        <v>1157.8</v>
+        <v>1164.8</v>
       </c>
       <c r="L337">
         <v>1116.53</v>
@@ -20129,13 +20150,13 @@
         <v>0</v>
       </c>
       <c r="P337">
-        <v>-140</v>
+        <v>-84</v>
       </c>
       <c r="Q337">
-        <v>-140</v>
+        <v>-84</v>
       </c>
       <c r="R337">
-        <v>-1.49</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -20143,13 +20164,13 @@
         <v>163</v>
       </c>
       <c r="B338" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C338" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D338" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -20167,7 +20188,7 @@
         <v>9894.4</v>
       </c>
       <c r="J338">
-        <v>618.4</v>
+        <v>611.2</v>
       </c>
       <c r="L338">
         <v>587.48</v>
@@ -20179,12 +20200,62 @@
         <v>0</v>
       </c>
       <c r="P338">
-        <v>0</v>
+        <v>-115.2</v>
       </c>
       <c r="Q338">
-        <v>0</v>
+        <v>-115.2</v>
       </c>
       <c r="R338">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18">
+      <c r="A339" t="s">
+        <v>164</v>
+      </c>
+      <c r="B339" t="s">
+        <v>177</v>
+      </c>
+      <c r="C339" t="s">
+        <v>256</v>
+      </c>
+      <c r="D339" t="s">
+        <v>260</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>463</v>
+      </c>
+      <c r="G339">
+        <v>21</v>
+      </c>
+      <c r="H339">
+        <v>21</v>
+      </c>
+      <c r="I339">
+        <v>9723</v>
+      </c>
+      <c r="J339">
+        <v>463</v>
+      </c>
+      <c r="L339">
+        <v>439.85</v>
+      </c>
+      <c r="M339">
+        <v>0</v>
+      </c>
+      <c r="O339">
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <v>0</v>
+      </c>
+      <c r="Q339">
+        <v>0</v>
+      </c>
+      <c r="R339">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="285">
   <si>
     <t>Buy Date</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1229,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S339"/>
+  <dimension ref="A1:S340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1306,13 +1309,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1342,7 +1345,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1362,13 +1365,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1398,7 +1401,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1421,13 +1424,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1457,7 +1460,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1477,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1513,7 +1516,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1533,13 +1536,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1569,7 +1572,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1589,13 +1592,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1625,7 +1628,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1645,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1681,7 +1684,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1701,13 +1704,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1737,7 +1740,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1757,13 +1760,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1793,7 +1796,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1813,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1840,7 +1843,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1849,7 +1852,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1864,7 +1867,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1872,13 +1875,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1908,7 +1911,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1931,13 +1934,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1967,7 +1970,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1987,13 +1990,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2023,7 +2026,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2043,13 +2046,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2079,7 +2082,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2099,13 +2102,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2135,7 +2138,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2155,13 +2158,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2191,7 +2194,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2211,13 +2214,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2247,7 +2250,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2267,13 +2270,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2303,7 +2306,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2323,13 +2326,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2359,7 +2362,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2379,13 +2382,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2406,7 +2409,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2415,7 +2418,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2435,13 +2438,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2462,7 +2465,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2471,7 +2474,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2491,13 +2494,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2527,7 +2530,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2547,13 +2550,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2583,7 +2586,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2603,13 +2606,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2639,7 +2642,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2659,13 +2662,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2686,7 +2689,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2695,7 +2698,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2715,13 +2718,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2751,7 +2754,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2771,13 +2774,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2807,7 +2810,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2827,13 +2830,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2863,7 +2866,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2883,13 +2886,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2919,7 +2922,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2939,13 +2942,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2966,7 +2969,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2975,7 +2978,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2995,13 +2998,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3031,7 +3034,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3051,13 +3054,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D33" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3087,7 +3090,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3107,13 +3110,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3134,7 +3137,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3143,7 +3146,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3163,13 +3166,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3190,7 +3193,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3199,7 +3202,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3219,13 +3222,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D36" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3255,7 +3258,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3275,13 +3278,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3311,7 +3314,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3331,13 +3334,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3367,7 +3370,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3390,13 +3393,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3426,7 +3429,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3446,13 +3449,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3482,7 +3485,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3502,13 +3505,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3538,7 +3541,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3558,13 +3561,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3585,7 +3588,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3594,7 +3597,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3614,13 +3617,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D43" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3641,7 +3644,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3650,7 +3653,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3670,13 +3673,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3706,7 +3709,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3726,13 +3729,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3762,7 +3765,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3782,13 +3785,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3818,7 +3821,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3841,13 +3844,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3877,7 +3880,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3897,13 +3900,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3933,7 +3936,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3953,13 +3956,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3989,7 +3992,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4012,13 +4015,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4048,7 +4051,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4068,13 +4071,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D51" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4104,7 +4107,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4124,13 +4127,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4160,7 +4163,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4183,13 +4186,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4219,7 +4222,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4239,13 +4242,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4275,7 +4278,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4298,13 +4301,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4334,7 +4337,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4357,13 +4360,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4393,7 +4396,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4413,13 +4416,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4440,7 +4443,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4449,7 +4452,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4469,13 +4472,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4505,7 +4508,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4525,13 +4528,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4561,7 +4564,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4584,13 +4587,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4620,7 +4623,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4640,13 +4643,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4676,7 +4679,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4699,13 +4702,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C62" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4735,7 +4738,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4750,7 +4753,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4758,13 +4761,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C63" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4794,7 +4797,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4814,13 +4817,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C64" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4850,7 +4853,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4870,13 +4873,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4906,7 +4909,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4926,13 +4929,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C66" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4962,7 +4965,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4982,13 +4985,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5018,7 +5021,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5038,13 +5041,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5074,7 +5077,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5094,13 +5097,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5121,7 +5124,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5130,7 +5133,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5150,13 +5153,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5186,7 +5189,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5206,13 +5209,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5242,7 +5245,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5262,13 +5265,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5298,7 +5301,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5318,13 +5321,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C73" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5354,7 +5357,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5374,13 +5377,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5410,7 +5413,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5430,13 +5433,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5466,7 +5469,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5486,13 +5489,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D76" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5522,7 +5525,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5542,13 +5545,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5578,7 +5581,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5598,13 +5601,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5634,7 +5637,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5654,13 +5657,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5690,7 +5693,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5710,13 +5713,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5746,7 +5749,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5766,13 +5769,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5802,7 +5805,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5822,13 +5825,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5858,7 +5861,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5881,13 +5884,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5917,7 +5920,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5937,13 +5940,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5973,7 +5976,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5993,13 +5996,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D85" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6029,7 +6032,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6049,13 +6052,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6085,7 +6088,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6105,13 +6108,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6141,7 +6144,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6161,13 +6164,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6197,7 +6200,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6217,13 +6220,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D89" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6253,7 +6256,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6273,13 +6276,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6309,7 +6312,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6329,13 +6332,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6365,7 +6368,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6388,13 +6391,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6424,7 +6427,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6444,13 +6447,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C93" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6480,7 +6483,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6500,13 +6503,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6536,7 +6539,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6556,13 +6559,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6592,7 +6595,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6612,13 +6615,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C96" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6648,7 +6651,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6668,13 +6671,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C97" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6704,7 +6707,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6724,13 +6727,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6760,7 +6763,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6783,13 +6786,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D99" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6819,7 +6822,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6839,13 +6842,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6875,7 +6878,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6895,13 +6898,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6931,7 +6934,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6951,13 +6954,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D102" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6987,7 +6990,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7007,13 +7010,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7043,7 +7046,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7063,13 +7066,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D104" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7099,7 +7102,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7119,13 +7122,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C105" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7155,7 +7158,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7175,13 +7178,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D106" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7202,7 +7205,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7211,7 +7214,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7231,13 +7234,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7267,7 +7270,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7287,13 +7290,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C108" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7323,7 +7326,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7343,13 +7346,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C109" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7370,7 +7373,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7379,7 +7382,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7399,13 +7402,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D110" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7435,7 +7438,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7455,13 +7458,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C111" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7491,7 +7494,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7511,13 +7514,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C112" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D112" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7547,7 +7550,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7567,13 +7570,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C113" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D113" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7603,7 +7606,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7623,13 +7626,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C114" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D114" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7659,7 +7662,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7679,13 +7682,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7715,7 +7718,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7735,13 +7738,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7771,7 +7774,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7791,13 +7794,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D117" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7827,7 +7830,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7847,13 +7850,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7883,7 +7886,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7906,13 +7909,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C119" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7942,7 +7945,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7962,13 +7965,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C120" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7998,7 +8001,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8018,13 +8021,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C121" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D121" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8054,7 +8057,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8074,13 +8077,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C122" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D122" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8110,7 +8113,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8130,13 +8133,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D123" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8157,7 +8160,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8166,7 +8169,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8186,13 +8189,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C124" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8222,7 +8225,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8242,13 +8245,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C125" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8278,7 +8281,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8298,13 +8301,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8334,7 +8337,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8357,13 +8360,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8393,7 +8396,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8413,13 +8416,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8449,7 +8452,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8472,13 +8475,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D129" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8508,7 +8511,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8528,13 +8531,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D130" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8564,7 +8567,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8584,13 +8587,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D131" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8620,7 +8623,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8640,13 +8643,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C132" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8676,7 +8679,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8696,13 +8699,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D133" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8723,7 +8726,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8732,7 +8735,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8752,13 +8755,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C134" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D134" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8788,7 +8791,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8808,13 +8811,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8844,7 +8847,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8864,13 +8867,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C136" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D136" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8900,7 +8903,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8920,13 +8923,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C137" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D137" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8956,7 +8959,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8979,13 +8982,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D138" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9015,7 +9018,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9035,13 +9038,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D139" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9071,7 +9074,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9091,13 +9094,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9127,7 +9130,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9147,13 +9150,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C141" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D141" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9183,7 +9186,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9203,13 +9206,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C142" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D142" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9239,7 +9242,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9259,13 +9262,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C143" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9295,7 +9298,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9315,13 +9318,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C144" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9351,7 +9354,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9371,13 +9374,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C145" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9407,7 +9410,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9427,13 +9430,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9463,7 +9466,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9486,13 +9489,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C147" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9522,7 +9525,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9545,13 +9548,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C148" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D148" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9581,7 +9584,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9604,13 +9607,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D149" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9631,7 +9634,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9640,7 +9643,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9663,13 +9666,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C150" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D150" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9699,7 +9702,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9722,13 +9725,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C151" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9758,7 +9761,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9778,13 +9781,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D152" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9814,7 +9817,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9837,13 +9840,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C153" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9873,7 +9876,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9896,13 +9899,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C154" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9932,7 +9935,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9947,7 +9950,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9955,13 +9958,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D155" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9991,7 +9994,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10014,13 +10017,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C156" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D156" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10050,7 +10053,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10070,13 +10073,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C157" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10106,7 +10109,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10126,13 +10129,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C158" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10162,7 +10165,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10182,13 +10185,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C159" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10218,7 +10221,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10241,13 +10244,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C160" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D160" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10277,7 +10280,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10297,13 +10300,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C161" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10333,7 +10336,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10356,13 +10359,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C162" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10392,7 +10395,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10412,13 +10415,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C163" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10448,7 +10451,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10471,13 +10474,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C164" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10498,7 +10501,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10507,7 +10510,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10530,13 +10533,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10557,7 +10560,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10566,7 +10569,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10586,13 +10589,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C166" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10622,7 +10625,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10645,13 +10648,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C167" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10681,7 +10684,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10701,13 +10704,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C168" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10737,7 +10740,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10757,13 +10760,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C169" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10793,7 +10796,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10816,13 +10819,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C170" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10852,7 +10855,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10875,13 +10878,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C171" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10911,7 +10914,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10931,13 +10934,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C172" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10967,7 +10970,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10990,13 +10993,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C173" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11026,7 +11029,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11046,13 +11049,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C174" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11082,7 +11085,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11105,13 +11108,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C175" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D175" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11141,7 +11144,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11161,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C176" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11197,7 +11200,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11217,13 +11220,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C177" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11253,7 +11256,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11276,13 +11279,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C178" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11303,7 +11306,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11312,7 +11315,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11332,13 +11335,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C179" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11368,7 +11371,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11388,13 +11391,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11424,7 +11427,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11444,13 +11447,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C181" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D181" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11480,7 +11483,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11500,13 +11503,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C182" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D182" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11536,7 +11539,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11559,13 +11562,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C183" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D183" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11595,7 +11598,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11615,13 +11618,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C184" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D184" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11651,7 +11654,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11674,13 +11677,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C185" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D185" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11710,7 +11713,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11730,13 +11733,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C186" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D186" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11757,7 +11760,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11766,7 +11769,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11786,13 +11789,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C187" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11813,7 +11816,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11822,7 +11825,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11845,13 +11848,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C188" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D188" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11872,7 +11875,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11881,7 +11884,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11901,13 +11904,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C189" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D189" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11937,7 +11940,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11957,13 +11960,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C190" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11993,7 +11996,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12013,13 +12016,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12040,7 +12043,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12049,7 +12052,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12064,7 +12067,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12072,13 +12075,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12108,7 +12111,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12128,13 +12131,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C193" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D193" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12164,7 +12167,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12184,13 +12187,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C194" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D194" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12211,7 +12214,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12220,7 +12223,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12240,13 +12243,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C195" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D195" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12276,7 +12279,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12291,7 +12294,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12299,13 +12302,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C196" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12335,7 +12338,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12358,13 +12361,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C197" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D197" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12385,7 +12388,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12394,7 +12397,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12414,13 +12417,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C198" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12450,7 +12453,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12470,13 +12473,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C199" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D199" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12506,7 +12509,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12526,13 +12529,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C200" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12562,7 +12565,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12582,13 +12585,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C201" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D201" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12618,7 +12621,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12638,13 +12641,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C202" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12674,7 +12677,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12694,13 +12697,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C203" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D203" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12730,7 +12733,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12745,7 +12748,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12753,13 +12756,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C204" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D204" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12789,7 +12792,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12809,13 +12812,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C205" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12845,7 +12848,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12865,13 +12868,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C206" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12901,7 +12904,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12921,13 +12924,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C207" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12957,7 +12960,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12980,13 +12983,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C208" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D208" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13016,7 +13019,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13036,13 +13039,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C209" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D209" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13072,7 +13075,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13092,13 +13095,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C210" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D210" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13119,7 +13122,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13128,7 +13131,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13148,13 +13151,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C211" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D211" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13184,7 +13187,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13204,13 +13207,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C212" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D212" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13240,7 +13243,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13260,13 +13263,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C213" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D213" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13296,7 +13299,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13316,13 +13319,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C214" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13352,7 +13355,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13367,7 +13370,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13375,13 +13378,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C215" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D215" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13411,7 +13414,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13431,13 +13434,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C216" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13467,7 +13470,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13487,13 +13490,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C217" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13523,7 +13526,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13543,13 +13546,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C218" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D218" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13579,7 +13582,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13599,13 +13602,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C219" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13635,7 +13638,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13655,13 +13658,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C220" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13682,7 +13685,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13691,7 +13694,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13711,13 +13714,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C221" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D221" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13738,7 +13741,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13747,7 +13750,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13767,13 +13770,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C222" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13803,7 +13806,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13823,13 +13826,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C223" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D223" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13850,7 +13853,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13859,7 +13862,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13879,13 +13882,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C224" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13915,7 +13918,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13935,13 +13938,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C225" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D225" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13971,7 +13974,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13991,13 +13994,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C226" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D226" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14027,7 +14030,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14047,13 +14050,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D227" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14083,7 +14086,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14103,13 +14106,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C228" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D228" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14139,7 +14142,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14159,13 +14162,13 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C229" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D229" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -14183,7 +14186,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8889</v>
+        <v>8860</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14195,13 +14198,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>598.5</v>
+        <v>569.5</v>
       </c>
       <c r="Q229">
-        <v>598.5</v>
+        <v>569.5</v>
       </c>
       <c r="R229">
-        <v>7.22</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14209,13 +14212,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C230" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D230" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14245,7 +14248,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14265,13 +14268,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C231" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D231" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14292,7 +14295,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14301,7 +14304,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14316,7 +14319,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14324,13 +14327,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C232" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D232" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14360,7 +14363,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14380,13 +14383,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C233" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D233" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14416,7 +14419,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14436,13 +14439,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C234" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14472,7 +14475,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14492,13 +14495,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C235" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D235" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14519,7 +14522,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14528,7 +14531,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14551,13 +14554,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C236" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D236" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14578,7 +14581,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14587,7 +14590,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14610,13 +14613,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C237" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14646,7 +14649,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14666,13 +14669,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C238" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14702,7 +14705,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14722,13 +14725,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C239" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D239" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14758,7 +14761,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14778,13 +14781,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C240" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D240" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14814,7 +14817,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14834,13 +14837,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C241" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D241" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14870,7 +14873,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14890,13 +14893,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C242" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14926,7 +14929,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14946,13 +14949,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C243" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D243" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14982,7 +14985,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -15005,13 +15008,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C244" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15041,7 +15044,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15056,7 +15059,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15064,13 +15067,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C245" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15091,7 +15094,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15100,7 +15103,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15120,13 +15123,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C246" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D246" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15156,7 +15159,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15176,13 +15179,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C247" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D247" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15212,7 +15215,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15232,13 +15235,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C248" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15268,7 +15271,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15288,13 +15291,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C249" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15324,7 +15327,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15344,13 +15347,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C250" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15380,7 +15383,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15400,13 +15403,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C251" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15436,7 +15439,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15456,13 +15459,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C252" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15492,7 +15495,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15515,13 +15518,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15551,7 +15554,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15571,13 +15574,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C254" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D254" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15595,7 +15598,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>726.8</v>
+        <v>711</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15607,13 +15610,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>276.5</v>
+        <v>55.3</v>
       </c>
       <c r="Q254">
-        <v>276.5</v>
+        <v>55.3</v>
       </c>
       <c r="R254">
-        <v>2.79</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15621,13 +15624,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C255" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15657,7 +15660,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15677,13 +15680,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C256" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15713,7 +15716,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15733,13 +15736,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C257" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D257" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15760,7 +15763,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15769,7 +15772,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15789,13 +15792,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C258" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D258" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15825,7 +15828,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15845,13 +15848,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C259" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D259" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15881,7 +15884,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15904,13 +15907,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C260" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D260" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15940,7 +15943,7 @@
         <v>1210.5</v>
       </c>
       <c r="N260" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O260">
         <v>-457.8000000000006</v>
@@ -15960,10 +15963,10 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C261" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D261" t="s">
         <v>260</v>
@@ -15978,7 +15981,7 @@
         <v>7</v>
       </c>
       <c r="H261">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I261">
         <v>9664.200000000001</v>
@@ -15986,23 +15989,29 @@
       <c r="J261">
         <v>1326.8</v>
       </c>
+      <c r="K261" t="s">
+        <v>165</v>
+      </c>
       <c r="L261">
         <v>1311.57</v>
       </c>
       <c r="M261">
-        <v>0</v>
+        <v>1311.57</v>
+      </c>
+      <c r="N261" t="s">
+        <v>279</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>-483.2099999999998</v>
       </c>
       <c r="P261">
-        <v>-376.6</v>
+        <v>0</v>
       </c>
       <c r="Q261">
-        <v>-376.6</v>
+        <v>-483.2099999999998</v>
       </c>
       <c r="R261">
-        <v>-3.9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="262" spans="1:19">
@@ -16010,13 +16019,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C262" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D262" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16046,7 +16055,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16069,13 +16078,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C263" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D263" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16105,7 +16114,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16125,13 +16134,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C264" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D264" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16161,7 +16170,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16184,13 +16193,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C265" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D265" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16220,7 +16229,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16243,13 +16252,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C266" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D266" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16279,7 +16288,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16299,13 +16308,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C267" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D267" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16335,7 +16344,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16355,13 +16364,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C268" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D268" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16391,7 +16400,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16411,13 +16420,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C269" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D269" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16447,7 +16456,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16467,13 +16476,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C270" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D270" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16503,7 +16512,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16523,13 +16532,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C271" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D271" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16559,7 +16568,7 @@
         <v>1511.73</v>
       </c>
       <c r="N271" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O271">
         <v>-477.4199999999996</v>
@@ -16579,13 +16588,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C272" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D272" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16615,7 +16624,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16635,13 +16644,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C273" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D273" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16671,7 +16680,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16691,13 +16700,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C274" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D274" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16718,7 +16727,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16727,7 +16736,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16747,13 +16756,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C275" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D275" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16783,7 +16792,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16803,13 +16812,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C276" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D276" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16839,7 +16848,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16859,13 +16868,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C277" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D277" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16895,7 +16904,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16915,13 +16924,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C278" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D278" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16951,7 +16960,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16971,13 +16980,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C279" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D279" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -17007,7 +17016,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17027,13 +17036,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C280" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D280" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17063,7 +17072,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17083,13 +17092,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C281" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D281" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17119,7 +17128,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17139,13 +17148,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C282" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D282" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17175,7 +17184,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17195,13 +17204,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C283" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D283" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17231,7 +17240,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17251,13 +17260,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C284" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D284" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17287,7 +17296,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17307,13 +17316,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C285" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D285" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17343,7 +17352,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17363,13 +17372,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C286" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D286" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17399,7 +17408,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17419,13 +17428,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C287" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D287" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17455,7 +17464,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17475,13 +17484,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C288" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D288" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17511,7 +17520,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17531,13 +17540,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C289" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D289" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17558,7 +17567,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17567,7 +17576,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17587,13 +17596,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C290" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D290" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17623,7 +17632,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17643,13 +17652,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C291" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D291" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17667,7 +17676,7 @@
         <v>9639</v>
       </c>
       <c r="J291">
-        <v>550.05</v>
+        <v>549.5</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17679,13 +17688,13 @@
         <v>0</v>
       </c>
       <c r="P291">
-        <v>-288.15</v>
+        <v>-297.5</v>
       </c>
       <c r="Q291">
-        <v>-288.15</v>
+        <v>-297.5</v>
       </c>
       <c r="R291">
-        <v>-2.99</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17693,13 +17702,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C292" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D292" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17720,7 +17729,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17729,7 +17738,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17749,13 +17758,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C293" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D293" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17785,7 +17794,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17805,13 +17814,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C294" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D294" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17841,7 +17850,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17864,13 +17873,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C295" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D295" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17900,7 +17909,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17920,13 +17929,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C296" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D296" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17956,7 +17965,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17976,13 +17985,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C297" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D297" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -18000,7 +18009,7 @@
         <v>9902.5</v>
       </c>
       <c r="J297">
-        <v>116.6</v>
+        <v>112.6</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -18012,13 +18021,13 @@
         <v>0</v>
       </c>
       <c r="P297">
-        <v>8.5</v>
+        <v>-331.5</v>
       </c>
       <c r="Q297">
-        <v>8.5</v>
+        <v>-331.5</v>
       </c>
       <c r="R297">
-        <v>0.09</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18026,13 +18035,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C298" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D298" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18062,7 +18071,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18082,13 +18091,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C299" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D299" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18118,7 +18127,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18138,13 +18147,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C300" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D300" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18174,7 +18183,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18194,13 +18203,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C301" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D301" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18230,7 +18239,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18250,13 +18259,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C302" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D302" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18286,7 +18295,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18306,13 +18315,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C303" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D303" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18333,7 +18342,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18342,7 +18351,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18362,13 +18371,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C304" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D304" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18398,7 +18407,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18418,13 +18427,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C305" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D305" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18454,7 +18463,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18474,13 +18483,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C306" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D306" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18510,7 +18519,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18530,13 +18539,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C307" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D307" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18566,7 +18575,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18586,13 +18595,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C308" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D308" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18622,7 +18631,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18642,13 +18651,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C309" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D309" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18669,7 +18678,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18678,7 +18687,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18698,13 +18707,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C310" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D310" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18734,7 +18743,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18754,13 +18763,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C311" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D311" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18790,7 +18799,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18810,13 +18819,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C312" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D312" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18846,7 +18855,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18866,13 +18875,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C313" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D313" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18902,7 +18911,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18922,13 +18931,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C314" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D314" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18958,7 +18967,7 @@
         <v>1003.11</v>
       </c>
       <c r="N314" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O314">
         <v>-475.1100000000007</v>
@@ -18978,13 +18987,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C315" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D315" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -19002,7 +19011,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4800</v>
+        <v>4738</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -19014,13 +19023,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>68.8</v>
+        <v>-55.2</v>
       </c>
       <c r="Q315">
-        <v>68.8</v>
+        <v>-55.2</v>
       </c>
       <c r="R315">
-        <v>0.72</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19028,13 +19037,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C316" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D316" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19052,7 +19061,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2916.5</v>
+        <v>2831.1</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19064,13 +19073,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-64.5</v>
+        <v>-320.7</v>
       </c>
       <c r="Q316">
-        <v>-64.5</v>
+        <v>-320.7</v>
       </c>
       <c r="R316">
-        <v>-0.73</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19078,13 +19087,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C317" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D317" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19102,7 +19111,7 @@
         <v>9879.700000000001</v>
       </c>
       <c r="J317">
-        <v>312.95</v>
+        <v>303.25</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19114,13 +19123,13 @@
         <v>0</v>
       </c>
       <c r="P317">
-        <v>-178.25</v>
+        <v>-478.95</v>
       </c>
       <c r="Q317">
-        <v>-178.25</v>
+        <v>-478.95</v>
       </c>
       <c r="R317">
-        <v>-1.8</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19128,13 +19137,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C318" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D318" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19155,7 +19164,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19164,7 +19173,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19184,13 +19193,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C319" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D319" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -19208,7 +19217,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="L319">
         <v>1086.99</v>
@@ -19220,13 +19229,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>454.4</v>
+        <v>614.4</v>
       </c>
       <c r="Q319">
-        <v>454.4</v>
+        <v>614.4</v>
       </c>
       <c r="R319">
-        <v>4.96</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19234,10 +19243,10 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C320" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D320" t="s">
         <v>260</v>
@@ -19252,7 +19261,7 @@
         <v>23</v>
       </c>
       <c r="H320">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I320">
         <v>9642.75</v>
@@ -19260,23 +19269,29 @@
       <c r="J320">
         <v>404</v>
       </c>
+      <c r="K320" t="s">
+        <v>165</v>
+      </c>
       <c r="L320">
         <v>398.29</v>
       </c>
       <c r="M320">
-        <v>0</v>
+        <v>398.29</v>
+      </c>
+      <c r="N320" t="s">
+        <v>279</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>-482.0799999999995</v>
       </c>
       <c r="P320">
-        <v>-350.75</v>
+        <v>0</v>
       </c>
       <c r="Q320">
-        <v>-350.75</v>
+        <v>-482.0799999999995</v>
       </c>
       <c r="R320">
-        <v>-3.64</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -19284,13 +19299,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C321" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D321" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19320,7 +19335,7 @@
         <v>2679</v>
       </c>
       <c r="N321" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O321">
         <v>-423</v>
@@ -19340,13 +19355,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C322" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D322" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19364,7 +19379,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1788</v>
+        <v>1743.7</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19376,13 +19391,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>65</v>
+        <v>-156.5</v>
       </c>
       <c r="Q322">
-        <v>65</v>
+        <v>-156.5</v>
       </c>
       <c r="R322">
-        <v>0.73</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19390,13 +19405,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C323" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D323" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19414,7 +19429,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1258</v>
+        <v>1252.6</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19426,13 +19441,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>225.6</v>
+        <v>182.4</v>
       </c>
       <c r="Q323">
-        <v>225.6</v>
+        <v>182.4</v>
       </c>
       <c r="R323">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19440,13 +19455,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C324" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D324" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19476,7 +19491,7 @@
         <v>447.45</v>
       </c>
       <c r="N324" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O324">
         <v>-494.5500000000002</v>
@@ -19496,13 +19511,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C325" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D325" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19532,7 +19547,7 @@
         <v>1001.97</v>
       </c>
       <c r="N325" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O325">
         <v>-474.5700000000002</v>
@@ -19552,13 +19567,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C326" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D326" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19576,7 +19591,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>165.71</v>
+        <v>162.37</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19588,13 +19603,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>476.28</v>
+        <v>265.86</v>
       </c>
       <c r="Q326">
-        <v>476.28</v>
+        <v>265.86</v>
       </c>
       <c r="R326">
-        <v>4.78</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19602,13 +19617,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C327" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D327" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19626,7 +19641,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1855.8</v>
+        <v>1845.9</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19638,13 +19653,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>177.5</v>
+        <v>128</v>
       </c>
       <c r="Q327">
-        <v>177.5</v>
+        <v>128</v>
       </c>
       <c r="R327">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19652,13 +19667,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C328" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D328" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19679,7 +19694,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19688,7 +19703,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19708,13 +19723,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C329" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D329" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -19732,7 +19747,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>335</v>
+        <v>330.95</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19744,13 +19759,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>612.25</v>
+        <v>486.7</v>
       </c>
       <c r="Q329">
-        <v>612.25</v>
+        <v>486.7</v>
       </c>
       <c r="R329">
-        <v>6.26</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19758,13 +19773,13 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C330" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D330" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -19782,7 +19797,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4884</v>
+        <v>4819.5</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19794,13 +19809,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>56</v>
+        <v>-73</v>
       </c>
       <c r="Q330">
-        <v>56</v>
+        <v>-73</v>
       </c>
       <c r="R330">
-        <v>0.58</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19808,13 +19823,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C331" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D331" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19832,7 +19847,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3191</v>
+        <v>3150</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19844,13 +19859,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>12</v>
+        <v>-111</v>
       </c>
       <c r="Q331">
-        <v>12</v>
+        <v>-111</v>
       </c>
       <c r="R331">
-        <v>0.13</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19858,10 +19873,10 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C332" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D332" t="s">
         <v>260</v>
@@ -19876,7 +19891,7 @@
         <v>8</v>
       </c>
       <c r="H332">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I332">
         <v>9059.200000000001</v>
@@ -19884,23 +19899,29 @@
       <c r="J332">
         <v>1096.5</v>
       </c>
+      <c r="K332" t="s">
+        <v>165</v>
+      </c>
       <c r="L332">
         <v>1075.78</v>
       </c>
       <c r="M332">
-        <v>0</v>
+        <v>1075.78</v>
+      </c>
+      <c r="N332" t="s">
+        <v>279</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>-452.9600000000009</v>
       </c>
       <c r="P332">
-        <v>-287.2</v>
+        <v>0</v>
       </c>
       <c r="Q332">
-        <v>-287.2</v>
+        <v>-452.9600000000009</v>
       </c>
       <c r="R332">
-        <v>-3.17</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -19908,13 +19929,13 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C333" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D333" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -19944,7 +19965,7 @@
         <v>1630</v>
       </c>
       <c r="N333" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O333">
         <v>-850</v>
@@ -19964,13 +19985,13 @@
         <v>161</v>
       </c>
       <c r="B334" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C334" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D334" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -19988,7 +20009,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1553.7</v>
+        <v>1540</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -20000,13 +20021,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>267.6</v>
+        <v>185.4</v>
       </c>
       <c r="Q334">
-        <v>267.6</v>
+        <v>185.4</v>
       </c>
       <c r="R334">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -20014,13 +20035,13 @@
         <v>161</v>
       </c>
       <c r="B335" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C335" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D335" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -20038,7 +20059,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>4937.5</v>
+        <v>4915</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -20050,13 +20071,13 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>-85.5</v>
+        <v>-108</v>
       </c>
       <c r="Q335">
-        <v>-85.5</v>
+        <v>-108</v>
       </c>
       <c r="R335">
-        <v>-1.7</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20064,13 +20085,13 @@
         <v>162</v>
       </c>
       <c r="B336" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C336" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D336" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -20088,7 +20109,7 @@
         <v>9654.75</v>
       </c>
       <c r="J336">
-        <v>458.35</v>
+        <v>452.85</v>
       </c>
       <c r="L336">
         <v>436.76</v>
@@ -20100,13 +20121,13 @@
         <v>0</v>
       </c>
       <c r="P336">
-        <v>-29.4</v>
+        <v>-144.9</v>
       </c>
       <c r="Q336">
-        <v>-29.4</v>
+        <v>-144.9</v>
       </c>
       <c r="R336">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -20114,13 +20135,13 @@
         <v>162</v>
       </c>
       <c r="B337" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C337" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D337" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -20138,7 +20159,7 @@
         <v>9402.4</v>
       </c>
       <c r="J337">
-        <v>1164.8</v>
+        <v>1139.6</v>
       </c>
       <c r="L337">
         <v>1116.53</v>
@@ -20150,13 +20171,13 @@
         <v>0</v>
       </c>
       <c r="P337">
-        <v>-84</v>
+        <v>-285.6</v>
       </c>
       <c r="Q337">
-        <v>-84</v>
+        <v>-285.6</v>
       </c>
       <c r="R337">
-        <v>-0.89</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -20164,13 +20185,13 @@
         <v>163</v>
       </c>
       <c r="B338" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C338" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D338" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -20188,7 +20209,7 @@
         <v>9894.4</v>
       </c>
       <c r="J338">
-        <v>611.2</v>
+        <v>591</v>
       </c>
       <c r="L338">
         <v>587.48</v>
@@ -20200,13 +20221,13 @@
         <v>0</v>
       </c>
       <c r="P338">
-        <v>-115.2</v>
+        <v>-438.4</v>
       </c>
       <c r="Q338">
-        <v>-115.2</v>
+        <v>-438.4</v>
       </c>
       <c r="R338">
-        <v>-1.16</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="339" spans="1:18">
@@ -20214,13 +20235,13 @@
         <v>164</v>
       </c>
       <c r="B339" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C339" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D339" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -20238,7 +20259,7 @@
         <v>9723</v>
       </c>
       <c r="J339">
-        <v>463</v>
+        <v>458.7</v>
       </c>
       <c r="L339">
         <v>439.85</v>
@@ -20250,12 +20271,62 @@
         <v>0</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>-90.3</v>
       </c>
       <c r="Q339">
-        <v>0</v>
+        <v>-90.3</v>
       </c>
       <c r="R339">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18">
+      <c r="A340" t="s">
+        <v>165</v>
+      </c>
+      <c r="B340" t="s">
+        <v>195</v>
+      </c>
+      <c r="C340" t="s">
+        <v>257</v>
+      </c>
+      <c r="D340" t="s">
+        <v>261</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>594.45</v>
+      </c>
+      <c r="G340">
+        <v>16</v>
+      </c>
+      <c r="H340">
+        <v>16</v>
+      </c>
+      <c r="I340">
+        <v>9511.200000000001</v>
+      </c>
+      <c r="J340">
+        <v>594.45</v>
+      </c>
+      <c r="L340">
+        <v>564.73</v>
+      </c>
+      <c r="M340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <v>0</v>
+      </c>
+      <c r="R340">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="286">
   <si>
     <t>Buy Date</t>
   </si>
@@ -848,6 +848,9 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
   </si>
   <si>
     <t>2026-09-22</t>
@@ -1345,7 +1348,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1401,7 +1404,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1460,7 +1463,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1516,7 +1519,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1572,7 +1575,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1628,7 +1631,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1684,7 +1687,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1740,7 +1743,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1796,7 +1799,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1852,7 +1855,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1911,7 +1914,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1970,7 +1973,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -2026,7 +2029,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2082,7 +2085,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2138,7 +2141,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2194,7 +2197,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2250,7 +2253,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2306,7 +2309,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2362,7 +2365,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2418,7 +2421,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2474,7 +2477,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2530,7 +2533,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2586,7 +2589,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2642,7 +2645,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2698,7 +2701,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2754,7 +2757,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2810,7 +2813,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2866,7 +2869,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2922,7 +2925,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2978,7 +2981,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -3034,7 +3037,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3090,7 +3093,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3146,7 +3149,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3202,7 +3205,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3258,7 +3261,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3314,7 +3317,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3370,7 +3373,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3429,7 +3432,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3485,7 +3488,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3541,7 +3544,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3597,7 +3600,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3653,7 +3656,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3709,7 +3712,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3765,7 +3768,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3821,7 +3824,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3880,7 +3883,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3936,7 +3939,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3992,7 +3995,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4051,7 +4054,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4107,7 +4110,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4163,7 +4166,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4222,7 +4225,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4278,7 +4281,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4337,7 +4340,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4396,7 +4399,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4452,7 +4455,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4508,7 +4511,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4564,7 +4567,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4623,7 +4626,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4679,7 +4682,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4738,7 +4741,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4753,7 +4756,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4797,7 +4800,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4853,7 +4856,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4909,7 +4912,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4965,7 +4968,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -5021,7 +5024,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5077,7 +5080,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5133,7 +5136,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5189,7 +5192,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5245,7 +5248,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5301,7 +5304,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5357,7 +5360,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5413,7 +5416,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5469,7 +5472,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5525,7 +5528,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5581,7 +5584,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5637,7 +5640,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5693,7 +5696,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5749,7 +5752,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5805,7 +5808,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5861,7 +5864,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5920,7 +5923,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5976,7 +5979,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -6032,7 +6035,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6088,7 +6091,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6144,7 +6147,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6200,7 +6203,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6256,7 +6259,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6312,7 +6315,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6368,7 +6371,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6427,7 +6430,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6483,7 +6486,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6539,7 +6542,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6595,7 +6598,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6651,7 +6654,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6707,7 +6710,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6763,7 +6766,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6822,7 +6825,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6878,7 +6881,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6934,7 +6937,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6990,7 +6993,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7046,7 +7049,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7102,7 +7105,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7158,7 +7161,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7214,7 +7217,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7270,7 +7273,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7326,7 +7329,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7382,7 +7385,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7438,7 +7441,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7494,7 +7497,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7550,7 +7553,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7606,7 +7609,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7662,7 +7665,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7718,7 +7721,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7774,7 +7777,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7830,7 +7833,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7886,7 +7889,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7945,7 +7948,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -8001,7 +8004,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8057,7 +8060,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8113,7 +8116,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8169,7 +8172,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8225,7 +8228,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8281,7 +8284,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8337,7 +8340,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8396,7 +8399,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8452,7 +8455,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8511,7 +8514,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8567,7 +8570,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8623,7 +8626,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8679,7 +8682,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8735,7 +8738,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8791,7 +8794,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8847,7 +8850,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8903,7 +8906,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8959,7 +8962,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -9018,7 +9021,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9074,7 +9077,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9130,7 +9133,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9186,7 +9189,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9242,7 +9245,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9298,7 +9301,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9354,7 +9357,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9410,7 +9413,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9466,7 +9469,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9525,7 +9528,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9584,7 +9587,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9643,7 +9646,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9702,7 +9705,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9761,7 +9764,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9817,7 +9820,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9876,7 +9879,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9935,7 +9938,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9950,7 +9953,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9994,7 +9997,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10053,7 +10056,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10109,7 +10112,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10165,7 +10168,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10221,7 +10224,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10280,7 +10283,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10336,7 +10339,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10395,7 +10398,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10451,7 +10454,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10510,7 +10513,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10569,7 +10572,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10625,7 +10628,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10684,7 +10687,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10740,7 +10743,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10796,7 +10799,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10855,7 +10858,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10914,7 +10917,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10970,7 +10973,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -11029,7 +11032,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11085,7 +11088,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11144,7 +11147,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11200,7 +11203,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11256,7 +11259,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11315,7 +11318,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11371,7 +11374,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11427,7 +11430,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11483,7 +11486,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11539,7 +11542,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11598,7 +11601,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11654,7 +11657,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11713,7 +11716,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11769,7 +11772,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11825,7 +11828,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11884,7 +11887,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11940,7 +11943,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11996,7 +11999,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12052,7 +12055,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12111,7 +12114,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12167,7 +12170,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12223,7 +12226,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12279,7 +12282,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12294,7 +12297,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12338,7 +12341,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12397,7 +12400,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12453,7 +12456,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12509,7 +12512,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12565,7 +12568,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12621,7 +12624,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12677,7 +12680,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12733,7 +12736,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12792,7 +12795,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12848,7 +12851,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12904,7 +12907,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12960,7 +12963,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -13019,7 +13022,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13075,7 +13078,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13131,7 +13134,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13187,7 +13190,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13243,7 +13246,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13299,7 +13302,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13355,7 +13358,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13414,7 +13417,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13470,7 +13473,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13526,7 +13529,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13582,7 +13585,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13638,7 +13641,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13694,7 +13697,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13750,7 +13753,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13806,7 +13809,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13862,7 +13865,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13918,7 +13921,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13974,7 +13977,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -14030,7 +14033,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14086,7 +14089,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14142,7 +14145,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14186,7 +14189,7 @@
         <v>8290.5</v>
       </c>
       <c r="J229">
-        <v>8860</v>
+        <v>8659</v>
       </c>
       <c r="L229">
         <v>8290.5</v>
@@ -14198,13 +14201,13 @@
         <v>0</v>
       </c>
       <c r="P229">
-        <v>569.5</v>
+        <v>368.5</v>
       </c>
       <c r="Q229">
-        <v>569.5</v>
+        <v>368.5</v>
       </c>
       <c r="R229">
-        <v>6.87</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14248,7 +14251,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14304,7 +14307,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14363,7 +14366,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14419,7 +14422,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14475,7 +14478,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14531,7 +14534,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14590,7 +14593,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14649,7 +14652,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14705,7 +14708,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14761,7 +14764,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14817,7 +14820,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14873,7 +14876,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14929,7 +14932,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14985,7 +14988,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -15044,7 +15047,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15059,7 +15062,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15103,7 +15106,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15159,7 +15162,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15215,7 +15218,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15271,7 +15274,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15327,7 +15330,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15383,7 +15386,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15439,7 +15442,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15495,7 +15498,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15554,7 +15557,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15598,7 +15601,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>711</v>
+        <v>714.35</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15610,13 +15613,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>55.3</v>
+        <v>102.2</v>
       </c>
       <c r="Q254">
-        <v>55.3</v>
+        <v>102.2</v>
       </c>
       <c r="R254">
-        <v>0.5600000000000001</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15660,7 +15663,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15716,7 +15719,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15772,7 +15775,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15828,7 +15831,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15884,7 +15887,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15943,7 +15946,7 @@
         <v>1210.5</v>
       </c>
       <c r="N260" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O260">
         <v>-457.8000000000006</v>
@@ -15999,7 +16002,7 @@
         <v>1311.57</v>
       </c>
       <c r="N261" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O261">
         <v>-483.2099999999998</v>
@@ -16055,7 +16058,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16114,7 +16117,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16170,7 +16173,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16229,7 +16232,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16288,7 +16291,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16344,7 +16347,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16400,7 +16403,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16456,7 +16459,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16512,7 +16515,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16568,7 +16571,7 @@
         <v>1511.73</v>
       </c>
       <c r="N271" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O271">
         <v>-477.4199999999996</v>
@@ -16624,7 +16627,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16680,7 +16683,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16736,7 +16739,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16792,7 +16795,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16848,7 +16851,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16904,7 +16907,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16960,7 +16963,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -17016,7 +17019,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17072,7 +17075,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17128,7 +17131,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17184,7 +17187,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17240,7 +17243,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17296,7 +17299,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17352,7 +17355,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17408,7 +17411,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17464,7 +17467,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17520,7 +17523,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17576,7 +17579,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17632,7 +17635,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17658,7 +17661,7 @@
         <v>257</v>
       </c>
       <c r="D291" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17670,7 +17673,7 @@
         <v>17</v>
       </c>
       <c r="H291">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I291">
         <v>9639</v>
@@ -17678,23 +17681,29 @@
       <c r="J291">
         <v>549.5</v>
       </c>
+      <c r="K291" t="s">
+        <v>278</v>
+      </c>
       <c r="L291">
         <v>538.65</v>
       </c>
       <c r="M291">
-        <v>0</v>
+        <v>538.65</v>
+      </c>
+      <c r="N291" t="s">
+        <v>280</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>-481.9500000000004</v>
       </c>
       <c r="P291">
-        <v>-297.5</v>
+        <v>0</v>
       </c>
       <c r="Q291">
-        <v>-297.5</v>
+        <v>-481.9500000000004</v>
       </c>
       <c r="R291">
-        <v>-3.09</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="292" spans="1:19">
@@ -17738,7 +17747,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17794,7 +17803,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17850,7 +17859,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17909,7 +17918,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17965,7 +17974,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17991,7 +18000,7 @@
         <v>259</v>
       </c>
       <c r="D297" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -18003,7 +18012,7 @@
         <v>85</v>
       </c>
       <c r="H297">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I297">
         <v>9902.5</v>
@@ -18011,23 +18020,29 @@
       <c r="J297">
         <v>112.6</v>
       </c>
+      <c r="K297" t="s">
+        <v>278</v>
+      </c>
       <c r="L297">
         <v>110.67</v>
       </c>
       <c r="M297">
-        <v>0</v>
+        <v>110.67</v>
+      </c>
+      <c r="N297" t="s">
+        <v>280</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>-495.5499999999998</v>
       </c>
       <c r="P297">
-        <v>-331.5</v>
+        <v>0</v>
       </c>
       <c r="Q297">
-        <v>-331.5</v>
+        <v>-495.5499999999998</v>
       </c>
       <c r="R297">
-        <v>-3.35</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="298" spans="1:19">
@@ -18071,7 +18086,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18127,7 +18142,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18183,7 +18198,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18239,7 +18254,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18295,7 +18310,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18351,7 +18366,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18407,7 +18422,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18463,7 +18478,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18519,7 +18534,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18575,7 +18590,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18631,7 +18646,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18687,7 +18702,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18743,7 +18758,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18799,7 +18814,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18855,7 +18870,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18911,7 +18926,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18967,7 +18982,7 @@
         <v>1003.11</v>
       </c>
       <c r="N314" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O314">
         <v>-475.1100000000007</v>
@@ -19011,7 +19026,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4738</v>
+        <v>4549.3</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -19023,13 +19038,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>-55.2</v>
+        <v>-432.6</v>
       </c>
       <c r="Q315">
-        <v>-55.2</v>
+        <v>-432.6</v>
       </c>
       <c r="R315">
-        <v>-0.58</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19061,7 +19076,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2831.1</v>
+        <v>2972.9</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19073,13 +19088,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>-320.7</v>
+        <v>104.7</v>
       </c>
       <c r="Q316">
-        <v>-320.7</v>
+        <v>104.7</v>
       </c>
       <c r="R316">
-        <v>-3.64</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19093,7 +19108,7 @@
         <v>257</v>
       </c>
       <c r="D317" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19105,7 +19120,7 @@
         <v>31</v>
       </c>
       <c r="H317">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I317">
         <v>9879.700000000001</v>
@@ -19113,23 +19128,29 @@
       <c r="J317">
         <v>303.25</v>
       </c>
+      <c r="K317" t="s">
+        <v>278</v>
+      </c>
       <c r="L317">
         <v>302.76</v>
       </c>
       <c r="M317">
-        <v>0</v>
+        <v>302.2</v>
+      </c>
+      <c r="N317" t="s">
+        <v>281</v>
       </c>
       <c r="O317">
-        <v>0</v>
+        <v>-511.5</v>
       </c>
       <c r="P317">
-        <v>-478.95</v>
+        <v>0</v>
       </c>
       <c r="Q317">
-        <v>-478.95</v>
+        <v>-511.5</v>
       </c>
       <c r="R317">
-        <v>-4.85</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -19173,7 +19194,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19202,7 +19223,7 @@
         <v>261</v>
       </c>
       <c r="E319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F319">
         <v>1144.2</v>
@@ -19217,10 +19238,10 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1221</v>
+        <v>1251.9</v>
       </c>
       <c r="L319">
-        <v>1086.99</v>
+        <v>1144.2</v>
       </c>
       <c r="M319">
         <v>0</v>
@@ -19229,13 +19250,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>614.4</v>
+        <v>861.6</v>
       </c>
       <c r="Q319">
-        <v>614.4</v>
+        <v>861.6</v>
       </c>
       <c r="R319">
-        <v>6.71</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19279,7 +19300,7 @@
         <v>398.29</v>
       </c>
       <c r="N320" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O320">
         <v>-482.0799999999995</v>
@@ -19335,7 +19356,7 @@
         <v>2679</v>
       </c>
       <c r="N321" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O321">
         <v>-423</v>
@@ -19379,7 +19400,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1743.7</v>
+        <v>1822</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19391,13 +19412,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>-156.5</v>
+        <v>235</v>
       </c>
       <c r="Q322">
-        <v>-156.5</v>
+        <v>235</v>
       </c>
       <c r="R322">
-        <v>-1.76</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19429,7 +19450,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1252.6</v>
+        <v>1222</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19441,13 +19462,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>182.4</v>
+        <v>-62.4</v>
       </c>
       <c r="Q323">
-        <v>182.4</v>
+        <v>-62.4</v>
       </c>
       <c r="R323">
-        <v>1.85</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19491,7 +19512,7 @@
         <v>447.45</v>
       </c>
       <c r="N324" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O324">
         <v>-494.5500000000002</v>
@@ -19547,7 +19568,7 @@
         <v>1001.97</v>
       </c>
       <c r="N325" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O325">
         <v>-474.5700000000002</v>
@@ -19591,7 +19612,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>162.37</v>
+        <v>158.56</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19603,13 +19624,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>265.86</v>
+        <v>25.83</v>
       </c>
       <c r="Q326">
-        <v>265.86</v>
+        <v>25.83</v>
       </c>
       <c r="R326">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19641,7 +19662,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1845.9</v>
+        <v>1785.1</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19653,13 +19674,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>128</v>
+        <v>-176</v>
       </c>
       <c r="Q327">
-        <v>128</v>
+        <v>-176</v>
       </c>
       <c r="R327">
-        <v>1.41</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19694,7 +19715,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19703,7 +19724,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19747,7 +19768,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>330.95</v>
+        <v>327.85</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19759,13 +19780,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>486.7</v>
+        <v>390.6</v>
       </c>
       <c r="Q329">
-        <v>486.7</v>
+        <v>390.6</v>
       </c>
       <c r="R329">
-        <v>4.98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19797,7 +19818,7 @@
         <v>9712</v>
       </c>
       <c r="J330">
-        <v>4819.5</v>
+        <v>4675</v>
       </c>
       <c r="L330">
         <v>4613.2</v>
@@ -19809,13 +19830,13 @@
         <v>0</v>
       </c>
       <c r="P330">
-        <v>-73</v>
+        <v>-362</v>
       </c>
       <c r="Q330">
-        <v>-73</v>
+        <v>-362</v>
       </c>
       <c r="R330">
-        <v>-0.75</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19847,7 +19868,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19859,13 +19880,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-111</v>
+        <v>-261</v>
       </c>
       <c r="Q331">
-        <v>-111</v>
+        <v>-261</v>
       </c>
       <c r="R331">
-        <v>-1.16</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19909,7 +19930,7 @@
         <v>1075.78</v>
       </c>
       <c r="N332" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O332">
         <v>-452.9600000000009</v>
@@ -19965,7 +19986,7 @@
         <v>1630</v>
       </c>
       <c r="N333" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O333">
         <v>-850</v>
@@ -20009,7 +20030,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1540</v>
+        <v>1515</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -20021,13 +20042,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>185.4</v>
+        <v>35.4</v>
       </c>
       <c r="Q334">
-        <v>185.4</v>
+        <v>35.4</v>
       </c>
       <c r="R334">
-        <v>2.05</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -20059,7 +20080,7 @@
         <v>5023</v>
       </c>
       <c r="J335">
-        <v>4915</v>
+        <v>4835</v>
       </c>
       <c r="L335">
         <v>4771.85</v>
@@ -20071,13 +20092,13 @@
         <v>0</v>
       </c>
       <c r="P335">
-        <v>-108</v>
+        <v>-188</v>
       </c>
       <c r="Q335">
-        <v>-108</v>
+        <v>-188</v>
       </c>
       <c r="R335">
-        <v>-2.15</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20109,7 +20130,7 @@
         <v>9654.75</v>
       </c>
       <c r="J336">
-        <v>452.85</v>
+        <v>448.2</v>
       </c>
       <c r="L336">
         <v>436.76</v>
@@ -20121,13 +20142,13 @@
         <v>0</v>
       </c>
       <c r="P336">
-        <v>-144.9</v>
+        <v>-242.55</v>
       </c>
       <c r="Q336">
-        <v>-144.9</v>
+        <v>-242.55</v>
       </c>
       <c r="R336">
-        <v>-1.5</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -20159,7 +20180,7 @@
         <v>9402.4</v>
       </c>
       <c r="J337">
-        <v>1139.6</v>
+        <v>1130</v>
       </c>
       <c r="L337">
         <v>1116.53</v>
@@ -20171,13 +20192,13 @@
         <v>0</v>
       </c>
       <c r="P337">
-        <v>-285.6</v>
+        <v>-362.4</v>
       </c>
       <c r="Q337">
-        <v>-285.6</v>
+        <v>-362.4</v>
       </c>
       <c r="R337">
-        <v>-3.04</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -20191,7 +20212,7 @@
         <v>257</v>
       </c>
       <c r="D338" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -20203,7 +20224,7 @@
         <v>16</v>
       </c>
       <c r="H338">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I338">
         <v>9894.4</v>
@@ -20211,23 +20232,29 @@
       <c r="J338">
         <v>591</v>
       </c>
+      <c r="K338" t="s">
+        <v>278</v>
+      </c>
       <c r="L338">
         <v>587.48</v>
       </c>
       <c r="M338">
-        <v>0</v>
+        <v>587.48</v>
+      </c>
+      <c r="N338" t="s">
+        <v>280</v>
       </c>
       <c r="O338">
-        <v>0</v>
+        <v>-494.7199999999993</v>
       </c>
       <c r="P338">
-        <v>-438.4</v>
+        <v>0</v>
       </c>
       <c r="Q338">
-        <v>-438.4</v>
+        <v>-494.7199999999993</v>
       </c>
       <c r="R338">
-        <v>-4.43</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="339" spans="1:18">
@@ -20259,7 +20286,7 @@
         <v>9723</v>
       </c>
       <c r="J339">
-        <v>458.7</v>
+        <v>444.55</v>
       </c>
       <c r="L339">
         <v>439.85</v>
@@ -20271,13 +20298,13 @@
         <v>0</v>
       </c>
       <c r="P339">
-        <v>-90.3</v>
+        <v>-387.45</v>
       </c>
       <c r="Q339">
-        <v>-90.3</v>
+        <v>-387.45</v>
       </c>
       <c r="R339">
-        <v>-0.93</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="340" spans="1:18">
@@ -20309,7 +20336,7 @@
         <v>9511.200000000001</v>
       </c>
       <c r="J340">
-        <v>594.45</v>
+        <v>588.4</v>
       </c>
       <c r="L340">
         <v>564.73</v>
@@ -20321,13 +20348,13 @@
         <v>0</v>
       </c>
       <c r="P340">
-        <v>0</v>
+        <v>-96.8</v>
       </c>
       <c r="Q340">
-        <v>0</v>
+        <v>-96.8</v>
       </c>
       <c r="R340">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="287">
   <si>
     <t>Buy Date</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1235,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S340"/>
+  <dimension ref="A1:S341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1312,13 +1315,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1348,7 +1351,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1368,13 +1371,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1404,7 +1407,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1427,13 +1430,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1463,7 +1466,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1483,13 +1486,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1519,7 +1522,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1539,13 +1542,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1575,7 +1578,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1595,13 +1598,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1631,7 +1634,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1651,13 +1654,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1687,7 +1690,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1707,13 +1710,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1743,7 +1746,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1763,13 +1766,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1799,7 +1802,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1819,13 +1822,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1846,7 +1849,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1855,7 +1858,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1870,7 +1873,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1878,13 +1881,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1914,7 +1917,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1937,13 +1940,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1973,7 +1976,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1993,13 +1996,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2029,7 +2032,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2049,13 +2052,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2085,7 +2088,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2105,13 +2108,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2141,7 +2144,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2161,13 +2164,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2197,7 +2200,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2217,13 +2220,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2253,7 +2256,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2273,13 +2276,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2309,7 +2312,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2329,13 +2332,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2365,7 +2368,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2385,13 +2388,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2412,7 +2415,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2421,7 +2424,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2441,13 +2444,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2468,7 +2471,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2477,7 +2480,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2497,13 +2500,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2533,7 +2536,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2553,13 +2556,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2589,7 +2592,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2609,13 +2612,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2645,7 +2648,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2665,13 +2668,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2692,7 +2695,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2701,7 +2704,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2721,13 +2724,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2757,7 +2760,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2777,13 +2780,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2813,7 +2816,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2833,13 +2836,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2869,7 +2872,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2889,13 +2892,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2925,7 +2928,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2945,13 +2948,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2972,7 +2975,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2981,7 +2984,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -3001,13 +3004,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3037,7 +3040,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3057,13 +3060,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3093,7 +3096,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3113,13 +3116,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3140,7 +3143,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3149,7 +3152,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3169,13 +3172,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3196,7 +3199,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3205,7 +3208,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3225,13 +3228,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3261,7 +3264,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3281,13 +3284,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3317,7 +3320,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3337,13 +3340,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3373,7 +3376,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3396,13 +3399,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3432,7 +3435,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3452,13 +3455,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D40" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3488,7 +3491,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3508,13 +3511,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3544,7 +3547,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3564,13 +3567,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3591,7 +3594,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3600,7 +3603,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3620,13 +3623,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3647,7 +3650,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3656,7 +3659,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3676,13 +3679,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3712,7 +3715,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3732,13 +3735,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3768,7 +3771,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3788,13 +3791,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3824,7 +3827,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3847,13 +3850,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D47" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3883,7 +3886,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3903,13 +3906,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3939,7 +3942,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3959,13 +3962,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D49" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3995,7 +3998,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4018,13 +4021,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4054,7 +4057,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4074,13 +4077,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C51" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4110,7 +4113,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4130,13 +4133,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C52" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D52" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4166,7 +4169,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4189,13 +4192,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4225,7 +4228,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4245,13 +4248,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D54" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4281,7 +4284,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4304,13 +4307,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4340,7 +4343,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4363,13 +4366,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4399,7 +4402,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4419,13 +4422,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D57" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4446,7 +4449,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4455,7 +4458,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4475,13 +4478,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D58" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4511,7 +4514,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4531,13 +4534,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4567,7 +4570,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4590,13 +4593,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D60" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4626,7 +4629,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4646,13 +4649,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4682,7 +4685,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4705,13 +4708,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D62" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4741,7 +4744,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4756,7 +4759,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4764,13 +4767,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4800,7 +4803,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4820,13 +4823,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4856,7 +4859,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4876,13 +4879,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4912,7 +4915,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4932,13 +4935,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D66" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4968,7 +4971,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4988,13 +4991,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5024,7 +5027,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5044,13 +5047,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5080,7 +5083,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5100,13 +5103,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5127,7 +5130,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5136,7 +5139,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5156,13 +5159,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D70" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5192,7 +5195,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5212,13 +5215,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D71" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5248,7 +5251,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5268,13 +5271,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D72" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5304,7 +5307,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5324,13 +5327,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5360,7 +5363,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5380,13 +5383,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D74" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5416,7 +5419,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5436,13 +5439,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5472,7 +5475,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5492,13 +5495,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5528,7 +5531,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5548,13 +5551,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5584,7 +5587,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5604,13 +5607,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5640,7 +5643,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5660,13 +5663,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D79" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5696,7 +5699,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5716,13 +5719,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D80" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5752,7 +5755,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5772,13 +5775,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5808,7 +5811,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5828,13 +5831,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C82" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5864,7 +5867,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5887,13 +5890,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5923,7 +5926,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5943,13 +5946,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5979,7 +5982,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5999,13 +6002,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6035,7 +6038,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6055,13 +6058,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6091,7 +6094,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6111,13 +6114,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D87" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6147,7 +6150,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6167,13 +6170,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6203,7 +6206,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6223,13 +6226,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C89" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6259,7 +6262,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6279,13 +6282,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6315,7 +6318,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6335,13 +6338,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6371,7 +6374,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6394,13 +6397,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6430,7 +6433,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6450,13 +6453,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D93" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6486,7 +6489,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6506,13 +6509,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6542,7 +6545,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6562,13 +6565,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6598,7 +6601,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6618,13 +6621,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C96" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D96" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6654,7 +6657,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6674,13 +6677,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C97" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D97" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6710,7 +6713,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6730,13 +6733,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D98" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6766,7 +6769,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6789,13 +6792,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6825,7 +6828,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6845,13 +6848,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D100" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6881,7 +6884,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6901,13 +6904,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6937,7 +6940,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6957,13 +6960,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D102" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6993,7 +6996,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7013,13 +7016,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7049,7 +7052,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7069,13 +7072,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C104" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D104" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7105,7 +7108,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7125,13 +7128,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D105" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7161,7 +7164,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7181,13 +7184,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7208,7 +7211,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7217,7 +7220,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7237,13 +7240,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D107" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7273,7 +7276,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7293,13 +7296,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C108" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7329,7 +7332,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7349,13 +7352,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C109" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7376,7 +7379,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7385,7 +7388,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7405,13 +7408,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C110" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7441,7 +7444,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7461,13 +7464,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7497,7 +7500,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7517,13 +7520,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C112" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D112" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7553,7 +7556,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7573,13 +7576,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C113" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7609,7 +7612,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7629,13 +7632,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C114" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D114" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7665,7 +7668,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7685,13 +7688,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D115" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7721,7 +7724,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7741,13 +7744,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C116" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7777,7 +7780,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7797,13 +7800,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C117" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D117" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7833,7 +7836,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7853,13 +7856,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C118" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7889,7 +7892,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7912,13 +7915,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7948,7 +7951,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7968,13 +7971,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C120" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -8004,7 +8007,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8024,13 +8027,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C121" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D121" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8060,7 +8063,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8080,13 +8083,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C122" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D122" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8116,7 +8119,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8136,13 +8139,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C123" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D123" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8163,7 +8166,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8172,7 +8175,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8192,13 +8195,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C124" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D124" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8228,7 +8231,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8248,13 +8251,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D125" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8284,7 +8287,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8304,13 +8307,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D126" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8340,7 +8343,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8363,13 +8366,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8399,7 +8402,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8419,13 +8422,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C128" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8455,7 +8458,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8478,13 +8481,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D129" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8514,7 +8517,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8534,13 +8537,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D130" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8570,7 +8573,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8590,13 +8593,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C131" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D131" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8626,7 +8629,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8646,13 +8649,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D132" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8682,7 +8685,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8702,13 +8705,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C133" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D133" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8729,7 +8732,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8738,7 +8741,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8758,13 +8761,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D134" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8794,7 +8797,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8814,13 +8817,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D135" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8850,7 +8853,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8870,13 +8873,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8906,7 +8909,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8926,13 +8929,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C137" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8962,7 +8965,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8985,13 +8988,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D138" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9021,7 +9024,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9041,13 +9044,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C139" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D139" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9077,7 +9080,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9097,13 +9100,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D140" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9133,7 +9136,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9153,13 +9156,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C141" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9189,7 +9192,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9209,13 +9212,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C142" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D142" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9245,7 +9248,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9265,13 +9268,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D143" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9301,7 +9304,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9321,13 +9324,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D144" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9357,7 +9360,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9377,13 +9380,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D145" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9413,7 +9416,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9433,13 +9436,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D146" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9469,7 +9472,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9492,13 +9495,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C147" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D147" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9528,7 +9531,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9551,13 +9554,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C148" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D148" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9587,7 +9590,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9610,13 +9613,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C149" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9637,7 +9640,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9646,7 +9649,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9669,13 +9672,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C150" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D150" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9705,7 +9708,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9728,13 +9731,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C151" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D151" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9764,7 +9767,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9784,13 +9787,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9820,7 +9823,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9843,13 +9846,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D153" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9879,7 +9882,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9902,13 +9905,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C154" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9938,7 +9941,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9953,7 +9956,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9961,13 +9964,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C155" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D155" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9997,7 +10000,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10020,13 +10023,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D156" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10056,7 +10059,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10076,13 +10079,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C157" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D157" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10112,7 +10115,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10132,13 +10135,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10168,7 +10171,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10188,13 +10191,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D159" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10224,7 +10227,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10247,13 +10250,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C160" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D160" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10283,7 +10286,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10303,13 +10306,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D161" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10339,7 +10342,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10362,13 +10365,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D162" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10398,7 +10401,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10418,13 +10421,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D163" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10454,7 +10457,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10477,13 +10480,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D164" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10504,7 +10507,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10513,7 +10516,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10536,13 +10539,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C165" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D165" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10563,7 +10566,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10572,7 +10575,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10592,13 +10595,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C166" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D166" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10628,7 +10631,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10651,13 +10654,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10687,7 +10690,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10707,13 +10710,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C168" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D168" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10743,7 +10746,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10763,13 +10766,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C169" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D169" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10799,7 +10802,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10822,13 +10825,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D170" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10858,7 +10861,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10881,13 +10884,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D171" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10917,7 +10920,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10937,13 +10940,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C172" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D172" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10973,7 +10976,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10996,13 +10999,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D173" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11032,7 +11035,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11052,13 +11055,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D174" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11088,7 +11091,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11111,13 +11114,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C175" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D175" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11147,7 +11150,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11167,13 +11170,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D176" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11203,7 +11206,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11223,13 +11226,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D177" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11259,7 +11262,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11282,13 +11285,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D178" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11309,7 +11312,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11318,7 +11321,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11338,13 +11341,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D179" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11374,7 +11377,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11394,13 +11397,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D180" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11430,7 +11433,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11450,13 +11453,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D181" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11486,7 +11489,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11506,13 +11509,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C182" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D182" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11542,7 +11545,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11565,13 +11568,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C183" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D183" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11601,7 +11604,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11621,13 +11624,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D184" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11657,7 +11660,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11680,13 +11683,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D185" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11716,7 +11719,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11736,13 +11739,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D186" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11763,7 +11766,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11772,7 +11775,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11792,13 +11795,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D187" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11819,7 +11822,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11828,7 +11831,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11851,13 +11854,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C188" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D188" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11878,7 +11881,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11887,7 +11890,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11907,13 +11910,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C189" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D189" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11943,7 +11946,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11963,13 +11966,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D190" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -11999,7 +12002,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12019,13 +12022,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D191" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12046,7 +12049,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12055,7 +12058,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12070,7 +12073,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12078,13 +12081,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D192" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12114,7 +12117,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12134,13 +12137,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C193" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D193" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12170,7 +12173,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12190,13 +12193,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C194" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12217,7 +12220,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12226,7 +12229,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12246,13 +12249,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C195" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D195" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12282,7 +12285,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12297,7 +12300,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12305,13 +12308,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D196" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12341,7 +12344,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12364,13 +12367,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C197" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D197" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12391,7 +12394,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12400,7 +12403,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12420,13 +12423,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D198" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12456,7 +12459,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12476,13 +12479,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C199" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D199" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12512,7 +12515,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12532,13 +12535,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D200" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12568,7 +12571,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12588,13 +12591,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C201" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12624,7 +12627,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12644,13 +12647,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D202" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12680,7 +12683,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12700,13 +12703,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C203" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D203" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12736,7 +12739,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12751,7 +12754,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12759,13 +12762,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C204" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D204" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12795,7 +12798,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12815,13 +12818,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12851,7 +12854,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12871,13 +12874,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D206" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12907,7 +12910,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12927,13 +12930,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C207" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D207" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12963,7 +12966,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12986,13 +12989,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C208" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D208" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13022,7 +13025,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13042,13 +13045,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D209" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13078,7 +13081,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13098,13 +13101,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C210" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D210" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13125,7 +13128,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13134,7 +13137,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13154,13 +13157,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C211" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D211" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13190,7 +13193,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13210,13 +13213,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D212" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13246,7 +13249,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13266,13 +13269,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C213" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D213" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13302,7 +13305,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13322,13 +13325,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C214" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D214" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13358,7 +13361,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13373,7 +13376,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13381,13 +13384,13 @@
         <v>94</v>
       </c>
       <c r="B215" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D215" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13417,7 +13420,7 @@
         <v>424.51</v>
       </c>
       <c r="N215" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O215">
         <v>-491.4800000000007</v>
@@ -13437,13 +13440,13 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C216" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D216" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13473,7 +13476,7 @@
         <v>7043.3</v>
       </c>
       <c r="N216" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O216">
         <v>-370.6999999999998</v>
@@ -13493,13 +13496,13 @@
         <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C217" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D217" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13529,7 +13532,7 @@
         <v>416.8</v>
       </c>
       <c r="N217" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O217">
         <v>-485.1000000000003</v>
@@ -13549,13 +13552,13 @@
         <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C218" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D218" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13585,7 +13588,7 @@
         <v>2706.55</v>
       </c>
       <c r="N218" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O218">
         <v>-427.3499999999995</v>
@@ -13605,13 +13608,13 @@
         <v>96</v>
       </c>
       <c r="B219" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C219" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D219" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -13641,7 +13644,7 @@
         <v>961.21</v>
       </c>
       <c r="N219" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O219">
         <v>-455.3099999999993</v>
@@ -13661,13 +13664,13 @@
         <v>97</v>
       </c>
       <c r="B220" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C220" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D220" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -13688,7 +13691,7 @@
         <v>3953.2</v>
       </c>
       <c r="K220" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L220">
         <v>3872.67</v>
@@ -13697,7 +13700,7 @@
         <v>3872.67</v>
       </c>
       <c r="N220" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O220">
         <v>-407.6599999999999</v>
@@ -13717,13 +13720,13 @@
         <v>97</v>
       </c>
       <c r="B221" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C221" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D221" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13744,7 +13747,7 @@
         <v>526.35</v>
       </c>
       <c r="K221" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L221">
         <v>511.77</v>
@@ -13753,7 +13756,7 @@
         <v>511.77</v>
       </c>
       <c r="N221" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O221">
         <v>-484.7400000000012</v>
@@ -13773,13 +13776,13 @@
         <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D222" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -13809,7 +13812,7 @@
         <v>501.6</v>
       </c>
       <c r="N222" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O222">
         <v>-475.1999999999996</v>
@@ -13829,13 +13832,13 @@
         <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C223" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D223" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13856,7 +13859,7 @@
         <v>575.3</v>
       </c>
       <c r="K223" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L223">
         <v>565.0599999999999</v>
@@ -13865,7 +13868,7 @@
         <v>565.0599999999999</v>
       </c>
       <c r="N223" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O223">
         <v>-475.8400000000001</v>
@@ -13885,13 +13888,13 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D224" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -13921,7 +13924,7 @@
         <v>141.77</v>
       </c>
       <c r="N224" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O224">
         <v>0</v>
@@ -13941,13 +13944,13 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D225" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -13977,7 +13980,7 @@
         <v>448.97</v>
       </c>
       <c r="N225" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O225">
         <v>-496.2299999999999</v>
@@ -13997,13 +14000,13 @@
         <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C226" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D226" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -14033,7 +14036,7 @@
         <v>1143.23</v>
       </c>
       <c r="N226" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O226">
         <v>-481.3600000000006</v>
@@ -14053,13 +14056,13 @@
         <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C227" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D227" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E227">
         <v>2</v>
@@ -14089,7 +14092,7 @@
         <v>2098.74</v>
       </c>
       <c r="N227" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O227">
         <v>499.7000000000014</v>
@@ -14109,13 +14112,13 @@
         <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D228" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -14145,7 +14148,7 @@
         <v>551.1900000000001</v>
       </c>
       <c r="N228" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O228">
         <v>-493.1699999999999</v>
@@ -14165,10 +14168,10 @@
         <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D229" t="s">
         <v>261</v>
@@ -14183,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="H229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229">
         <v>8290.5</v>
@@ -14191,23 +14194,29 @@
       <c r="J229">
         <v>8659</v>
       </c>
+      <c r="K229" t="s">
+        <v>166</v>
+      </c>
       <c r="L229">
         <v>8290.5</v>
       </c>
       <c r="M229">
-        <v>0</v>
+        <v>8290.5</v>
+      </c>
+      <c r="N229" t="s">
+        <v>281</v>
       </c>
       <c r="O229">
         <v>0</v>
       </c>
       <c r="P229">
-        <v>368.5</v>
+        <v>0</v>
       </c>
       <c r="Q229">
-        <v>368.5</v>
+        <v>0</v>
       </c>
       <c r="R229">
-        <v>4.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -14215,13 +14224,13 @@
         <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C230" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D230" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -14251,7 +14260,7 @@
         <v>403.42</v>
       </c>
       <c r="N230" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O230">
         <v>-488.2899999999991</v>
@@ -14271,13 +14280,13 @@
         <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D231" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -14298,7 +14307,7 @@
         <v>1068.7</v>
       </c>
       <c r="K231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L231">
         <v>1045.17</v>
@@ -14307,7 +14316,7 @@
         <v>1045.17</v>
       </c>
       <c r="N231" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O231">
         <v>746.5500000000009</v>
@@ -14322,7 +14331,7 @@
         <v>7.5</v>
       </c>
       <c r="S231" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -14330,13 +14339,13 @@
         <v>102</v>
       </c>
       <c r="B232" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C232" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -14366,7 +14375,7 @@
         <v>196.43</v>
       </c>
       <c r="N232" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O232">
         <v>-496.3200000000002</v>
@@ -14386,13 +14395,13 @@
         <v>102</v>
       </c>
       <c r="B233" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C233" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D233" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14422,7 +14431,7 @@
         <v>2015.42</v>
       </c>
       <c r="N233" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O233">
         <v>-424.3199999999997</v>
@@ -14442,13 +14451,13 @@
         <v>103</v>
       </c>
       <c r="B234" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C234" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D234" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14478,7 +14487,7 @@
         <v>91.01000000000001</v>
       </c>
       <c r="N234" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O234">
         <v>-520</v>
@@ -14498,13 +14507,13 @@
         <v>104</v>
       </c>
       <c r="B235" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C235" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D235" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E235">
         <v>3</v>
@@ -14525,7 +14534,7 @@
         <v>1198.65</v>
       </c>
       <c r="K235" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L235">
         <v>1192.15</v>
@@ -14534,7 +14543,7 @@
         <v>1185</v>
       </c>
       <c r="N235" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O235">
         <v>1981.6</v>
@@ -14557,13 +14566,13 @@
         <v>105</v>
       </c>
       <c r="B236" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C236" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -14584,7 +14593,7 @@
         <v>401.95</v>
       </c>
       <c r="K236" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L236">
         <v>389.18</v>
@@ -14593,7 +14602,7 @@
         <v>389.18</v>
       </c>
       <c r="N236" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O236">
         <v>722.735000000001</v>
@@ -14616,13 +14625,13 @@
         <v>105</v>
       </c>
       <c r="B237" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C237" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D237" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14652,7 +14661,7 @@
         <v>1251.43</v>
       </c>
       <c r="N237" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O237">
         <v>-461.0899999999992</v>
@@ -14672,13 +14681,13 @@
         <v>106</v>
       </c>
       <c r="B238" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C238" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D238" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -14708,7 +14717,7 @@
         <v>964.72</v>
       </c>
       <c r="N238" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O238">
         <v>-457.0199999999998</v>
@@ -14728,13 +14737,13 @@
         <v>107</v>
       </c>
       <c r="B239" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C239" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D239" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -14764,7 +14773,7 @@
         <v>486.15</v>
       </c>
       <c r="N239" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O239">
         <v>0</v>
@@ -14784,13 +14793,13 @@
         <v>107</v>
       </c>
       <c r="B240" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C240" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -14820,7 +14829,7 @@
         <v>963.2</v>
       </c>
       <c r="N240" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O240">
         <v>-456.2999999999994</v>
@@ -14840,13 +14849,13 @@
         <v>107</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C241" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D241" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14876,7 +14885,7 @@
         <v>227.71</v>
       </c>
       <c r="N241" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O241">
         <v>-491.5899999999992</v>
@@ -14896,13 +14905,13 @@
         <v>107</v>
       </c>
       <c r="B242" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D242" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -14932,7 +14941,7 @@
         <v>3950</v>
       </c>
       <c r="N242" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O242">
         <v>-439.6000000000004</v>
@@ -14952,13 +14961,13 @@
         <v>108</v>
       </c>
       <c r="B243" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D243" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E243">
         <v>2</v>
@@ -14988,7 +14997,7 @@
         <v>1764.42</v>
       </c>
       <c r="N243" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O243">
         <v>588.1400000000003</v>
@@ -15011,13 +15020,13 @@
         <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D244" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E244">
         <v>3</v>
@@ -15047,7 +15056,7 @@
         <v>4883.9</v>
       </c>
       <c r="N244" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O244">
         <v>979.6999999999998</v>
@@ -15062,7 +15071,7 @@
         <v>11.29</v>
       </c>
       <c r="S244" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -15070,13 +15079,13 @@
         <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D245" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -15097,7 +15106,7 @@
         <v>6861</v>
       </c>
       <c r="K245" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L245">
         <v>6805.8</v>
@@ -15106,7 +15115,7 @@
         <v>6805.8</v>
       </c>
       <c r="N245" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O245">
         <v>-358.1999999999998</v>
@@ -15126,13 +15135,13 @@
         <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C246" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D246" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -15162,7 +15171,7 @@
         <v>3080</v>
       </c>
       <c r="N246" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O246">
         <v>-68.40000000000055</v>
@@ -15182,13 +15191,13 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D247" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -15218,7 +15227,7 @@
         <v>546.77</v>
       </c>
       <c r="N247" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O247">
         <v>-489.2599999999995</v>
@@ -15238,13 +15247,13 @@
         <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -15274,7 +15283,7 @@
         <v>418.9</v>
       </c>
       <c r="N248" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O248">
         <v>-485.1000000000003</v>
@@ -15294,13 +15303,13 @@
         <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D249" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -15330,7 +15339,7 @@
         <v>271.75</v>
       </c>
       <c r="N249" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O249">
         <v>-486.2000000000004</v>
@@ -15350,13 +15359,13 @@
         <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D250" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -15386,7 +15395,7 @@
         <v>4289.44</v>
       </c>
       <c r="N250" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O250">
         <v>-451.5200000000005</v>
@@ -15406,13 +15415,13 @@
         <v>112</v>
       </c>
       <c r="B251" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C251" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D251" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -15442,7 +15451,7 @@
         <v>2628.65</v>
       </c>
       <c r="N251" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O251">
         <v>-415.0499999999997</v>
@@ -15462,13 +15471,13 @@
         <v>113</v>
       </c>
       <c r="B252" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -15498,7 +15507,7 @@
         <v>1149</v>
       </c>
       <c r="N252" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O252">
         <v>1290.12</v>
@@ -15521,13 +15530,13 @@
         <v>113</v>
       </c>
       <c r="B253" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C253" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D253" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -15557,7 +15566,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="N253" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O253">
         <v>-495.7199999999988</v>
@@ -15577,13 +15586,13 @@
         <v>114</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -15601,7 +15610,7 @@
         <v>9898.700000000001</v>
       </c>
       <c r="J254">
-        <v>714.35</v>
+        <v>728.65</v>
       </c>
       <c r="L254">
         <v>671.7</v>
@@ -15613,13 +15622,13 @@
         <v>0</v>
       </c>
       <c r="P254">
-        <v>102.2</v>
+        <v>302.4</v>
       </c>
       <c r="Q254">
-        <v>102.2</v>
+        <v>302.4</v>
       </c>
       <c r="R254">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -15627,13 +15636,13 @@
         <v>115</v>
       </c>
       <c r="B255" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D255" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -15663,7 +15672,7 @@
         <v>541.45</v>
       </c>
       <c r="N255" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O255">
         <v>-484.5</v>
@@ -15683,13 +15692,13 @@
         <v>115</v>
       </c>
       <c r="B256" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D256" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -15719,7 +15728,7 @@
         <v>397.91</v>
       </c>
       <c r="N256" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O256">
         <v>-481.62</v>
@@ -15739,13 +15748,13 @@
         <v>116</v>
       </c>
       <c r="B257" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D257" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -15766,7 +15775,7 @@
         <v>2569</v>
       </c>
       <c r="K257" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L257">
         <v>2542.67</v>
@@ -15775,7 +15784,7 @@
         <v>2542.67</v>
       </c>
       <c r="N257" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O257">
         <v>-401.4899999999998</v>
@@ -15795,13 +15804,13 @@
         <v>116</v>
       </c>
       <c r="B258" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C258" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D258" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -15831,7 +15840,7 @@
         <v>7471.5</v>
       </c>
       <c r="N258" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O258">
         <v>0</v>
@@ -15851,13 +15860,13 @@
         <v>117</v>
       </c>
       <c r="B259" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C259" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D259" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E259">
         <v>3</v>
@@ -15887,7 +15896,7 @@
         <v>414.095</v>
       </c>
       <c r="N259" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O259">
         <v>978.770000000001</v>
@@ -15910,13 +15919,13 @@
         <v>118</v>
       </c>
       <c r="B260" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C260" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D260" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -15946,7 +15955,7 @@
         <v>1210.5</v>
       </c>
       <c r="N260" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O260">
         <v>-457.8000000000006</v>
@@ -15966,13 +15975,13 @@
         <v>118</v>
       </c>
       <c r="B261" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C261" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D261" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -16002,7 +16011,7 @@
         <v>1311.57</v>
       </c>
       <c r="N261" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O261">
         <v>-483.2099999999998</v>
@@ -16022,13 +16031,13 @@
         <v>118</v>
       </c>
       <c r="B262" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C262" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D262" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E262">
         <v>3</v>
@@ -16058,7 +16067,7 @@
         <v>167.99</v>
       </c>
       <c r="N262" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O262">
         <v>1370.392500000001</v>
@@ -16081,13 +16090,13 @@
         <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C263" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D263" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -16117,7 +16126,7 @@
         <v>1702.31</v>
       </c>
       <c r="N263" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O263">
         <v>-447.9500000000007</v>
@@ -16137,13 +16146,13 @@
         <v>120</v>
       </c>
       <c r="B264" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C264" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D264" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E264">
         <v>2</v>
@@ -16173,7 +16182,7 @@
         <v>4732.14</v>
       </c>
       <c r="N264" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O264">
         <v>676.0200000000004</v>
@@ -16196,13 +16205,13 @@
         <v>121</v>
       </c>
       <c r="B265" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C265" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D265" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -16232,7 +16241,7 @@
         <v>327.15</v>
       </c>
       <c r="N265" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O265">
         <v>1246.58</v>
@@ -16255,13 +16264,13 @@
         <v>122</v>
       </c>
       <c r="B266" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C266" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D266" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -16291,7 +16300,7 @@
         <v>7204.5</v>
       </c>
       <c r="N266" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -16311,13 +16320,13 @@
         <v>123</v>
       </c>
       <c r="B267" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C267" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D267" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16347,7 +16356,7 @@
         <v>2744.84</v>
       </c>
       <c r="N267" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O267">
         <v>-433.3800000000001</v>
@@ -16367,13 +16376,13 @@
         <v>124</v>
       </c>
       <c r="B268" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C268" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D268" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -16403,7 +16412,7 @@
         <v>1007</v>
       </c>
       <c r="N268" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O268">
         <v>-477</v>
@@ -16423,13 +16432,13 @@
         <v>124</v>
       </c>
       <c r="B269" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C269" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D269" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E269">
         <v>2</v>
@@ -16459,7 +16468,7 @@
         <v>3072.195</v>
       </c>
       <c r="N269" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O269">
         <v>438.8850000000002</v>
@@ -16479,13 +16488,13 @@
         <v>124</v>
       </c>
       <c r="B270" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D270" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -16515,7 +16524,7 @@
         <v>738.5</v>
       </c>
       <c r="N270" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O270">
         <v>-469.2000000000003</v>
@@ -16535,13 +16544,13 @@
         <v>125</v>
       </c>
       <c r="B271" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C271" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D271" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -16571,7 +16580,7 @@
         <v>1511.73</v>
       </c>
       <c r="N271" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O271">
         <v>-477.4199999999996</v>
@@ -16591,13 +16600,13 @@
         <v>126</v>
       </c>
       <c r="B272" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C272" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D272" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -16627,7 +16636,7 @@
         <v>2859.5</v>
       </c>
       <c r="N272" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O272">
         <v>-451.5</v>
@@ -16647,13 +16656,13 @@
         <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C273" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D273" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -16683,7 +16692,7 @@
         <v>1619</v>
       </c>
       <c r="N273" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O273">
         <v>0</v>
@@ -16703,13 +16712,13 @@
         <v>127</v>
       </c>
       <c r="B274" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C274" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D274" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -16730,7 +16739,7 @@
         <v>1366</v>
       </c>
       <c r="K274" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L274">
         <v>1325.34</v>
@@ -16739,7 +16748,7 @@
         <v>1325.34</v>
       </c>
       <c r="N274" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O274">
         <v>-488.32</v>
@@ -16759,13 +16768,13 @@
         <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C275" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D275" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -16795,7 +16804,7 @@
         <v>7006.72</v>
       </c>
       <c r="N275" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O275">
         <v>-368.7799999999997</v>
@@ -16815,13 +16824,13 @@
         <v>127</v>
       </c>
       <c r="B276" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C276" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D276" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -16851,7 +16860,7 @@
         <v>1679.88</v>
       </c>
       <c r="N276" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O276">
         <v>-442.0999999999992</v>
@@ -16871,13 +16880,13 @@
         <v>128</v>
       </c>
       <c r="B277" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C277" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D277" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -16907,7 +16916,7 @@
         <v>1052.2</v>
       </c>
       <c r="N277" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -16927,13 +16936,13 @@
         <v>128</v>
       </c>
       <c r="B278" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C278" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D278" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -16963,7 +16972,7 @@
         <v>1785.2</v>
       </c>
       <c r="N278" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -16983,13 +16992,13 @@
         <v>129</v>
       </c>
       <c r="B279" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C279" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D279" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -17019,7 +17028,7 @@
         <v>710.79</v>
       </c>
       <c r="N279" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O279">
         <v>-486.3300000000011</v>
@@ -17039,13 +17048,13 @@
         <v>130</v>
       </c>
       <c r="B280" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C280" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D280" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17075,7 +17084,7 @@
         <v>1858.96</v>
       </c>
       <c r="N280" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O280">
         <v>-489.1999999999996</v>
@@ -17095,13 +17104,13 @@
         <v>131</v>
       </c>
       <c r="B281" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C281" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D281" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17131,7 +17140,7 @@
         <v>1181.75</v>
       </c>
       <c r="N281" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O281">
         <v>-497.6000000000004</v>
@@ -17151,13 +17160,13 @@
         <v>132</v>
       </c>
       <c r="B282" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C282" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D282" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -17187,7 +17196,7 @@
         <v>1865.32</v>
       </c>
       <c r="N282" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O282">
         <v>-490.9000000000003</v>
@@ -17207,13 +17216,13 @@
         <v>132</v>
       </c>
       <c r="B283" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C283" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D283" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -17243,7 +17252,7 @@
         <v>540.55</v>
       </c>
       <c r="N283" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O283">
         <v>-483.6500000000008</v>
@@ -17263,13 +17272,13 @@
         <v>133</v>
       </c>
       <c r="B284" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C284" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D284" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -17299,7 +17308,7 @@
         <v>1909.5</v>
       </c>
       <c r="N284" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O284">
         <v>-402</v>
@@ -17319,13 +17328,13 @@
         <v>133</v>
       </c>
       <c r="B285" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C285" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D285" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -17355,7 +17364,7 @@
         <v>969</v>
       </c>
       <c r="N285" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O285">
         <v>-459</v>
@@ -17375,13 +17384,13 @@
         <v>134</v>
       </c>
       <c r="B286" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C286" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D286" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -17411,7 +17420,7 @@
         <v>1002.25</v>
       </c>
       <c r="N286" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O286">
         <v>-474.75</v>
@@ -17431,13 +17440,13 @@
         <v>135</v>
       </c>
       <c r="B287" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C287" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D287" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -17467,7 +17476,7 @@
         <v>1550.59</v>
       </c>
       <c r="N287" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O287">
         <v>-489.6600000000008</v>
@@ -17487,13 +17496,13 @@
         <v>135</v>
       </c>
       <c r="B288" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C288" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D288" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -17523,7 +17532,7 @@
         <v>3235.7</v>
       </c>
       <c r="N288" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O288">
         <v>-340.6000000000004</v>
@@ -17543,13 +17552,13 @@
         <v>136</v>
       </c>
       <c r="B289" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C289" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D289" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -17570,7 +17579,7 @@
         <v>1940.5</v>
       </c>
       <c r="K289" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L289">
         <v>1908.45</v>
@@ -17579,7 +17588,7 @@
         <v>1908.45</v>
       </c>
       <c r="N289" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O289">
         <v>-401.8000000000002</v>
@@ -17599,13 +17608,13 @@
         <v>137</v>
       </c>
       <c r="B290" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C290" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D290" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -17635,7 +17644,7 @@
         <v>1047.09</v>
       </c>
       <c r="N290" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O290">
         <v>-495.9900000000012</v>
@@ -17655,13 +17664,13 @@
         <v>137</v>
       </c>
       <c r="B291" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C291" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D291" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -17682,7 +17691,7 @@
         <v>549.5</v>
       </c>
       <c r="K291" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L291">
         <v>538.65</v>
@@ -17691,7 +17700,7 @@
         <v>538.65</v>
       </c>
       <c r="N291" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O291">
         <v>-481.9500000000004</v>
@@ -17711,13 +17720,13 @@
         <v>138</v>
       </c>
       <c r="B292" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C292" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D292" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -17738,7 +17747,7 @@
         <v>1025</v>
       </c>
       <c r="K292" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L292">
         <v>973.75</v>
@@ -17747,7 +17756,7 @@
         <v>922.5</v>
       </c>
       <c r="N292" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O292">
         <v>-922.5</v>
@@ -17767,13 +17776,13 @@
         <v>138</v>
       </c>
       <c r="B293" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C293" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D293" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -17803,7 +17812,7 @@
         <v>1561.32</v>
       </c>
       <c r="N293" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O293">
         <v>-493.0800000000004</v>
@@ -17823,13 +17832,13 @@
         <v>138</v>
       </c>
       <c r="B294" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C294" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D294" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E294">
         <v>2</v>
@@ -17859,7 +17868,7 @@
         <v>542</v>
       </c>
       <c r="N294" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O294">
         <v>558.2700000000009</v>
@@ -17882,13 +17891,13 @@
         <v>139</v>
       </c>
       <c r="B295" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C295" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D295" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -17918,7 +17927,7 @@
         <v>1503.85</v>
       </c>
       <c r="N295" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O295">
         <v>-474.9000000000005</v>
@@ -17938,13 +17947,13 @@
         <v>140</v>
       </c>
       <c r="B296" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C296" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D296" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -17974,7 +17983,7 @@
         <v>2798.7</v>
       </c>
       <c r="N296" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O296">
         <v>-441.9000000000005</v>
@@ -17994,13 +18003,13 @@
         <v>141</v>
       </c>
       <c r="B297" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C297" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D297" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -18021,7 +18030,7 @@
         <v>112.6</v>
       </c>
       <c r="K297" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L297">
         <v>110.67</v>
@@ -18030,7 +18039,7 @@
         <v>110.67</v>
       </c>
       <c r="N297" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O297">
         <v>-495.5499999999998</v>
@@ -18050,13 +18059,13 @@
         <v>141</v>
       </c>
       <c r="B298" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C298" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D298" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -18086,7 +18095,7 @@
         <v>615</v>
       </c>
       <c r="N298" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -18106,13 +18115,13 @@
         <v>141</v>
       </c>
       <c r="B299" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C299" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D299" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -18142,7 +18151,7 @@
         <v>168.7</v>
       </c>
       <c r="N299" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O299">
         <v>-524.1600000000008</v>
@@ -18162,13 +18171,13 @@
         <v>142</v>
       </c>
       <c r="B300" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C300" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D300" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18198,7 +18207,7 @@
         <v>5424.02</v>
       </c>
       <c r="N300" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O300">
         <v>-285.4799999999996</v>
@@ -18218,13 +18227,13 @@
         <v>143</v>
       </c>
       <c r="B301" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C301" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D301" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18254,7 +18263,7 @@
         <v>899.65</v>
       </c>
       <c r="N301" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O301">
         <v>-473.5000000000002</v>
@@ -18274,13 +18283,13 @@
         <v>143</v>
       </c>
       <c r="B302" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C302" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D302" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -18310,7 +18319,7 @@
         <v>1234.71</v>
       </c>
       <c r="N302" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O302">
         <v>-454.9300000000001</v>
@@ -18330,13 +18339,13 @@
         <v>144</v>
       </c>
       <c r="B303" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C303" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D303" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -18357,7 +18366,7 @@
         <v>1942.3</v>
       </c>
       <c r="K303" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L303">
         <v>1928.5</v>
@@ -18366,7 +18375,7 @@
         <v>1928.5</v>
       </c>
       <c r="N303" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O303">
         <v>-406</v>
@@ -18386,13 +18395,13 @@
         <v>145</v>
       </c>
       <c r="B304" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C304" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D304" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -18422,7 +18431,7 @@
         <v>3913.05</v>
       </c>
       <c r="N304" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O304">
         <v>-411.8999999999997</v>
@@ -18442,13 +18451,13 @@
         <v>146</v>
       </c>
       <c r="B305" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C305" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D305" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -18478,7 +18487,7 @@
         <v>396.2</v>
       </c>
       <c r="N305" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O305">
         <v>-576.1500000000003</v>
@@ -18498,13 +18507,13 @@
         <v>146</v>
       </c>
       <c r="B306" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C306" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D306" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -18534,7 +18543,7 @@
         <v>2156.5</v>
       </c>
       <c r="N306" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O306">
         <v>-454</v>
@@ -18554,13 +18563,13 @@
         <v>146</v>
       </c>
       <c r="B307" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C307" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D307" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -18590,7 +18599,7 @@
         <v>528</v>
       </c>
       <c r="N307" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O307">
         <v>-476.8499999999992</v>
@@ -18610,13 +18619,13 @@
         <v>146</v>
       </c>
       <c r="B308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C308" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D308" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -18646,7 +18655,7 @@
         <v>791.35</v>
       </c>
       <c r="N308" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O308">
         <v>-499.7999999999997</v>
@@ -18666,13 +18675,13 @@
         <v>147</v>
       </c>
       <c r="B309" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C309" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D309" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -18693,7 +18702,7 @@
         <v>593.6</v>
       </c>
       <c r="K309" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L309">
         <v>579.6</v>
@@ -18702,7 +18711,7 @@
         <v>575.45</v>
       </c>
       <c r="N309" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O309">
         <v>-554.3999999999996</v>
@@ -18722,13 +18731,13 @@
         <v>147</v>
       </c>
       <c r="B310" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C310" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D310" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -18758,7 +18767,7 @@
         <v>1055.26</v>
       </c>
       <c r="N310" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O310">
         <v>-499.8599999999997</v>
@@ -18778,13 +18787,13 @@
         <v>148</v>
       </c>
       <c r="B311" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C311" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D311" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -18814,7 +18823,7 @@
         <v>1161.76</v>
       </c>
       <c r="N311" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O311">
         <v>-489.1200000000008</v>
@@ -18834,13 +18843,13 @@
         <v>149</v>
       </c>
       <c r="B312" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C312" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D312" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -18870,7 +18879,7 @@
         <v>1802.72</v>
       </c>
       <c r="N312" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O312">
         <v>-474.3999999999994</v>
@@ -18890,13 +18899,13 @@
         <v>150</v>
       </c>
       <c r="B313" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C313" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D313" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -18926,7 +18935,7 @@
         <v>513.28</v>
       </c>
       <c r="N313" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O313">
         <v>-486.3599999999997</v>
@@ -18946,13 +18955,13 @@
         <v>151</v>
       </c>
       <c r="B314" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C314" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D314" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -18982,7 +18991,7 @@
         <v>1003.11</v>
       </c>
       <c r="N314" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O314">
         <v>-475.1100000000007</v>
@@ -19002,13 +19011,13 @@
         <v>152</v>
       </c>
       <c r="B315" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C315" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D315" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -19026,7 +19035,7 @@
         <v>9531.200000000001</v>
       </c>
       <c r="J315">
-        <v>4549.3</v>
+        <v>4668</v>
       </c>
       <c r="L315">
         <v>4527.32</v>
@@ -19038,13 +19047,13 @@
         <v>0</v>
       </c>
       <c r="P315">
-        <v>-432.6</v>
+        <v>-195.2</v>
       </c>
       <c r="Q315">
-        <v>-432.6</v>
+        <v>-195.2</v>
       </c>
       <c r="R315">
-        <v>-4.54</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -19052,13 +19061,13 @@
         <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C316" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D316" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -19076,7 +19085,7 @@
         <v>8814</v>
       </c>
       <c r="J316">
-        <v>2972.9</v>
+        <v>2903.4</v>
       </c>
       <c r="L316">
         <v>2791.1</v>
@@ -19088,13 +19097,13 @@
         <v>0</v>
       </c>
       <c r="P316">
-        <v>104.7</v>
+        <v>-103.8</v>
       </c>
       <c r="Q316">
-        <v>104.7</v>
+        <v>-103.8</v>
       </c>
       <c r="R316">
-        <v>1.19</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -19102,13 +19111,13 @@
         <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C317" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D317" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -19129,7 +19138,7 @@
         <v>303.25</v>
       </c>
       <c r="K317" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L317">
         <v>302.76</v>
@@ -19138,7 +19147,7 @@
         <v>302.2</v>
       </c>
       <c r="N317" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O317">
         <v>-511.5</v>
@@ -19158,13 +19167,13 @@
         <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C318" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D318" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -19185,7 +19194,7 @@
         <v>1137</v>
       </c>
       <c r="K318" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L318">
         <v>1106.75</v>
@@ -19194,7 +19203,7 @@
         <v>1106.75</v>
       </c>
       <c r="N318" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O318">
         <v>-466</v>
@@ -19214,13 +19223,13 @@
         <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C319" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D319" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E319">
         <v>1</v>
@@ -19238,7 +19247,7 @@
         <v>9153.6</v>
       </c>
       <c r="J319">
-        <v>1251.9</v>
+        <v>1233</v>
       </c>
       <c r="L319">
         <v>1144.2</v>
@@ -19250,13 +19259,13 @@
         <v>0</v>
       </c>
       <c r="P319">
-        <v>861.6</v>
+        <v>710.4</v>
       </c>
       <c r="Q319">
-        <v>861.6</v>
+        <v>710.4</v>
       </c>
       <c r="R319">
-        <v>9.41</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -19264,13 +19273,13 @@
         <v>155</v>
       </c>
       <c r="B320" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C320" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D320" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -19300,7 +19309,7 @@
         <v>398.29</v>
       </c>
       <c r="N320" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O320">
         <v>-482.0799999999995</v>
@@ -19320,13 +19329,13 @@
         <v>156</v>
       </c>
       <c r="B321" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C321" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D321" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -19356,7 +19365,7 @@
         <v>2679</v>
       </c>
       <c r="N321" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O321">
         <v>-423</v>
@@ -19376,13 +19385,13 @@
         <v>156</v>
       </c>
       <c r="B322" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C322" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D322" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -19400,7 +19409,7 @@
         <v>8875</v>
       </c>
       <c r="J322">
-        <v>1822</v>
+        <v>1798.3</v>
       </c>
       <c r="L322">
         <v>1686.25</v>
@@ -19412,13 +19421,13 @@
         <v>0</v>
       </c>
       <c r="P322">
-        <v>235</v>
+        <v>116.5</v>
       </c>
       <c r="Q322">
-        <v>235</v>
+        <v>116.5</v>
       </c>
       <c r="R322">
-        <v>2.65</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -19426,13 +19435,13 @@
         <v>156</v>
       </c>
       <c r="B323" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C323" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D323" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -19450,7 +19459,7 @@
         <v>9838.4</v>
       </c>
       <c r="J323">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="L323">
         <v>1168.31</v>
@@ -19462,13 +19471,13 @@
         <v>0</v>
       </c>
       <c r="P323">
-        <v>-62.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q323">
-        <v>-62.4</v>
+        <v>1.6</v>
       </c>
       <c r="R323">
-        <v>-0.63</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -19476,13 +19485,13 @@
         <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C324" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D324" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -19512,7 +19521,7 @@
         <v>447.45</v>
       </c>
       <c r="N324" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O324">
         <v>-494.5500000000002</v>
@@ -19532,13 +19541,13 @@
         <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C325" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D325" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -19568,7 +19577,7 @@
         <v>1001.97</v>
       </c>
       <c r="N325" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O325">
         <v>-474.5700000000002</v>
@@ -19588,13 +19597,13 @@
         <v>158</v>
       </c>
       <c r="B326" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C326" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D326" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -19612,7 +19621,7 @@
         <v>9963.450000000001</v>
       </c>
       <c r="J326">
-        <v>158.56</v>
+        <v>163.26</v>
       </c>
       <c r="L326">
         <v>150.24</v>
@@ -19624,13 +19633,13 @@
         <v>0</v>
       </c>
       <c r="P326">
-        <v>25.83</v>
+        <v>321.93</v>
       </c>
       <c r="Q326">
-        <v>25.83</v>
+        <v>321.93</v>
       </c>
       <c r="R326">
-        <v>0.26</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -19638,13 +19647,13 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C327" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D327" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -19662,7 +19671,7 @@
         <v>9101.5</v>
       </c>
       <c r="J327">
-        <v>1785.1</v>
+        <v>1763.3</v>
       </c>
       <c r="L327">
         <v>1729.28</v>
@@ -19674,13 +19683,13 @@
         <v>0</v>
       </c>
       <c r="P327">
-        <v>-176</v>
+        <v>-285</v>
       </c>
       <c r="Q327">
-        <v>-176</v>
+        <v>-285</v>
       </c>
       <c r="R327">
-        <v>-1.93</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -19688,13 +19697,13 @@
         <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C328" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D328" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -19715,7 +19724,7 @@
         <v>1038.5</v>
       </c>
       <c r="K328" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L328">
         <v>1023.15</v>
@@ -19724,7 +19733,7 @@
         <v>1023.15</v>
       </c>
       <c r="N328" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O328">
         <v>-484.6500000000002</v>
@@ -19744,13 +19753,13 @@
         <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C329" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D329" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -19768,7 +19777,7 @@
         <v>9772.75</v>
       </c>
       <c r="J329">
-        <v>327.85</v>
+        <v>320</v>
       </c>
       <c r="L329">
         <v>315.25</v>
@@ -19780,13 +19789,13 @@
         <v>0</v>
       </c>
       <c r="P329">
-        <v>390.6</v>
+        <v>147.25</v>
       </c>
       <c r="Q329">
-        <v>390.6</v>
+        <v>147.25</v>
       </c>
       <c r="R329">
-        <v>4</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -19794,10 +19803,10 @@
         <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C330" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D330" t="s">
         <v>261</v>
@@ -19812,7 +19821,7 @@
         <v>2</v>
       </c>
       <c r="H330">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I330">
         <v>9712</v>
@@ -19820,23 +19829,29 @@
       <c r="J330">
         <v>4675</v>
       </c>
+      <c r="K330" t="s">
+        <v>166</v>
+      </c>
       <c r="L330">
         <v>4613.2</v>
       </c>
       <c r="M330">
-        <v>0</v>
+        <v>4613.2</v>
+      </c>
+      <c r="N330" t="s">
+        <v>281</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>-485.6000000000004</v>
       </c>
       <c r="P330">
-        <v>-362</v>
+        <v>0</v>
       </c>
       <c r="Q330">
-        <v>-362</v>
+        <v>-485.6000000000004</v>
       </c>
       <c r="R330">
-        <v>-3.73</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -19844,13 +19859,13 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C331" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D331" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -19868,7 +19883,7 @@
         <v>9561</v>
       </c>
       <c r="J331">
-        <v>3100</v>
+        <v>3061.9</v>
       </c>
       <c r="L331">
         <v>3027.65</v>
@@ -19880,13 +19895,13 @@
         <v>0</v>
       </c>
       <c r="P331">
-        <v>-261</v>
+        <v>-375.3</v>
       </c>
       <c r="Q331">
-        <v>-261</v>
+        <v>-375.3</v>
       </c>
       <c r="R331">
-        <v>-2.73</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -19894,13 +19909,13 @@
         <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C332" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D332" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -19930,7 +19945,7 @@
         <v>1075.78</v>
       </c>
       <c r="N332" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O332">
         <v>-452.9600000000009</v>
@@ -19950,13 +19965,13 @@
         <v>160</v>
       </c>
       <c r="B333" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C333" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D333" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -19986,7 +20001,7 @@
         <v>1630</v>
       </c>
       <c r="N333" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O333">
         <v>-850</v>
@@ -20006,13 +20021,13 @@
         <v>161</v>
       </c>
       <c r="B334" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C334" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D334" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -20030,7 +20045,7 @@
         <v>9054.6</v>
       </c>
       <c r="J334">
-        <v>1515</v>
+        <v>1590</v>
       </c>
       <c r="L334">
         <v>1433.64</v>
@@ -20042,13 +20057,13 @@
         <v>0</v>
       </c>
       <c r="P334">
-        <v>35.4</v>
+        <v>485.4</v>
       </c>
       <c r="Q334">
-        <v>35.4</v>
+        <v>485.4</v>
       </c>
       <c r="R334">
-        <v>0.39</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -20056,10 +20071,10 @@
         <v>161</v>
       </c>
       <c r="B335" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C335" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D335" t="s">
         <v>261</v>
@@ -20074,7 +20089,7 @@
         <v>1</v>
       </c>
       <c r="H335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I335">
         <v>5023</v>
@@ -20082,23 +20097,29 @@
       <c r="J335">
         <v>4835</v>
       </c>
+      <c r="K335" t="s">
+        <v>166</v>
+      </c>
       <c r="L335">
         <v>4771.85</v>
       </c>
       <c r="M335">
-        <v>0</v>
+        <v>4771.85</v>
+      </c>
+      <c r="N335" t="s">
+        <v>281</v>
       </c>
       <c r="O335">
-        <v>0</v>
+        <v>-251.1499999999996</v>
       </c>
       <c r="P335">
-        <v>-188</v>
+        <v>0</v>
       </c>
       <c r="Q335">
-        <v>-188</v>
+        <v>-251.1499999999996</v>
       </c>
       <c r="R335">
-        <v>-3.74</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20106,13 +20127,13 @@
         <v>162</v>
       </c>
       <c r="B336" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C336" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D336" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -20130,7 +20151,7 @@
         <v>9654.75</v>
       </c>
       <c r="J336">
-        <v>448.2</v>
+        <v>455.45</v>
       </c>
       <c r="L336">
         <v>436.76</v>
@@ -20142,13 +20163,13 @@
         <v>0</v>
       </c>
       <c r="P336">
-        <v>-242.55</v>
+        <v>-90.3</v>
       </c>
       <c r="Q336">
-        <v>-242.55</v>
+        <v>-90.3</v>
       </c>
       <c r="R336">
-        <v>-2.51</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -20156,13 +20177,13 @@
         <v>162</v>
       </c>
       <c r="B337" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C337" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D337" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -20180,7 +20201,7 @@
         <v>9402.4</v>
       </c>
       <c r="J337">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="L337">
         <v>1116.53</v>
@@ -20192,13 +20213,13 @@
         <v>0</v>
       </c>
       <c r="P337">
-        <v>-362.4</v>
+        <v>-323.2</v>
       </c>
       <c r="Q337">
-        <v>-362.4</v>
+        <v>-323.2</v>
       </c>
       <c r="R337">
-        <v>-3.85</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -20206,13 +20227,13 @@
         <v>163</v>
       </c>
       <c r="B338" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C338" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D338" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -20233,7 +20254,7 @@
         <v>591</v>
       </c>
       <c r="K338" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L338">
         <v>587.48</v>
@@ -20242,7 +20263,7 @@
         <v>587.48</v>
       </c>
       <c r="N338" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O338">
         <v>-494.7199999999993</v>
@@ -20262,13 +20283,13 @@
         <v>164</v>
       </c>
       <c r="B339" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C339" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D339" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -20286,7 +20307,7 @@
         <v>9723</v>
       </c>
       <c r="J339">
-        <v>444.55</v>
+        <v>443.8</v>
       </c>
       <c r="L339">
         <v>439.85</v>
@@ -20298,13 +20319,13 @@
         <v>0</v>
       </c>
       <c r="P339">
-        <v>-387.45</v>
+        <v>-403.2</v>
       </c>
       <c r="Q339">
-        <v>-387.45</v>
+        <v>-403.2</v>
       </c>
       <c r="R339">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="340" spans="1:18">
@@ -20312,13 +20333,13 @@
         <v>165</v>
       </c>
       <c r="B340" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C340" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D340" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -20336,7 +20357,7 @@
         <v>9511.200000000001</v>
       </c>
       <c r="J340">
-        <v>588.4</v>
+        <v>593.9</v>
       </c>
       <c r="L340">
         <v>564.73</v>
@@ -20348,13 +20369,63 @@
         <v>0</v>
       </c>
       <c r="P340">
-        <v>-96.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q340">
-        <v>-96.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="R340">
-        <v>-1.02</v>
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18">
+      <c r="A341" t="s">
+        <v>166</v>
+      </c>
+      <c r="B341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C341" t="s">
+        <v>260</v>
+      </c>
+      <c r="D341" t="s">
+        <v>262</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>417</v>
+      </c>
+      <c r="G341">
+        <v>23</v>
+      </c>
+      <c r="H341">
+        <v>23</v>
+      </c>
+      <c r="I341">
+        <v>9591</v>
+      </c>
+      <c r="J341">
+        <v>417</v>
+      </c>
+      <c r="L341">
+        <v>396.15</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>0</v>
+      </c>
+      <c r="R341">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="288">
   <si>
     <t>Buy Date</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -1238,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S341"/>
+  <dimension ref="A1:S342"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -1315,13 +1318,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1351,7 +1354,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1371,13 +1374,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1407,7 +1410,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1430,13 +1433,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1466,7 +1469,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1486,13 +1489,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1522,7 +1525,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1542,13 +1545,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1578,7 +1581,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1598,13 +1601,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1634,7 +1637,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1654,13 +1657,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1690,7 +1693,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1710,13 +1713,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1746,7 +1749,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1766,13 +1769,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1802,7 +1805,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1822,13 +1825,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1849,7 +1852,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1858,7 +1861,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1873,7 +1876,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1881,13 +1884,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1917,7 +1920,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1940,13 +1943,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1976,7 +1979,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1996,13 +1999,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2032,7 +2035,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2052,13 +2055,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2088,7 +2091,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -2108,13 +2111,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2144,7 +2147,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -2164,13 +2167,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2200,7 +2203,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -2220,13 +2223,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2256,7 +2259,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2276,13 +2279,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2312,7 +2315,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2332,13 +2335,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2368,7 +2371,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2388,13 +2391,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2415,7 +2418,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2424,7 +2427,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2444,13 +2447,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2471,7 +2474,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2480,7 +2483,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2500,13 +2503,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2536,7 +2539,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2556,13 +2559,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2592,7 +2595,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2612,13 +2615,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2648,7 +2651,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2668,13 +2671,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2695,7 +2698,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2704,7 +2707,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2724,13 +2727,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2760,7 +2763,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2780,13 +2783,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2816,7 +2819,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2836,13 +2839,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2872,7 +2875,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2892,13 +2895,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2928,7 +2931,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2948,13 +2951,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2975,7 +2978,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2984,7 +2987,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -3004,13 +3007,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3040,7 +3043,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -3060,13 +3063,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3096,7 +3099,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -3116,13 +3119,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3143,7 +3146,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -3152,7 +3155,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -3172,13 +3175,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3199,7 +3202,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -3208,7 +3211,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -3228,13 +3231,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3264,7 +3267,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -3284,13 +3287,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D37" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3320,7 +3323,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3340,13 +3343,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3376,7 +3379,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3399,13 +3402,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3435,7 +3438,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3455,13 +3458,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C40" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3491,7 +3494,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3511,13 +3514,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3547,7 +3550,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3567,13 +3570,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3594,7 +3597,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3603,7 +3606,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3623,13 +3626,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3650,7 +3653,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3659,7 +3662,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3679,13 +3682,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3715,7 +3718,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3735,13 +3738,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3771,7 +3774,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3791,13 +3794,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3827,7 +3830,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3850,13 +3853,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3886,7 +3889,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3906,13 +3909,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3942,7 +3945,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3962,13 +3965,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3998,7 +4001,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -4021,13 +4024,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4057,7 +4060,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -4077,13 +4080,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4113,7 +4116,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -4133,13 +4136,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D52" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4169,7 +4172,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -4192,13 +4195,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4228,7 +4231,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -4248,13 +4251,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4284,7 +4287,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -4307,13 +4310,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -4343,7 +4346,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4366,13 +4369,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C56" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4402,7 +4405,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4422,13 +4425,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4449,7 +4452,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4458,7 +4461,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4478,13 +4481,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C58" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4514,7 +4517,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4534,13 +4537,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4570,7 +4573,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4593,13 +4596,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4629,7 +4632,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4649,13 +4652,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4685,7 +4688,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4708,13 +4711,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4744,7 +4747,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4759,7 +4762,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4767,13 +4770,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4803,7 +4806,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4823,13 +4826,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4859,7 +4862,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4879,13 +4882,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4915,7 +4918,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4935,13 +4938,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C66" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4971,7 +4974,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4991,13 +4994,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5027,7 +5030,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -5047,13 +5050,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5083,7 +5086,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -5103,13 +5106,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5130,7 +5133,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -5139,7 +5142,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -5159,13 +5162,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5195,7 +5198,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -5215,13 +5218,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -5251,7 +5254,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5271,13 +5274,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -5307,7 +5310,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5327,13 +5330,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D73" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5363,7 +5366,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5383,13 +5386,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5419,7 +5422,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5439,13 +5442,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5475,7 +5478,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5495,13 +5498,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5531,7 +5534,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5551,13 +5554,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5587,7 +5590,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5607,13 +5610,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5643,7 +5646,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5663,13 +5666,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5699,7 +5702,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5719,13 +5722,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D80" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5755,7 +5758,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5775,13 +5778,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5811,7 +5814,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5831,13 +5834,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5867,7 +5870,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5890,13 +5893,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5926,7 +5929,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5946,13 +5949,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5982,7 +5985,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -6002,13 +6005,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6038,7 +6041,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -6058,13 +6061,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6094,7 +6097,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -6114,13 +6117,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C87" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6150,7 +6153,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -6170,13 +6173,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -6206,7 +6209,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -6226,13 +6229,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C89" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -6262,7 +6265,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -6282,13 +6285,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -6318,7 +6321,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6338,13 +6341,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E91">
         <v>2</v>
@@ -6374,7 +6377,7 @@
         <v>309.38</v>
       </c>
       <c r="N91" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O91">
         <v>721.8500000000008</v>
@@ -6397,13 +6400,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6433,7 +6436,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6453,13 +6456,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D93" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6489,7 +6492,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6509,13 +6512,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D94" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6545,7 +6548,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6565,13 +6568,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6601,7 +6604,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6621,13 +6624,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C96" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D96" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6657,7 +6660,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6677,13 +6680,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C97" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D97" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6713,7 +6716,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6733,13 +6736,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C98" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D98" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6769,7 +6772,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6792,13 +6795,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6828,7 +6831,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6848,13 +6851,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D100" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6884,7 +6887,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6904,13 +6907,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6940,7 +6943,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6960,13 +6963,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6996,7 +6999,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -7016,13 +7019,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7052,7 +7055,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -7072,13 +7075,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C104" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7108,7 +7111,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -7128,13 +7131,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C105" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -7164,7 +7167,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -7184,13 +7187,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C106" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -7211,7 +7214,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -7220,7 +7223,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -7240,13 +7243,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -7276,7 +7279,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -7296,13 +7299,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -7332,7 +7335,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7352,13 +7355,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7379,7 +7382,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7388,7 +7391,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7408,13 +7411,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7444,7 +7447,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7464,13 +7467,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7500,7 +7503,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7520,13 +7523,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C112" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7556,7 +7559,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7576,13 +7579,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D113" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7612,7 +7615,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7632,13 +7635,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D114" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7668,7 +7671,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7688,13 +7691,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C115" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7724,7 +7727,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7744,13 +7747,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C116" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7780,7 +7783,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7800,13 +7803,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7836,7 +7839,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7856,13 +7859,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D118" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7892,7 +7895,7 @@
         <v>1201.31</v>
       </c>
       <c r="N118" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O118">
         <v>686.4800000000005</v>
@@ -7915,13 +7918,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7951,7 +7954,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7971,13 +7974,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -8007,7 +8010,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -8027,13 +8030,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C121" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D121" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8063,7 +8066,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -8083,13 +8086,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D122" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8119,7 +8122,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -8139,13 +8142,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C123" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D123" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8166,7 +8169,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -8175,7 +8178,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -8195,13 +8198,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -8231,7 +8234,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -8251,13 +8254,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C125" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D125" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -8287,7 +8290,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -8307,13 +8310,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C126" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -8343,7 +8346,7 @@
         <v>216.9</v>
       </c>
       <c r="N126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O126">
         <v>2070.147</v>
@@ -8366,13 +8369,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D127" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8402,7 +8405,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8422,13 +8425,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D128" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8458,7 +8461,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8481,13 +8484,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8517,7 +8520,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8537,13 +8540,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C130" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8573,7 +8576,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8593,13 +8596,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C131" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8629,7 +8632,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8649,13 +8652,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8685,7 +8688,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8705,13 +8708,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C133" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8732,7 +8735,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8741,7 +8744,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8761,13 +8764,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8797,7 +8800,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8817,13 +8820,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8853,7 +8856,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8873,13 +8876,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8909,7 +8912,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8929,13 +8932,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C137" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8965,7 +8968,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8988,13 +8991,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C138" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -9024,7 +9027,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -9044,13 +9047,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -9080,7 +9083,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -9100,13 +9103,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -9136,7 +9139,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -9156,13 +9159,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9192,7 +9195,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -9212,13 +9215,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C142" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -9248,7 +9251,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -9268,13 +9271,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C143" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -9304,7 +9307,7 @@
         <v>7328.5</v>
       </c>
       <c r="N143" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O143">
         <v>1116</v>
@@ -9324,13 +9327,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C144" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -9360,7 +9363,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9380,13 +9383,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9416,7 +9419,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9436,13 +9439,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C146" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9472,7 +9475,7 @@
         <v>3707.9</v>
       </c>
       <c r="N146" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O146">
         <v>1839.300000000001</v>
@@ -9495,13 +9498,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C147" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -9531,7 +9534,7 @@
         <v>911.1</v>
       </c>
       <c r="N147" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O147">
         <v>1201.2825</v>
@@ -9554,13 +9557,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C148" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -9590,7 +9593,7 @@
         <v>354.3100000000001</v>
       </c>
       <c r="N148" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O148">
         <v>998.5100000000012</v>
@@ -9613,13 +9616,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C149" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9640,7 +9643,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9649,7 +9652,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9672,13 +9675,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C150" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -9708,7 +9711,7 @@
         <v>485.1</v>
       </c>
       <c r="N150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O150">
         <v>1336.17</v>
@@ -9731,13 +9734,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C151" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D151" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9767,7 +9770,7 @@
         <v>4246.1</v>
       </c>
       <c r="N151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -9787,13 +9790,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -9823,7 +9826,7 @@
         <v>384.41</v>
       </c>
       <c r="N152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O152">
         <v>732.2700000000002</v>
@@ -9846,13 +9849,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -9882,7 +9885,7 @@
         <v>1080.61</v>
       </c>
       <c r="N153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O153">
         <v>668.9599999999998</v>
@@ -9905,13 +9908,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C154" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E154">
         <v>2</v>
@@ -9941,7 +9944,7 @@
         <v>2216.13</v>
       </c>
       <c r="N154" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O154">
         <v>633.1800000000012</v>
@@ -9956,7 +9959,7 @@
         <v>7.5</v>
       </c>
       <c r="S154" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9964,13 +9967,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C155" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -10000,7 +10003,7 @@
         <v>1262</v>
       </c>
       <c r="N155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O155">
         <v>605.2400000000007</v>
@@ -10023,13 +10026,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C156" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -10059,7 +10062,7 @@
         <v>204.18</v>
       </c>
       <c r="N156" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -10079,13 +10082,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C157" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -10115,7 +10118,7 @@
         <v>1977.4</v>
       </c>
       <c r="N157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O157">
         <v>352.0000000000005</v>
@@ -10135,13 +10138,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D158" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -10171,7 +10174,7 @@
         <v>1266.35</v>
       </c>
       <c r="N158" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O158">
         <v>-466.5500000000006</v>
@@ -10191,13 +10194,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C159" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D159" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -10227,7 +10230,7 @@
         <v>1016.19</v>
       </c>
       <c r="N159" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O159">
         <v>725.8500000000004</v>
@@ -10250,13 +10253,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C160" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -10286,7 +10289,7 @@
         <v>514.52</v>
       </c>
       <c r="N160" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O160">
         <v>-487.4400000000008</v>
@@ -10306,13 +10309,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C161" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D161" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -10342,7 +10345,7 @@
         <v>449.45</v>
       </c>
       <c r="N161" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O161">
         <v>727.6550000000004</v>
@@ -10365,13 +10368,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C162" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E162">
         <v>2</v>
@@ -10401,7 +10404,7 @@
         <v>9992.85</v>
       </c>
       <c r="N162" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O162">
         <v>475.8500000000004</v>
@@ -10421,13 +10424,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C163" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -10457,7 +10460,7 @@
         <v>344.4</v>
       </c>
       <c r="N163" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O163">
         <v>1477.98</v>
@@ -10480,13 +10483,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C164" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D164" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -10507,7 +10510,7 @@
         <v>1283.4</v>
       </c>
       <c r="K164" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L164">
         <v>1270.19</v>
@@ -10516,7 +10519,7 @@
         <v>1270.19</v>
       </c>
       <c r="N164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O164">
         <v>725.8400000000001</v>
@@ -10539,13 +10542,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C165" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D165" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10566,7 +10569,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10575,7 +10578,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10595,13 +10598,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C166" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E166">
         <v>2</v>
@@ -10631,7 +10634,7 @@
         <v>457.49</v>
       </c>
       <c r="N166" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O166">
         <v>718.9600000000007</v>
@@ -10654,13 +10657,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D167" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -10690,7 +10693,7 @@
         <v>122.16</v>
       </c>
       <c r="N167" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -10710,13 +10713,13 @@
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C168" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D168" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10746,7 +10749,7 @@
         <v>3872.49</v>
       </c>
       <c r="N168" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O168">
         <v>-407.6200000000008</v>
@@ -10766,13 +10769,13 @@
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C169" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D169" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E169">
         <v>2</v>
@@ -10802,7 +10805,7 @@
         <v>575.87</v>
       </c>
       <c r="N169" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O169">
         <v>740.3849999999999</v>
@@ -10825,13 +10828,13 @@
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C170" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D170" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -10861,7 +10864,7 @@
         <v>1725</v>
       </c>
       <c r="N170" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O170">
         <v>1106.71</v>
@@ -10884,13 +10887,13 @@
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C171" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D171" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E171">
         <v>2</v>
@@ -10920,7 +10923,7 @@
         <v>7816</v>
       </c>
       <c r="N171" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O171">
         <v>174</v>
@@ -10940,13 +10943,13 @@
         <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C172" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D172" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -10976,7 +10979,7 @@
         <v>622.12</v>
       </c>
       <c r="N172" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O172">
         <v>710.96</v>
@@ -10999,13 +11002,13 @@
         <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C173" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D173" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -11035,7 +11038,7 @@
         <v>282.75</v>
       </c>
       <c r="N173" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -11055,13 +11058,13 @@
         <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C174" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D174" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -11091,7 +11094,7 @@
         <v>1456</v>
       </c>
       <c r="N174" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O174">
         <v>1067.280000000001</v>
@@ -11114,13 +11117,13 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -11150,7 +11153,7 @@
         <v>579.26</v>
       </c>
       <c r="N175" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O175">
         <v>-487.8400000000001</v>
@@ -11170,13 +11173,13 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C176" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -11206,7 +11209,7 @@
         <v>1052.46</v>
       </c>
       <c r="N176" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O176">
         <v>-498.5099999999989</v>
@@ -11226,13 +11229,13 @@
         <v>77</v>
       </c>
       <c r="B177" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C177" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D177" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -11262,7 +11265,7 @@
         <v>878.7</v>
       </c>
       <c r="N177" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O177">
         <v>1129.725</v>
@@ -11285,13 +11288,13 @@
         <v>78</v>
       </c>
       <c r="B178" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C178" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D178" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11312,7 +11315,7 @@
         <v>458.15</v>
       </c>
       <c r="K178" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L178">
         <v>433.2</v>
@@ -11321,7 +11324,7 @@
         <v>429</v>
       </c>
       <c r="N178" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O178">
         <v>-567</v>
@@ -11341,13 +11344,13 @@
         <v>78</v>
       </c>
       <c r="B179" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C179" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D179" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -11377,7 +11380,7 @@
         <v>4221.32</v>
       </c>
       <c r="N179" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O179">
         <v>-444.3600000000006</v>
@@ -11397,13 +11400,13 @@
         <v>78</v>
       </c>
       <c r="B180" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C180" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D180" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -11433,7 +11436,7 @@
         <v>1245.6</v>
       </c>
       <c r="N180" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O180">
         <v>-500.5</v>
@@ -11453,13 +11456,13 @@
         <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C181" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -11489,7 +11492,7 @@
         <v>517.7</v>
       </c>
       <c r="N181" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O181">
         <v>-490.5</v>
@@ -11509,13 +11512,13 @@
         <v>79</v>
       </c>
       <c r="B182" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C182" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -11545,7 +11548,7 @@
         <v>545.58</v>
       </c>
       <c r="N182" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O182">
         <v>727.4400000000005</v>
@@ -11568,13 +11571,13 @@
         <v>80</v>
       </c>
       <c r="B183" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C183" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D183" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -11604,7 +11607,7 @@
         <v>1189.88</v>
       </c>
       <c r="N183" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O183">
         <v>-438.3399999999992</v>
@@ -11624,13 +11627,13 @@
         <v>80</v>
       </c>
       <c r="B184" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C184" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -11660,7 +11663,7 @@
         <v>1976.7</v>
       </c>
       <c r="N184" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O184">
         <v>949.7400000000002</v>
@@ -11683,13 +11686,13 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C185" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -11719,7 +11722,7 @@
         <v>965.15</v>
       </c>
       <c r="N185" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O185">
         <v>-457.2000000000006</v>
@@ -11739,13 +11742,13 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C186" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E186">
         <v>2</v>
@@ -11766,7 +11769,7 @@
         <v>1176.2</v>
       </c>
       <c r="K186" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L186">
         <v>1218.42</v>
@@ -11775,7 +11778,7 @@
         <v>1202.2</v>
       </c>
       <c r="N186" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O186">
         <v>334.3999999999996</v>
@@ -11795,13 +11798,13 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C187" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E187">
         <v>3</v>
@@ -11822,7 +11825,7 @@
         <v>3322.2</v>
       </c>
       <c r="K187" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L187">
         <v>3322.2</v>
@@ -11831,7 +11834,7 @@
         <v>3322.2</v>
       </c>
       <c r="N187" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O187">
         <v>1218</v>
@@ -11854,13 +11857,13 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C188" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D188" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -11881,7 +11884,7 @@
         <v>417.55</v>
       </c>
       <c r="K188" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L188">
         <v>411.44</v>
@@ -11890,7 +11893,7 @@
         <v>411.44</v>
       </c>
       <c r="N188" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O188">
         <v>-498.1800000000006</v>
@@ -11910,13 +11913,13 @@
         <v>83</v>
       </c>
       <c r="B189" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C189" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D189" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -11946,7 +11949,7 @@
         <v>4008.43</v>
       </c>
       <c r="N189" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O189">
         <v>-421.9399999999996</v>
@@ -11966,13 +11969,13 @@
         <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C190" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -12002,7 +12005,7 @@
         <v>434.05</v>
       </c>
       <c r="N190" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O190">
         <v>-479.8499999999993</v>
@@ -12022,13 +12025,13 @@
         <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C191" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E191">
         <v>3</v>
@@ -12049,7 +12052,7 @@
         <v>142.41</v>
       </c>
       <c r="K191" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L191">
         <v>140.15</v>
@@ -12058,7 +12061,7 @@
         <v>136</v>
       </c>
       <c r="N191" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O191">
         <v>831.9090000000007</v>
@@ -12073,7 +12076,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="S191" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -12081,13 +12084,13 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C192" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12117,7 +12120,7 @@
         <v>1604.74</v>
       </c>
       <c r="N192" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O192">
         <v>-422.3000000000002</v>
@@ -12137,13 +12140,13 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C193" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -12173,7 +12176,7 @@
         <v>984.77</v>
       </c>
       <c r="N193" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O193">
         <v>-466.4699999999993</v>
@@ -12193,13 +12196,13 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -12220,7 +12223,7 @@
         <v>287.5</v>
       </c>
       <c r="K194" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L194">
         <v>279.2</v>
@@ -12229,7 +12232,7 @@
         <v>279.2</v>
       </c>
       <c r="N194" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -12249,13 +12252,13 @@
         <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C195" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -12285,7 +12288,7 @@
         <v>658.2</v>
       </c>
       <c r="N195" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O195">
         <v>1241.880000000001</v>
@@ -12300,7 +12303,7 @@
         <v>12.83</v>
       </c>
       <c r="S195" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -12308,13 +12311,13 @@
         <v>87</v>
       </c>
       <c r="B196" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -12344,7 +12347,7 @@
         <v>1772.61</v>
       </c>
       <c r="N196" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O196">
         <v>590.8699999999999</v>
@@ -12367,13 +12370,13 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C197" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -12394,7 +12397,7 @@
         <v>96.47</v>
       </c>
       <c r="K197" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L197">
         <v>94.39</v>
@@ -12403,7 +12406,7 @@
         <v>94.39</v>
       </c>
       <c r="N197" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O197">
         <v>-496.9999999999999</v>
@@ -12423,13 +12426,13 @@
         <v>87</v>
       </c>
       <c r="B198" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C198" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D198" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -12459,7 +12462,7 @@
         <v>4343.88</v>
       </c>
       <c r="N198" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O198">
         <v>-457.2399999999998</v>
@@ -12479,13 +12482,13 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C199" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -12515,7 +12518,7 @@
         <v>1139.24</v>
       </c>
       <c r="N199" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O199">
         <v>-479.6800000000003</v>
@@ -12535,13 +12538,13 @@
         <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C200" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D200" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -12571,7 +12574,7 @@
         <v>1303.6</v>
       </c>
       <c r="N200" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -12591,13 +12594,13 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D201" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E201">
         <v>2</v>
@@ -12627,7 +12630,7 @@
         <v>6750.45</v>
       </c>
       <c r="N201" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O201">
         <v>321.4499999999998</v>
@@ -12647,13 +12650,13 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C202" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D202" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12683,7 +12686,7 @@
         <v>1166.88</v>
       </c>
       <c r="N202" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O202">
         <v>-491.3599999999988</v>
@@ -12703,13 +12706,13 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C203" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -12739,7 +12742,7 @@
         <v>892.45</v>
       </c>
       <c r="N203" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O203">
         <v>679.9750000000006</v>
@@ -12754,7 +12757,7 @@
         <v>7.27</v>
       </c>
       <c r="S203" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -12762,13 +12765,13 @@
         <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C204" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12798,7 +12801,7 @@
         <v>507.95</v>
       </c>
       <c r="N204" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O204">
         <v>-497.7000000000006</v>
@@ -12818,13 +12821,13 @@
         <v>90</v>
       </c>
       <c r="B205" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D205" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E205">
         <v>3</v>
@@ -12854,7 +12857,7 @@
         <v>7428.5</v>
       </c>
       <c r="N205" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O205">
         <v>668</v>
@@ -12874,13 +12877,13 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C206" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -12910,7 +12913,7 @@
         <v>552.09</v>
       </c>
       <c r="N206" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O206">
         <v>-494.0199999999991</v>
@@ -12930,13 +12933,13 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C207" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -12966,7 +12969,7 @@
         <v>350.38</v>
       </c>
       <c r="N207" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O207">
         <v>717.3800000000001</v>
@@ -12989,13 +12992,13 @@
         <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C208" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -13025,7 +13028,7 @@
         <v>496.04</v>
       </c>
       <c r="N208" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O208">
         <v>-496.0899999999992</v>
@@ -13045,13 +13048,13 @@
         <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C209" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -13081,7 +13084,7 @@
         <v>600.97</v>
       </c>
       <c r="N209" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O209">
         <v>-474.4499999999999</v>
@@ -13101,13 +13104,13 @@
         <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C210" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D210" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -13128,7 +13131,7 @@
         <v>259.75</v>
       </c>
       <c r="K210" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L210">
         <v>256.12</v>
@@ -13137,7 +13140,7 @@
         <v>256.12</v>
       </c>
       <c r="N210" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O210">
         <v>-498.7600000000007</v>
@@ -13157,13 +13160,13 @@
         <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C211" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -13193,7 +13196,7 @@
         <v>2756.14</v>
       </c>
       <c r="N211" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O211">
         <v>-435.1799999999998</v>
@@ -13213,13 +13216,13 @@
         <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C212" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -13249,7 +13252,7 @@
         <v>1420.1</v>
       </c>
       <c r="N212" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -13269,13 +13272,13 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C213" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -13305,7 +13308,7 @@
         <v>2098.84</v>
       </c>
       <c r="N213" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O213">
         <v>-441.8400000000001</v>
@@ -13325,13 +13328,13 @@
         <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D214" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E214">
         <v>2</v>
@@ -13361,7 +13364,7 @@
         <v>575.87</v>
       </c>
       <c r="N214" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O214">
         <v>740.3849999999999</v>
@@ -13376,7 +13379,7 @@
         <v>7.5</v>
       </c>
       <c r="S214" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -13384,1